--- a/outlook_2025.xlsx
+++ b/outlook_2025.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/896b44b4c208da2c/Documents/^NUW/Autumn 25/db_project/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_E97DD032EEFF7A45656FC4CC776F21ED797ADADE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="14295" yWindow="-16200" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ref2025.d032025a" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -592,13 +598,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -615,7 +619,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -623,7 +627,7 @@
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -639,7 +643,7 @@
     </font>
     <font>
       <b/>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -675,42 +679,374 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF000000"/>
-      </font>
-      <numFmt numFmtId="167" formatCode="0.0%"/>
-    </dxf>
+  <dxfs count="55">
     <dxf>
       <font>
         <color rgb="FF000000"/>
       </font>
-      <numFmt numFmtId="167" formatCode="0.0%"/>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
     </dxf>
     <dxf>
       <font>
         <b/>
         <color rgb="FF000000"/>
       </font>
-      <numFmt numFmtId="167" formatCode="0.0%"/>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
     </dxf>
     <dxf>
       <border>
@@ -724,29 +1060,23 @@
         <horizontal/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF000000"/>
-      </font>
-      <numFmt numFmtId="167" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF000000"/>
-      </font>
-      <numFmt numFmtId="167" formatCode="0.0%"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -784,7 +1114,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -818,6 +1148,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -852,9 +1183,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1027,22 +1359,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AD153"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="0" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="40.7109375" customWidth="1"/>
-    <col min="30" max="30" width="9.140625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="1" customFormat="1">
+    <row r="1" spans="1:30" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:30" s="2" customFormat="1"/>
-    <row r="3" spans="1:30" s="2" customFormat="1">
+    <row r="2" spans="1:30" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:30" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="C3" s="2" t="s">
         <v>180</v>
       </c>
@@ -1050,7 +1381,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="4" spans="1:30" s="2" customFormat="1">
+    <row r="4" spans="1:30" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="C4" s="2" t="s">
         <v>181</v>
       </c>
@@ -1061,7 +1392,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="5" spans="1:30" s="2" customFormat="1">
+    <row r="5" spans="1:30" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="C5" s="2" t="s">
         <v>182</v>
       </c>
@@ -1069,7 +1400,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="6" spans="1:30" s="2" customFormat="1">
+    <row r="6" spans="1:30" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="C6" s="2" t="s">
         <v>183</v>
       </c>
@@ -1077,22 +1408,22 @@
         <v>187</v>
       </c>
     </row>
-    <row r="7" spans="1:30" s="3" customFormat="1">
+    <row r="7" spans="1:30" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:30" s="4" customFormat="1">
+    <row r="8" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B8" s="4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:30" s="2" customFormat="1">
+    <row r="9" spans="1:30" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="AD9" s="2" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="10" spans="1:30" s="5" customFormat="1">
+    <row r="10" spans="1:30" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B10" s="5" t="s">
         <v>87</v>
       </c>
@@ -1181,19 +1512,19 @@
         <v>190</v>
       </c>
     </row>
-    <row r="11" spans="1:30" s="4" customFormat="1"/>
-    <row r="12" spans="1:30" s="6" customFormat="1">
+    <row r="11" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:30" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B12" s="6" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:30" s="4" customFormat="1"/>
-    <row r="14" spans="1:30" s="6" customFormat="1">
+    <row r="13" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:30" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B14" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="1:30" s="7" customFormat="1">
+    <row r="15" spans="1:30" s="7" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>0</v>
       </c>
@@ -1210,7 +1541,7 @@
         <v>102.9834060668945</v>
       </c>
       <c r="F15" s="7">
-        <v>104.3823089599609</v>
+        <v>104.38230895996089</v>
       </c>
       <c r="G15" s="7">
         <v>105.9497375488281</v>
@@ -1243,7 +1574,7 @@
         <v>120.4086380004883</v>
       </c>
       <c r="Q15" s="7">
-        <v>121.9526214599609</v>
+        <v>121.95262145996089</v>
       </c>
       <c r="R15" s="7">
         <v>123.4674987792969</v>
@@ -1255,7 +1586,7 @@
         <v>126.4302291870117</v>
       </c>
       <c r="U15" s="7">
-        <v>127.8888092041016</v>
+        <v>127.88880920410161</v>
       </c>
       <c r="V15" s="7">
         <v>129.3374328613281</v>
@@ -1267,7 +1598,7 @@
         <v>132.2179870605469</v>
       </c>
       <c r="Y15" s="7">
-        <v>133.6573028564453</v>
+        <v>133.65730285644531</v>
       </c>
       <c r="Z15" s="7">
         <v>135.1004333496094</v>
@@ -1279,13 +1610,13 @@
         <v>138.0076904296875</v>
       </c>
       <c r="AC15" s="7">
-        <v>139.4739532470703</v>
+        <v>139.47395324707031</v>
       </c>
       <c r="AD15" s="7">
-        <v>0.01263412320604695</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" s="7" customFormat="1">
+        <v>1.2634123206046949E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" s="7" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
         <v>1</v>
       </c>
@@ -1293,16 +1624,16 @@
         <v>91</v>
       </c>
       <c r="C16" s="7">
-        <v>2.742075204849243</v>
+        <v>2.7420752048492432</v>
       </c>
       <c r="D16" s="7">
         <v>2.676446676254272</v>
       </c>
       <c r="E16" s="7">
-        <v>2.951615810394287</v>
+        <v>2.9516158103942871</v>
       </c>
       <c r="F16" s="7">
-        <v>3.136872053146362</v>
+        <v>3.1368720531463619</v>
       </c>
       <c r="G16" s="7">
         <v>3.245102167129517</v>
@@ -1314,19 +1645,19 @@
         <v>3.235985279083252</v>
       </c>
       <c r="J16" s="7">
-        <v>3.227937936782837</v>
+        <v>3.2279379367828369</v>
       </c>
       <c r="K16" s="7">
-        <v>3.254823923110962</v>
+        <v>3.2548239231109619</v>
       </c>
       <c r="L16" s="7">
-        <v>3.29215931892395</v>
+        <v>3.2921593189239502</v>
       </c>
       <c r="M16" s="7">
-        <v>3.321621894836426</v>
+        <v>3.3216218948364258</v>
       </c>
       <c r="N16" s="7">
-        <v>3.336881875991821</v>
+        <v>3.3368818759918208</v>
       </c>
       <c r="O16" s="7">
         <v>3.335924386978149</v>
@@ -1335,49 +1666,49 @@
         <v>3.326909065246582</v>
       </c>
       <c r="Q16" s="7">
-        <v>3.320310592651367</v>
+        <v>3.3203105926513672</v>
       </c>
       <c r="R16" s="7">
-        <v>3.318532228469849</v>
+        <v>3.3185322284698491</v>
       </c>
       <c r="S16" s="7">
-        <v>3.321971654891968</v>
+        <v>3.3219716548919682</v>
       </c>
       <c r="T16" s="7">
-        <v>3.330599546432495</v>
+        <v>3.3305995464324951</v>
       </c>
       <c r="U16" s="7">
-        <v>3.342515707015991</v>
+        <v>3.3425157070159912</v>
       </c>
       <c r="V16" s="7">
         <v>3.357473611831665</v>
       </c>
       <c r="W16" s="7">
-        <v>3.376159429550171</v>
+        <v>3.3761594295501709</v>
       </c>
       <c r="X16" s="7">
-        <v>3.398342847824097</v>
+        <v>3.3983428478240971</v>
       </c>
       <c r="Y16" s="7">
-        <v>3.423772573471069</v>
+        <v>3.4237725734710689</v>
       </c>
       <c r="Z16" s="7">
         <v>3.451867818832397</v>
       </c>
       <c r="AA16" s="7">
-        <v>3.481558799743652</v>
+        <v>3.4815587997436519</v>
       </c>
       <c r="AB16" s="7">
-        <v>3.511919975280762</v>
+        <v>3.5119199752807622</v>
       </c>
       <c r="AC16" s="7">
-        <v>3.542278051376343</v>
+        <v>3.5422780513763432</v>
       </c>
       <c r="AD16" s="7">
-        <v>0.009896924176951538</v>
-      </c>
-    </row>
-    <row r="17" spans="1:30" s="8" customFormat="1">
+        <v>9.8969241769515381E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" s="8" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>2</v>
       </c>
@@ -1388,16 +1719,16 @@
         <v>103.3718719482422</v>
       </c>
       <c r="D17" s="8">
-        <v>104.5219497680664</v>
+        <v>104.52194976806641</v>
       </c>
       <c r="E17" s="8">
         <v>105.9350204467773</v>
       </c>
       <c r="F17" s="8">
-        <v>107.5191802978516</v>
+        <v>107.51918029785161</v>
       </c>
       <c r="G17" s="8">
-        <v>109.1948394775391</v>
+        <v>109.19483947753911</v>
       </c>
       <c r="H17" s="8">
         <v>110.8656845092773</v>
@@ -1409,31 +1740,31 @@
         <v>114.0929336547852</v>
       </c>
       <c r="K17" s="8">
-        <v>115.6983032226562</v>
+        <v>115.69830322265619</v>
       </c>
       <c r="L17" s="8">
-        <v>117.3196792602539</v>
+        <v>117.31967926025391</v>
       </c>
       <c r="M17" s="8">
         <v>118.9486465454102</v>
       </c>
       <c r="N17" s="8">
-        <v>120.5705718994141</v>
+        <v>120.57057189941411</v>
       </c>
       <c r="O17" s="8">
-        <v>122.1689224243164</v>
+        <v>122.16892242431641</v>
       </c>
       <c r="P17" s="8">
         <v>123.7355499267578</v>
       </c>
       <c r="Q17" s="8">
-        <v>125.2729339599609</v>
+        <v>125.27293395996089</v>
       </c>
       <c r="R17" s="8">
-        <v>126.7860336303711</v>
+        <v>126.78603363037109</v>
       </c>
       <c r="S17" s="8">
-        <v>128.2802124023438</v>
+        <v>128.28021240234381</v>
       </c>
       <c r="T17" s="8">
         <v>129.7608337402344</v>
@@ -1442,7 +1773,7 @@
         <v>131.2313232421875</v>
       </c>
       <c r="V17" s="8">
-        <v>132.6949005126953</v>
+        <v>132.69490051269531</v>
       </c>
       <c r="W17" s="8">
         <v>134.1553649902344</v>
@@ -1451,36 +1782,36 @@
         <v>135.6163330078125</v>
       </c>
       <c r="Y17" s="8">
-        <v>137.0810699462891</v>
+        <v>137.08106994628909</v>
       </c>
       <c r="Z17" s="8">
-        <v>138.5523071289062</v>
+        <v>138.55230712890619</v>
       </c>
       <c r="AA17" s="8">
-        <v>140.0316009521484</v>
+        <v>140.03160095214841</v>
       </c>
       <c r="AB17" s="8">
-        <v>141.5196075439453</v>
+        <v>141.51960754394531</v>
       </c>
       <c r="AC17" s="8">
         <v>143.0162353515625</v>
       </c>
       <c r="AD17" s="8">
-        <v>0.01256385743529265</v>
-      </c>
-    </row>
-    <row r="18" spans="1:30" s="4" customFormat="1"/>
-    <row r="19" spans="1:30" s="6" customFormat="1">
+        <v>1.256385743529265E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:30" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B19" s="6" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="1:30" s="6" customFormat="1">
+    <row r="20" spans="1:30" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B20" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="21" spans="1:30" s="7" customFormat="1">
+    <row r="21" spans="1:30" s="7" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
         <v>3</v>
       </c>
@@ -1488,91 +1819,91 @@
         <v>95</v>
       </c>
       <c r="C21" s="7">
-        <v>91.29741668701172</v>
+        <v>91.297416687011719</v>
       </c>
       <c r="D21" s="7">
-        <v>93.08963775634766</v>
+        <v>93.089637756347656</v>
       </c>
       <c r="E21" s="7">
-        <v>92.09773254394531</v>
+        <v>92.097732543945313</v>
       </c>
       <c r="F21" s="7">
-        <v>91.44508361816406</v>
+        <v>91.445083618164063</v>
       </c>
       <c r="G21" s="7">
-        <v>90.49540710449219</v>
+        <v>90.495407104492188</v>
       </c>
       <c r="H21" s="7">
-        <v>89.93583679199219</v>
+        <v>89.935836791992188</v>
       </c>
       <c r="I21" s="7">
         <v>89.15826416015625</v>
       </c>
       <c r="J21" s="7">
-        <v>88.45890808105469</v>
+        <v>88.458908081054688</v>
       </c>
       <c r="K21" s="7">
-        <v>87.73761749267578</v>
+        <v>87.737617492675781</v>
       </c>
       <c r="L21" s="7">
-        <v>86.97842407226562</v>
+        <v>86.978424072265625</v>
       </c>
       <c r="M21" s="7">
-        <v>86.33541107177734</v>
+        <v>86.335411071777344</v>
       </c>
       <c r="N21" s="7">
-        <v>85.87261199951172</v>
+        <v>85.872611999511719</v>
       </c>
       <c r="O21" s="7">
-        <v>85.58816528320312</v>
+        <v>85.588165283203125</v>
       </c>
       <c r="P21" s="7">
-        <v>85.41545104980469</v>
+        <v>85.415451049804688</v>
       </c>
       <c r="Q21" s="7">
-        <v>85.30679321289062</v>
+        <v>85.306793212890625</v>
       </c>
       <c r="R21" s="7">
-        <v>85.25411224365234</v>
+        <v>85.254112243652344</v>
       </c>
       <c r="S21" s="7">
-        <v>85.18038940429688</v>
+        <v>85.180389404296875</v>
       </c>
       <c r="T21" s="7">
-        <v>85.08011627197266</v>
+        <v>85.080116271972656</v>
       </c>
       <c r="U21" s="7">
-        <v>84.94991302490234</v>
+        <v>84.949913024902344</v>
       </c>
       <c r="V21" s="7">
-        <v>84.81881713867188</v>
+        <v>84.818817138671875</v>
       </c>
       <c r="W21" s="7">
-        <v>84.72840118408203</v>
+        <v>84.728401184082031</v>
       </c>
       <c r="X21" s="7">
-        <v>84.66356658935547</v>
+        <v>84.663566589355469</v>
       </c>
       <c r="Y21" s="7">
         <v>84.5985107421875</v>
       </c>
       <c r="Z21" s="7">
-        <v>84.58738708496094</v>
+        <v>84.587387084960938</v>
       </c>
       <c r="AA21" s="7">
-        <v>84.64241027832031</v>
+        <v>84.642410278320313</v>
       </c>
       <c r="AB21" s="7">
-        <v>84.75161743164062</v>
+        <v>84.751617431640625</v>
       </c>
       <c r="AC21" s="7">
-        <v>84.92007446289062</v>
+        <v>84.920074462890625</v>
       </c>
       <c r="AD21" s="7">
-        <v>-0.002781201378566189</v>
-      </c>
-    </row>
-    <row r="22" spans="1:30" s="7" customFormat="1">
+        <v>-2.7812013785661889E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" s="7" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
         <v>4</v>
       </c>
@@ -1580,102 +1911,102 @@
         <v>96</v>
       </c>
       <c r="C22" s="7">
-        <v>89.92622375488281</v>
+        <v>89.926223754882813</v>
       </c>
       <c r="D22" s="7">
-        <v>91.57162475585938</v>
+        <v>91.571624755859375</v>
       </c>
       <c r="E22" s="7">
-        <v>90.44429779052734</v>
+        <v>90.444297790527344</v>
       </c>
       <c r="F22" s="7">
-        <v>89.75080871582031</v>
+        <v>89.750808715820313</v>
       </c>
       <c r="G22" s="7">
-        <v>88.75996398925781</v>
+        <v>88.759963989257813</v>
       </c>
       <c r="H22" s="7">
-        <v>88.13794708251953</v>
+        <v>88.137947082519531</v>
       </c>
       <c r="I22" s="7">
-        <v>87.28134155273438</v>
+        <v>87.281341552734375</v>
       </c>
       <c r="J22" s="7">
-        <v>86.47559356689453</v>
+        <v>86.475593566894531</v>
       </c>
       <c r="K22" s="7">
         <v>85.68035888671875</v>
       </c>
       <c r="L22" s="7">
-        <v>84.81456756591797</v>
+        <v>84.814567565917969</v>
       </c>
       <c r="M22" s="7">
-        <v>84.11869049072266</v>
+        <v>84.118690490722656</v>
       </c>
       <c r="N22" s="7">
-        <v>83.61708831787109</v>
+        <v>83.617088317871094</v>
       </c>
       <c r="O22" s="7">
         <v>83.3077392578125</v>
       </c>
       <c r="P22" s="7">
-        <v>83.09767913818359</v>
+        <v>83.097679138183594</v>
       </c>
       <c r="Q22" s="7">
-        <v>82.97336578369141</v>
+        <v>82.973365783691406</v>
       </c>
       <c r="R22" s="7">
-        <v>82.92579650878906</v>
+        <v>82.925796508789063</v>
       </c>
       <c r="S22" s="7">
-        <v>82.83527374267578</v>
+        <v>82.835273742675781</v>
       </c>
       <c r="T22" s="7">
-        <v>82.70189666748047</v>
+        <v>82.701896667480469</v>
       </c>
       <c r="U22" s="7">
-        <v>82.52808380126953</v>
+        <v>82.528083801269531</v>
       </c>
       <c r="V22" s="7">
-        <v>82.34838104248047</v>
+        <v>82.348381042480469</v>
       </c>
       <c r="W22" s="7">
         <v>82.2064208984375</v>
       </c>
       <c r="X22" s="7">
-        <v>82.09544372558594</v>
+        <v>82.095443725585938</v>
       </c>
       <c r="Y22" s="7">
-        <v>81.97590637207031</v>
+        <v>81.975906372070313</v>
       </c>
       <c r="Z22" s="7">
-        <v>81.92298889160156</v>
+        <v>81.922988891601563</v>
       </c>
       <c r="AA22" s="7">
-        <v>81.93915557861328</v>
+        <v>81.939155578613281</v>
       </c>
       <c r="AB22" s="7">
         <v>82.02484130859375</v>
       </c>
       <c r="AC22" s="7">
-        <v>82.17780303955078</v>
+        <v>82.177803039550781</v>
       </c>
       <c r="AD22" s="7">
-        <v>-0.003459554538965626</v>
-      </c>
-    </row>
-    <row r="23" spans="1:30" s="4" customFormat="1"/>
-    <row r="24" spans="1:30" s="6" customFormat="1">
+        <v>-3.4595545389656261E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:30" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B24" s="6" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:30" s="6" customFormat="1">
+    <row r="25" spans="1:30" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B25" s="6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="26" spans="1:30" s="4" customFormat="1">
+    <row r="26" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>5</v>
       </c>
@@ -1683,31 +2014,31 @@
         <v>99</v>
       </c>
       <c r="C26" s="4">
-        <v>0.1865231543779373</v>
+        <v>0.18652315437793729</v>
       </c>
       <c r="D26" s="4">
         <v>0.1979862451553345</v>
       </c>
       <c r="E26" s="4">
-        <v>0.1980705112218857</v>
+        <v>0.19807051122188571</v>
       </c>
       <c r="F26" s="4">
-        <v>0.1991029381752014</v>
+        <v>0.19910293817520139</v>
       </c>
       <c r="G26" s="4">
-        <v>0.1990821212530136</v>
+        <v>0.19908212125301361</v>
       </c>
       <c r="H26" s="4">
-        <v>0.1979473829269409</v>
+        <v>0.19794738292694089</v>
       </c>
       <c r="I26" s="4">
-        <v>0.1964488625526428</v>
+        <v>0.19644886255264279</v>
       </c>
       <c r="J26" s="4">
-        <v>0.1947658658027649</v>
+        <v>0.19476586580276489</v>
       </c>
       <c r="K26" s="4">
-        <v>0.1931598484516144</v>
+        <v>0.19315984845161441</v>
       </c>
       <c r="L26" s="4">
         <v>0.1906101852655411</v>
@@ -1719,19 +2050,19 @@
         <v>0.1872121840715408</v>
       </c>
       <c r="O26" s="4">
-        <v>0.1864397376775742</v>
+        <v>0.18643973767757421</v>
       </c>
       <c r="P26" s="4">
-        <v>0.1856438666582108</v>
+        <v>0.18564386665821081</v>
       </c>
       <c r="Q26" s="4">
-        <v>0.1847200989723206</v>
+        <v>0.18472009897232061</v>
       </c>
       <c r="R26" s="4">
-        <v>0.1837673783302307</v>
+        <v>0.18376737833023071</v>
       </c>
       <c r="S26" s="4">
-        <v>0.1826205998659134</v>
+        <v>0.18262059986591339</v>
       </c>
       <c r="T26" s="4">
         <v>0.1812715828418732</v>
@@ -1743,31 +2074,31 @@
         <v>0.1777535080909729</v>
       </c>
       <c r="W26" s="4">
-        <v>0.1757447570562363</v>
+        <v>0.17574475705623629</v>
       </c>
       <c r="X26" s="4">
-        <v>0.1737014204263687</v>
+        <v>0.17370142042636871</v>
       </c>
       <c r="Y26" s="4">
-        <v>0.171582043170929</v>
+        <v>0.17158204317092901</v>
       </c>
       <c r="Z26" s="4">
-        <v>0.1695217192173004</v>
+        <v>0.16952171921730039</v>
       </c>
       <c r="AA26" s="4">
-        <v>0.1675739735364914</v>
+        <v>0.16757397353649139</v>
       </c>
       <c r="AB26" s="4">
-        <v>0.1657863110303879</v>
+        <v>0.16578631103038791</v>
       </c>
       <c r="AC26" s="4">
-        <v>0.1641120463609695</v>
+        <v>0.16411204636096949</v>
       </c>
       <c r="AD26" s="4">
-        <v>-0.004911207292382369</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30" s="4" customFormat="1">
+        <v>-4.9112072923823691E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>6</v>
       </c>
@@ -1775,91 +2106,91 @@
         <v>100</v>
       </c>
       <c r="C27" s="4">
-        <v>0.5728323459625244</v>
+        <v>0.57283234596252441</v>
       </c>
       <c r="D27" s="4">
-        <v>0.5553528070449829</v>
+        <v>0.55535280704498291</v>
       </c>
       <c r="E27" s="4">
-        <v>0.566855251789093</v>
+        <v>0.56685525178909302</v>
       </c>
       <c r="F27" s="4">
-        <v>0.5814115405082703</v>
+        <v>0.58141154050827026</v>
       </c>
       <c r="G27" s="4">
-        <v>0.5930807590484619</v>
+        <v>0.59308075904846191</v>
       </c>
       <c r="H27" s="4">
-        <v>0.6007307171821594</v>
+        <v>0.60073071718215942</v>
       </c>
       <c r="I27" s="4">
-        <v>0.6060745120048523</v>
+        <v>0.60607451200485229</v>
       </c>
       <c r="J27" s="4">
-        <v>0.6112245917320251</v>
+        <v>0.61122459173202515</v>
       </c>
       <c r="K27" s="4">
-        <v>0.6173355579376221</v>
+        <v>0.61733555793762207</v>
       </c>
       <c r="L27" s="4">
-        <v>0.622646152973175</v>
+        <v>0.62264615297317505</v>
       </c>
       <c r="M27" s="4">
-        <v>0.6290578246116638</v>
+        <v>0.62905782461166382</v>
       </c>
       <c r="N27" s="4">
-        <v>0.6370689272880554</v>
+        <v>0.63706892728805542</v>
       </c>
       <c r="O27" s="4">
-        <v>0.6466624140739441</v>
+        <v>0.64666241407394409</v>
       </c>
       <c r="P27" s="4">
-        <v>0.6569246053695679</v>
+        <v>0.65692460536956787</v>
       </c>
       <c r="Q27" s="4">
-        <v>0.6671252846717834</v>
+        <v>0.66712528467178345</v>
       </c>
       <c r="R27" s="4">
-        <v>0.677840530872345</v>
+        <v>0.67784053087234497</v>
       </c>
       <c r="S27" s="4">
-        <v>0.6879954934120178</v>
+        <v>0.68799549341201782</v>
       </c>
       <c r="T27" s="4">
-        <v>0.6979280710220337</v>
+        <v>0.69792807102203369</v>
       </c>
       <c r="U27" s="4">
-        <v>0.7068910598754883</v>
+        <v>0.70689105987548828</v>
       </c>
       <c r="V27" s="4">
-        <v>0.7158882021903992</v>
+        <v>0.71588820219039917</v>
       </c>
       <c r="W27" s="4">
-        <v>0.7247987985610962</v>
+        <v>0.72479879856109619</v>
       </c>
       <c r="X27" s="4">
-        <v>0.733715295791626</v>
+        <v>0.73371529579162598</v>
       </c>
       <c r="Y27" s="4">
-        <v>0.7425738573074341</v>
+        <v>0.74257385730743408</v>
       </c>
       <c r="Z27" s="4">
-        <v>0.7519573569297791</v>
+        <v>0.75195735692977905</v>
       </c>
       <c r="AA27" s="4">
-        <v>0.76215660572052</v>
+        <v>0.76215660572052002</v>
       </c>
       <c r="AB27" s="4">
-        <v>0.7735642194747925</v>
+        <v>0.77356421947479248</v>
       </c>
       <c r="AC27" s="4">
-        <v>0.7861006259918213</v>
+        <v>0.78610062599182129</v>
       </c>
       <c r="AD27" s="4">
-        <v>0.01224714814471706</v>
-      </c>
-    </row>
-    <row r="28" spans="1:30" s="4" customFormat="1">
+        <v>1.2247148144717061E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>7</v>
       </c>
@@ -1867,91 +2198,91 @@
         <v>101</v>
       </c>
       <c r="C28" s="4">
-        <v>0.07448957115411758</v>
+        <v>7.4489571154117584E-2</v>
       </c>
       <c r="D28" s="4">
-        <v>0.07405783981084824</v>
+        <v>7.4057839810848236E-2</v>
       </c>
       <c r="E28" s="4">
-        <v>0.07415957748889923</v>
+        <v>7.4159577488899231E-2</v>
       </c>
       <c r="F28" s="4">
-        <v>0.07469534128904343</v>
+        <v>7.4695341289043427E-2</v>
       </c>
       <c r="G28" s="4">
-        <v>0.07483182102441788</v>
+        <v>7.4831821024417877E-2</v>
       </c>
       <c r="H28" s="4">
-        <v>0.07446745783090591</v>
+        <v>7.4467457830905914E-2</v>
       </c>
       <c r="I28" s="4">
-        <v>0.07381346076726913</v>
+        <v>7.3813460767269135E-2</v>
       </c>
       <c r="J28" s="4">
-        <v>0.0730288103222847</v>
+        <v>7.3028810322284698E-2</v>
       </c>
       <c r="K28" s="4">
-        <v>0.07231543958187103</v>
+        <v>7.2315439581871033E-2</v>
       </c>
       <c r="L28" s="4">
-        <v>0.07146961241960526</v>
+        <v>7.1469612419605255E-2</v>
       </c>
       <c r="M28" s="4">
-        <v>0.07071322202682495</v>
+        <v>7.0713222026824951E-2</v>
       </c>
       <c r="N28" s="4">
-        <v>0.07008703052997589</v>
+        <v>7.0087030529975891E-2</v>
       </c>
       <c r="O28" s="4">
-        <v>0.06961338967084885</v>
+        <v>6.9613389670848846E-2</v>
       </c>
       <c r="P28" s="4">
-        <v>0.06917618960142136</v>
+        <v>6.9176189601421356E-2</v>
       </c>
       <c r="Q28" s="4">
-        <v>0.06871427595615387</v>
+        <v>6.871427595615387E-2</v>
       </c>
       <c r="R28" s="4">
-        <v>0.06826204061508179</v>
+        <v>6.8262040615081787E-2</v>
       </c>
       <c r="S28" s="4">
-        <v>0.0677487775683403</v>
+        <v>6.7748777568340302E-2</v>
       </c>
       <c r="T28" s="4">
-        <v>0.06716802716255188</v>
+        <v>6.716802716255188E-2</v>
       </c>
       <c r="U28" s="4">
-        <v>0.06647238880395889</v>
+        <v>6.6472388803958893E-2</v>
       </c>
       <c r="V28" s="4">
-        <v>0.06573563814163208</v>
+        <v>6.573563814163208E-2</v>
       </c>
       <c r="W28" s="4">
-        <v>0.06497213989496231</v>
+        <v>6.4972139894962311E-2</v>
       </c>
       <c r="X28" s="4">
-        <v>0.06419967114925385</v>
+        <v>6.4199671149253845E-2</v>
       </c>
       <c r="Y28" s="4">
-        <v>0.06341559439897537</v>
+        <v>6.3415594398975372E-2</v>
       </c>
       <c r="Z28" s="4">
-        <v>0.06266665458679199</v>
+        <v>6.2666654586791992E-2</v>
       </c>
       <c r="AA28" s="4">
-        <v>0.06196612864732742</v>
+        <v>6.1966128647327423E-2</v>
       </c>
       <c r="AB28" s="4">
-        <v>0.06132806837558746</v>
+        <v>6.1328068375587463E-2</v>
       </c>
       <c r="AC28" s="4">
-        <v>0.0607495903968811</v>
+        <v>6.0749590396881097E-2</v>
       </c>
       <c r="AD28" s="4">
-        <v>-0.007811590901369847</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30" s="4" customFormat="1">
+        <v>-7.811590901369847E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>8</v>
       </c>
@@ -1959,91 +2290,91 @@
         <v>102</v>
       </c>
       <c r="C29" s="4">
-        <v>0.7446191310882568</v>
+        <v>0.74461913108825684</v>
       </c>
       <c r="D29" s="4">
-        <v>0.7564954161643982</v>
+        <v>0.75649541616439819</v>
       </c>
       <c r="E29" s="4">
         <v>0.7730255126953125</v>
       </c>
       <c r="F29" s="4">
-        <v>0.7947636842727661</v>
+        <v>0.79476368427276611</v>
       </c>
       <c r="G29" s="4">
-        <v>0.8128076195716858</v>
+        <v>0.81280761957168579</v>
       </c>
       <c r="H29" s="4">
-        <v>0.8256902098655701</v>
+        <v>0.82569020986557007</v>
       </c>
       <c r="I29" s="4">
-        <v>0.8330134153366089</v>
+        <v>0.83301341533660889</v>
       </c>
       <c r="J29" s="4">
-        <v>0.8399519920349121</v>
+        <v>0.83995199203491211</v>
       </c>
       <c r="K29" s="4">
-        <v>0.8478609323501587</v>
+        <v>0.84786093235015869</v>
       </c>
       <c r="L29" s="4">
-        <v>0.8551452159881592</v>
+        <v>0.85514521598815918</v>
       </c>
       <c r="M29" s="4">
-        <v>0.8636964559555054</v>
+        <v>0.86369645595550537</v>
       </c>
       <c r="N29" s="4">
-        <v>0.8739328980445862</v>
+        <v>0.87393289804458618</v>
       </c>
       <c r="O29" s="4">
-        <v>0.8862233757972717</v>
+        <v>0.88622337579727173</v>
       </c>
       <c r="P29" s="4">
-        <v>0.8987996578216553</v>
+        <v>0.89879965782165527</v>
       </c>
       <c r="Q29" s="4">
-        <v>0.9113155007362366</v>
+        <v>0.91131550073623657</v>
       </c>
       <c r="R29" s="4">
-        <v>0.9241510033607483</v>
+        <v>0.92415100336074829</v>
       </c>
       <c r="S29" s="4">
-        <v>0.9365066289901733</v>
+        <v>0.93650662899017334</v>
       </c>
       <c r="T29" s="4">
-        <v>0.9482896327972412</v>
+        <v>0.94828963279724121</v>
       </c>
       <c r="U29" s="4">
-        <v>0.9588725566864014</v>
+        <v>0.95887255668640137</v>
       </c>
       <c r="V29" s="4">
-        <v>0.968958854675293</v>
+        <v>0.96895885467529297</v>
       </c>
       <c r="W29" s="4">
-        <v>0.9787622690200806</v>
+        <v>0.97876226902008057</v>
       </c>
       <c r="X29" s="4">
-        <v>0.9886872172355652</v>
+        <v>0.98868721723556519</v>
       </c>
       <c r="Y29" s="4">
-        <v>0.9984681606292725</v>
+        <v>0.99846816062927246</v>
       </c>
       <c r="Z29" s="4">
         <v>1.008850574493408</v>
       </c>
       <c r="AA29" s="4">
-        <v>1.020036816596985</v>
+        <v>1.0200368165969851</v>
       </c>
       <c r="AB29" s="4">
-        <v>1.032297134399414</v>
+        <v>1.0322971343994141</v>
       </c>
       <c r="AC29" s="4">
-        <v>1.045639514923096</v>
+        <v>1.0456395149230959</v>
       </c>
       <c r="AD29" s="4">
-        <v>0.01314374874526014</v>
-      </c>
-    </row>
-    <row r="30" spans="1:30" s="4" customFormat="1">
+        <v>1.314374874526014E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>9</v>
       </c>
@@ -2051,91 +2382,91 @@
         <v>103</v>
       </c>
       <c r="C30" s="4">
-        <v>0.08435720950365067</v>
+        <v>8.4357209503650665E-2</v>
       </c>
       <c r="D30" s="4">
-        <v>0.08457059413194656</v>
+        <v>8.4570594131946564E-2</v>
       </c>
       <c r="E30" s="4">
-        <v>0.08503340929746628</v>
+        <v>8.5033409297466278E-2</v>
       </c>
       <c r="F30" s="4">
-        <v>0.08595827966928482</v>
+        <v>8.5958279669284821E-2</v>
       </c>
       <c r="G30" s="4">
-        <v>0.08644069731235504</v>
+        <v>8.6440697312355042E-2</v>
       </c>
       <c r="H30" s="4">
-        <v>0.08634744584560394</v>
+        <v>8.6347445845603943E-2</v>
       </c>
       <c r="I30" s="4">
-        <v>0.08592312037944794</v>
+        <v>8.5923120379447937E-2</v>
       </c>
       <c r="J30" s="4">
-        <v>0.08539837598800659</v>
+        <v>8.5398375988006592E-2</v>
       </c>
       <c r="K30" s="4">
-        <v>0.08494658023118973</v>
+        <v>8.4946580231189728E-2</v>
       </c>
       <c r="L30" s="4">
-        <v>0.08440286666154861</v>
+        <v>8.4402866661548615E-2</v>
       </c>
       <c r="M30" s="4">
-        <v>0.0839560255408287</v>
+        <v>8.3956025540828705E-2</v>
       </c>
       <c r="N30" s="4">
-        <v>0.08365260064601898</v>
+        <v>8.3652600646018982E-2</v>
       </c>
       <c r="O30" s="4">
-        <v>0.08352412283420563</v>
+        <v>8.3524122834205627E-2</v>
       </c>
       <c r="P30" s="4">
-        <v>0.08339636027812958</v>
+        <v>8.3396360278129578E-2</v>
       </c>
       <c r="Q30" s="4">
-        <v>0.08321172744035721</v>
+        <v>8.3211727440357208E-2</v>
       </c>
       <c r="R30" s="4">
-        <v>0.08300384879112244</v>
+        <v>8.3003848791122437E-2</v>
       </c>
       <c r="S30" s="4">
-        <v>0.08271349966526031</v>
+        <v>8.2713499665260315E-2</v>
       </c>
       <c r="T30" s="4">
-        <v>0.08236639201641083</v>
+        <v>8.2366392016410828E-2</v>
       </c>
       <c r="U30" s="4">
-        <v>0.08189582824707031</v>
+        <v>8.1895828247070313E-2</v>
       </c>
       <c r="V30" s="4">
-        <v>0.08136520534753799</v>
+        <v>8.1365205347537994E-2</v>
       </c>
       <c r="W30" s="4">
-        <v>0.08079382032155991</v>
+        <v>8.0793820321559906E-2</v>
       </c>
       <c r="X30" s="4">
-        <v>0.08020898699760437</v>
+        <v>8.020898699760437E-2</v>
       </c>
       <c r="Y30" s="4">
-        <v>0.07958963513374329</v>
+        <v>7.9589635133743286E-2</v>
       </c>
       <c r="Z30" s="4">
-        <v>0.07899990677833557</v>
+        <v>7.8999906778335571E-2</v>
       </c>
       <c r="AA30" s="4">
-        <v>0.078455850481987</v>
+        <v>7.8455850481987E-2</v>
       </c>
       <c r="AB30" s="4">
-        <v>0.07797322422266006</v>
+        <v>7.7973224222660065E-2</v>
       </c>
       <c r="AC30" s="4">
-        <v>0.07755403220653534</v>
+        <v>7.7554032206535339E-2</v>
       </c>
       <c r="AD30" s="4">
-        <v>-0.003228829675377631</v>
-      </c>
-    </row>
-    <row r="31" spans="1:30" s="4" customFormat="1">
+        <v>-3.2288296753776309E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>10</v>
       </c>
@@ -2143,7 +2474,7 @@
         <v>104</v>
       </c>
       <c r="C31" s="4">
-        <v>0.5755947232246399</v>
+        <v>0.57559472322463989</v>
       </c>
       <c r="D31" s="4">
         <v>0.5640031099319458</v>
@@ -2152,82 +2483,82 @@
         <v>0.5612906813621521</v>
       </c>
       <c r="F31" s="4">
-        <v>0.5649812817573547</v>
+        <v>0.56498128175735474</v>
       </c>
       <c r="G31" s="4">
-        <v>0.5679190754890442</v>
+        <v>0.56791907548904419</v>
       </c>
       <c r="H31" s="4">
-        <v>0.5683069229125977</v>
+        <v>0.56830692291259766</v>
       </c>
       <c r="I31" s="4">
-        <v>0.5582931637763977</v>
+        <v>0.55829316377639771</v>
       </c>
       <c r="J31" s="4">
-        <v>0.5493459105491638</v>
+        <v>0.54934591054916382</v>
       </c>
       <c r="K31" s="4">
-        <v>0.5419877767562866</v>
+        <v>0.54198777675628662</v>
       </c>
       <c r="L31" s="4">
-        <v>0.5346543788909912</v>
+        <v>0.53465437889099121</v>
       </c>
       <c r="M31" s="4">
-        <v>0.5281133651733398</v>
+        <v>0.52811336517333984</v>
       </c>
       <c r="N31" s="4">
-        <v>0.5227332711219788</v>
+        <v>0.52273327112197876</v>
       </c>
       <c r="O31" s="4">
-        <v>0.5190929174423218</v>
+        <v>0.51909291744232178</v>
       </c>
       <c r="P31" s="4">
-        <v>0.5165110230445862</v>
+        <v>0.51651102304458618</v>
       </c>
       <c r="Q31" s="4">
-        <v>0.5145660042762756</v>
+        <v>0.51456600427627563</v>
       </c>
       <c r="R31" s="4">
-        <v>0.51337069272995</v>
+        <v>0.51337069272994995</v>
       </c>
       <c r="S31" s="4">
-        <v>0.5109866857528687</v>
+        <v>0.51098668575286865</v>
       </c>
       <c r="T31" s="4">
-        <v>0.5093018412590027</v>
+        <v>0.50930184125900269</v>
       </c>
       <c r="U31" s="4">
-        <v>0.5074021220207214</v>
+        <v>0.50740212202072144</v>
       </c>
       <c r="V31" s="4">
-        <v>0.5057253837585449</v>
+        <v>0.50572538375854492</v>
       </c>
       <c r="W31" s="4">
-        <v>0.5042718648910522</v>
+        <v>0.50427186489105225</v>
       </c>
       <c r="X31" s="4">
         <v>0.5030590295791626</v>
       </c>
       <c r="Y31" s="4">
-        <v>0.5016676187515259</v>
+        <v>0.50166761875152588</v>
       </c>
       <c r="Z31" s="4">
-        <v>0.5007129907608032</v>
+        <v>0.50071299076080322</v>
       </c>
       <c r="AA31" s="4">
         <v>0.5003892183303833</v>
       </c>
       <c r="AB31" s="4">
-        <v>0.5006906390190125</v>
+        <v>0.50069063901901245</v>
       </c>
       <c r="AC31" s="4">
-        <v>0.5018773674964905</v>
+        <v>0.50187736749649048</v>
       </c>
       <c r="AD31" s="4">
-        <v>-0.005257209385896688</v>
-      </c>
-    </row>
-    <row r="32" spans="1:30" s="4" customFormat="1">
+        <v>-5.2572093858966884E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>11</v>
       </c>
@@ -2235,10 +2566,10 @@
         <v>105</v>
       </c>
       <c r="C32" s="4">
-        <v>0.3673001527786255</v>
+        <v>0.36730015277862549</v>
       </c>
       <c r="D32" s="4">
-        <v>0.3686024844646454</v>
+        <v>0.36860248446464539</v>
       </c>
       <c r="E32" s="4">
         <v>0.3707335889339447</v>
@@ -2247,79 +2578,79 @@
         <v>0.3743739128112793</v>
       </c>
       <c r="G32" s="4">
-        <v>0.3776519894599915</v>
+        <v>0.37765198945999151</v>
       </c>
       <c r="H32" s="4">
-        <v>0.3800609707832336</v>
+        <v>0.38006097078323359</v>
       </c>
       <c r="I32" s="4">
-        <v>0.3808006942272186</v>
+        <v>0.38080069422721857</v>
       </c>
       <c r="J32" s="4">
-        <v>0.3818013370037079</v>
+        <v>0.38180133700370789</v>
       </c>
       <c r="K32" s="4">
-        <v>0.3831851482391357</v>
+        <v>0.38318514823913569</v>
       </c>
       <c r="L32" s="4">
-        <v>0.3846486806869507</v>
+        <v>0.38464868068695068</v>
       </c>
       <c r="M32" s="4">
-        <v>0.3864732086658478</v>
+        <v>0.38647320866584778</v>
       </c>
       <c r="N32" s="4">
-        <v>0.3886882364749908</v>
+        <v>0.38868823647499079</v>
       </c>
       <c r="O32" s="4">
-        <v>0.3912994265556335</v>
+        <v>0.39129942655563349</v>
       </c>
       <c r="P32" s="4">
         <v>0.393959641456604</v>
       </c>
       <c r="Q32" s="4">
-        <v>0.3965804278850555</v>
+        <v>0.39658042788505549</v>
       </c>
       <c r="R32" s="4">
-        <v>0.3992148637771606</v>
+        <v>0.39921486377716059</v>
       </c>
       <c r="S32" s="4">
-        <v>0.4017241299152374</v>
+        <v>0.40172412991523743</v>
       </c>
       <c r="T32" s="4">
-        <v>0.4043815433979034</v>
+        <v>0.40438154339790339</v>
       </c>
       <c r="U32" s="4">
-        <v>0.4068149924278259</v>
+        <v>0.40681499242782593</v>
       </c>
       <c r="V32" s="4">
-        <v>0.4091392755508423</v>
+        <v>0.40913927555084229</v>
       </c>
       <c r="W32" s="4">
-        <v>0.4113937616348267</v>
+        <v>0.41139376163482672</v>
       </c>
       <c r="X32" s="4">
-        <v>0.4136457741260529</v>
+        <v>0.41364577412605291</v>
       </c>
       <c r="Y32" s="4">
-        <v>0.4158335328102112</v>
+        <v>0.41583353281021118</v>
       </c>
       <c r="Z32" s="4">
-        <v>0.4180770814418793</v>
+        <v>0.41807708144187927</v>
       </c>
       <c r="AA32" s="4">
-        <v>0.4204134047031403</v>
+        <v>0.42041340470314031</v>
       </c>
       <c r="AB32" s="4">
-        <v>0.4228944480419159</v>
+        <v>0.42289444804191589</v>
       </c>
       <c r="AC32" s="4">
-        <v>0.4255006313323975</v>
+        <v>0.42550063133239752</v>
       </c>
       <c r="AD32" s="4">
-        <v>0.00567322687411842</v>
-      </c>
-    </row>
-    <row r="33" spans="1:30" s="4" customFormat="1">
+        <v>5.67322687411842E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>12</v>
       </c>
@@ -2327,70 +2658,70 @@
         <v>106</v>
       </c>
       <c r="C33" s="4">
-        <v>0.3410233557224274</v>
+        <v>0.34102335572242742</v>
       </c>
       <c r="D33" s="4">
-        <v>0.3573471009731293</v>
+        <v>0.35734710097312927</v>
       </c>
       <c r="E33" s="4">
-        <v>0.3753615021705627</v>
+        <v>0.37536150217056269</v>
       </c>
       <c r="F33" s="4">
-        <v>0.3948878943920135</v>
+        <v>0.39488789439201349</v>
       </c>
       <c r="G33" s="4">
-        <v>0.4153228402137756</v>
+        <v>0.41532284021377558</v>
       </c>
       <c r="H33" s="4">
-        <v>0.4354186654090881</v>
+        <v>0.43541866540908808</v>
       </c>
       <c r="I33" s="4">
-        <v>0.4556160271167755</v>
+        <v>0.45561602711677551</v>
       </c>
       <c r="J33" s="4">
-        <v>0.4765667021274567</v>
+        <v>0.47656670212745672</v>
       </c>
       <c r="K33" s="4">
-        <v>0.498712956905365</v>
+        <v>0.49871295690536499</v>
       </c>
       <c r="L33" s="4">
-        <v>0.5220028162002563</v>
+        <v>0.52200281620025635</v>
       </c>
       <c r="M33" s="4">
-        <v>0.5467246770858765</v>
+        <v>0.54672467708587646</v>
       </c>
       <c r="N33" s="4">
-        <v>0.5729601979255676</v>
+        <v>0.57296019792556763</v>
       </c>
       <c r="O33" s="4">
         <v>0.6007838249206543</v>
       </c>
       <c r="P33" s="4">
-        <v>0.6306106448173523</v>
+        <v>0.63061064481735229</v>
       </c>
       <c r="Q33" s="4">
-        <v>0.6613415479660034</v>
+        <v>0.66134154796600342</v>
       </c>
       <c r="R33" s="4">
-        <v>0.6936936974525452</v>
+        <v>0.69369369745254517</v>
       </c>
       <c r="S33" s="4">
-        <v>0.7276855111122131</v>
+        <v>0.72768551111221313</v>
       </c>
       <c r="T33" s="4">
-        <v>0.7633203268051147</v>
+        <v>0.76332032680511475</v>
       </c>
       <c r="U33" s="4">
         <v>0.7999948263168335</v>
       </c>
       <c r="V33" s="4">
-        <v>0.8378559350967407</v>
+        <v>0.83785593509674072</v>
       </c>
       <c r="W33" s="4">
-        <v>0.8777375817298889</v>
+        <v>0.87773758172988892</v>
       </c>
       <c r="X33" s="4">
-        <v>0.9190672636032104</v>
+        <v>0.91906726360321045</v>
       </c>
       <c r="Y33" s="4">
         <v>0.9618690013885498</v>
@@ -2399,19 +2730,19 @@
         <v>1.007150530815125</v>
       </c>
       <c r="AA33" s="4">
-        <v>1.054268836975098</v>
+        <v>1.0542688369750981</v>
       </c>
       <c r="AB33" s="4">
         <v>1.102479934692383</v>
       </c>
       <c r="AC33" s="4">
-        <v>1.153587460517883</v>
+        <v>1.1535874605178831</v>
       </c>
       <c r="AD33" s="4">
-        <v>0.0479882179842217</v>
-      </c>
-    </row>
-    <row r="34" spans="1:30" s="4" customFormat="1">
+        <v>4.7988217984221697E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>13</v>
       </c>
@@ -2419,91 +2750,91 @@
         <v>107</v>
       </c>
       <c r="C34" s="4">
-        <v>0.04323187842965126</v>
+        <v>4.323187842965126E-2</v>
       </c>
       <c r="D34" s="4">
-        <v>0.043303232640028</v>
+        <v>4.3303232640028E-2</v>
       </c>
       <c r="E34" s="4">
-        <v>0.04352026432752609</v>
+        <v>4.3520264327526093E-2</v>
       </c>
       <c r="F34" s="4">
-        <v>0.04388755932450294</v>
+        <v>4.3887559324502938E-2</v>
       </c>
       <c r="G34" s="4">
-        <v>0.04433385282754898</v>
+        <v>4.4333852827548981E-2</v>
       </c>
       <c r="H34" s="4">
-        <v>0.04471053555607796</v>
+        <v>4.4710535556077957E-2</v>
       </c>
       <c r="I34" s="4">
-        <v>0.04503057524561882</v>
+        <v>4.503057524561882E-2</v>
       </c>
       <c r="J34" s="4">
-        <v>0.04537007585167885</v>
+        <v>4.5370075851678848E-2</v>
       </c>
       <c r="K34" s="4">
-        <v>0.04571310058236122</v>
+        <v>4.5713100582361221E-2</v>
       </c>
       <c r="L34" s="4">
-        <v>0.04610182344913483</v>
+        <v>4.6101823449134827E-2</v>
       </c>
       <c r="M34" s="4">
-        <v>0.04655520617961884</v>
+        <v>4.6555206179618842E-2</v>
       </c>
       <c r="N34" s="4">
-        <v>0.04701841622591019</v>
+        <v>4.7018416225910187E-2</v>
       </c>
       <c r="O34" s="4">
-        <v>0.04749026149511337</v>
+        <v>4.7490261495113373E-2</v>
       </c>
       <c r="P34" s="4">
-        <v>0.04795121029019356</v>
+        <v>4.7951210290193558E-2</v>
       </c>
       <c r="Q34" s="4">
-        <v>0.04833761230111122</v>
+        <v>4.8337612301111221E-2</v>
       </c>
       <c r="R34" s="4">
-        <v>0.04871273040771484</v>
+        <v>4.8712730407714837E-2</v>
       </c>
       <c r="S34" s="4">
-        <v>0.04900911450386047</v>
+        <v>4.9009114503860467E-2</v>
       </c>
       <c r="T34" s="4">
-        <v>0.04915787652134895</v>
+        <v>4.9157876521348953E-2</v>
       </c>
       <c r="U34" s="4">
-        <v>0.04921872913837433</v>
+        <v>4.9218729138374329E-2</v>
       </c>
       <c r="V34" s="4">
-        <v>0.04919819161295891</v>
+        <v>4.9198191612958908E-2</v>
       </c>
       <c r="W34" s="4">
-        <v>0.04903504624962807</v>
+        <v>4.9035046249628067E-2</v>
       </c>
       <c r="X34" s="4">
-        <v>0.04866769164800644</v>
+        <v>4.8667691648006439E-2</v>
       </c>
       <c r="Y34" s="4">
-        <v>0.04821724072098732</v>
+        <v>4.821724072098732E-2</v>
       </c>
       <c r="Z34" s="4">
-        <v>0.04755975306034088</v>
+        <v>4.7559753060340881E-2</v>
       </c>
       <c r="AA34" s="4">
-        <v>0.04669306799769402</v>
+        <v>4.6693067997694022E-2</v>
       </c>
       <c r="AB34" s="4">
-        <v>0.045680221170187</v>
+        <v>4.5680221170187003E-2</v>
       </c>
       <c r="AC34" s="4">
-        <v>0.04444917663931847</v>
+        <v>4.4449176639318473E-2</v>
       </c>
       <c r="AD34" s="4">
-        <v>0.001068581633108634</v>
-      </c>
-    </row>
-    <row r="35" spans="1:30" s="4" customFormat="1">
+        <v>1.068581633108634E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>14</v>
       </c>
@@ -2511,31 +2842,31 @@
         <v>108</v>
       </c>
       <c r="C35" s="4">
-        <v>1.90110981464386</v>
+        <v>1.9011098146438601</v>
       </c>
       <c r="D35" s="4">
-        <v>1.978697061538696</v>
+        <v>1.9786970615386961</v>
       </c>
       <c r="E35" s="4">
-        <v>1.908885359764099</v>
+        <v>1.9088853597640989</v>
       </c>
       <c r="F35" s="4">
-        <v>1.895129084587097</v>
+        <v>1.8951290845870969</v>
       </c>
       <c r="G35" s="4">
-        <v>1.879241585731506</v>
+        <v>1.8792415857315059</v>
       </c>
       <c r="H35" s="4">
         <v>1.913681626319885</v>
       </c>
       <c r="I35" s="4">
-        <v>1.944713473320007</v>
+        <v>1.9447134733200071</v>
       </c>
       <c r="J35" s="4">
-        <v>1.974898815155029</v>
+        <v>1.9748988151550291</v>
       </c>
       <c r="K35" s="4">
-        <v>2.005690097808838</v>
+        <v>2.0056900978088379</v>
       </c>
       <c r="L35" s="4">
         <v>2.037068367004395</v>
@@ -2550,40 +2881,40 @@
         <v>2.140647172927856</v>
       </c>
       <c r="P35" s="4">
-        <v>2.177844285964966</v>
+        <v>2.1778442859649658</v>
       </c>
       <c r="Q35" s="4">
-        <v>2.215766191482544</v>
+        <v>2.2157661914825439</v>
       </c>
       <c r="R35" s="4">
-        <v>2.254404306411743</v>
+        <v>2.2544043064117432</v>
       </c>
       <c r="S35" s="4">
-        <v>2.293491840362549</v>
+        <v>2.2934918403625488</v>
       </c>
       <c r="T35" s="4">
-        <v>2.332742691040039</v>
+        <v>2.3327426910400391</v>
       </c>
       <c r="U35" s="4">
-        <v>2.372154474258423</v>
+        <v>2.3721544742584229</v>
       </c>
       <c r="V35" s="4">
         <v>2.412049293518066</v>
       </c>
       <c r="W35" s="4">
-        <v>2.452809810638428</v>
+        <v>2.4528098106384282</v>
       </c>
       <c r="X35" s="4">
-        <v>2.494549512863159</v>
+        <v>2.4945495128631592</v>
       </c>
       <c r="Y35" s="4">
         <v>2.536953449249268</v>
       </c>
       <c r="Z35" s="4">
-        <v>2.580348253250122</v>
+        <v>2.5803482532501221</v>
       </c>
       <c r="AA35" s="4">
-        <v>2.625485420227051</v>
+        <v>2.6254854202270508</v>
       </c>
       <c r="AB35" s="4">
         <v>2.672209739685059</v>
@@ -2592,10 +2923,10 @@
         <v>2.720864057540894</v>
       </c>
       <c r="AD35" s="4">
-        <v>0.01388441585571698</v>
-      </c>
-    </row>
-    <row r="36" spans="1:30" s="6" customFormat="1">
+        <v>1.3884415855716981E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
         <v>15</v>
       </c>
@@ -2603,64 +2934,64 @@
         <v>109</v>
       </c>
       <c r="C36" s="6">
-        <v>4.8910813331604</v>
+        <v>4.8910813331604004</v>
       </c>
       <c r="D36" s="6">
-        <v>4.980415821075439</v>
+        <v>4.9804158210754386</v>
       </c>
       <c r="E36" s="6">
-        <v>4.956935405731201</v>
+        <v>4.9569354057312012</v>
       </c>
       <c r="F36" s="6">
-        <v>5.009191513061523</v>
+        <v>5.0091915130615234</v>
       </c>
       <c r="G36" s="6">
-        <v>5.050712585449219</v>
+        <v>5.0507125854492188</v>
       </c>
       <c r="H36" s="6">
-        <v>5.127362251281738</v>
+        <v>5.1273622512817383</v>
       </c>
       <c r="I36" s="6">
-        <v>5.179727077484131</v>
+        <v>5.1797270774841309</v>
       </c>
       <c r="J36" s="6">
-        <v>5.232352733612061</v>
+        <v>5.2323527336120614</v>
       </c>
       <c r="K36" s="6">
-        <v>5.290907382965088</v>
+        <v>5.2909073829650879</v>
       </c>
       <c r="L36" s="6">
-        <v>5.34874963760376</v>
+        <v>5.3487496376037598</v>
       </c>
       <c r="M36" s="6">
-        <v>5.41348123550415</v>
+        <v>5.4134812355041504</v>
       </c>
       <c r="N36" s="6">
-        <v>5.487559795379639</v>
+        <v>5.4875597953796387</v>
       </c>
       <c r="O36" s="6">
-        <v>5.571776866912842</v>
+        <v>5.5717768669128418</v>
       </c>
       <c r="P36" s="6">
-        <v>5.660817623138428</v>
+        <v>5.6608176231384277</v>
       </c>
       <c r="Q36" s="6">
-        <v>5.751678943634033</v>
+        <v>5.7516789436340332</v>
       </c>
       <c r="R36" s="6">
-        <v>5.846420764923096</v>
+        <v>5.8464207649230957</v>
       </c>
       <c r="S36" s="6">
-        <v>5.940482139587402</v>
+        <v>5.9404821395874023</v>
       </c>
       <c r="T36" s="6">
-        <v>6.035927772521973</v>
+        <v>6.0359277725219727</v>
       </c>
       <c r="U36" s="6">
-        <v>6.129320621490479</v>
+        <v>6.1293206214904794</v>
       </c>
       <c r="V36" s="6">
-        <v>6.223669052124023</v>
+        <v>6.2236690521240234</v>
       </c>
       <c r="W36" s="6">
         <v>6.320319652557373</v>
@@ -2672,22 +3003,22 @@
         <v>6.520169734954834</v>
       </c>
       <c r="Z36" s="6">
-        <v>6.625844955444336</v>
+        <v>6.6258449554443359</v>
       </c>
       <c r="AA36" s="6">
-        <v>6.737439155578613</v>
+        <v>6.7374391555786133</v>
       </c>
       <c r="AB36" s="6">
-        <v>6.854903697967529</v>
+        <v>6.8549036979675293</v>
       </c>
       <c r="AC36" s="6">
-        <v>6.980434417724609</v>
+        <v>6.9804344177246094</v>
       </c>
       <c r="AD36" s="6">
-        <v>0.01377469112288709</v>
-      </c>
-    </row>
-    <row r="37" spans="1:30" s="4" customFormat="1">
+        <v>1.377469112288709E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>16</v>
       </c>
@@ -2695,19 +3026,19 @@
         <v>110</v>
       </c>
       <c r="C37" s="4">
-        <v>0.01876222528517246</v>
+        <v>1.8762225285172459E-2</v>
       </c>
       <c r="D37" s="4">
-        <v>0.02811118774116039</v>
+        <v>2.8111187741160389E-2</v>
       </c>
       <c r="E37" s="4">
-        <v>0.0422167144715786</v>
+        <v>4.2216714471578598E-2</v>
       </c>
       <c r="F37" s="4">
-        <v>0.06163442134857178</v>
+        <v>6.1634421348571777E-2</v>
       </c>
       <c r="G37" s="4">
-        <v>0.086184062063694</v>
+        <v>8.6184062063694E-2</v>
       </c>
       <c r="H37" s="4">
         <v>0.1169434636831284</v>
@@ -2716,16 +3047,16 @@
         <v>0.1592939347028732</v>
       </c>
       <c r="J37" s="4">
-        <v>0.2128296792507172</v>
+        <v>0.21282967925071719</v>
       </c>
       <c r="K37" s="4">
-        <v>0.2839672565460205</v>
+        <v>0.28396725654602051</v>
       </c>
       <c r="L37" s="4">
-        <v>0.3598229885101318</v>
+        <v>0.35982298851013178</v>
       </c>
       <c r="M37" s="4">
-        <v>0.4345318377017975</v>
+        <v>0.43453183770179749</v>
       </c>
       <c r="N37" s="4">
         <v>0.5064389705657959</v>
@@ -2734,34 +3065,34 @@
         <v>0.5746803879737854</v>
       </c>
       <c r="P37" s="4">
-        <v>0.6394470930099487</v>
+        <v>0.63944709300994873</v>
       </c>
       <c r="Q37" s="4">
-        <v>0.6999316215515137</v>
+        <v>0.69993162155151367</v>
       </c>
       <c r="R37" s="4">
-        <v>0.7563762068748474</v>
+        <v>0.75637620687484741</v>
       </c>
       <c r="S37" s="4">
-        <v>0.8084619641304016</v>
+        <v>0.80846196413040161</v>
       </c>
       <c r="T37" s="4">
-        <v>0.8559121489524841</v>
+        <v>0.85591214895248413</v>
       </c>
       <c r="U37" s="4">
         <v>0.8987807035446167</v>
       </c>
       <c r="V37" s="4">
-        <v>0.9363086819648743</v>
+        <v>0.93630868196487427</v>
       </c>
       <c r="W37" s="4">
-        <v>0.9690288901329041</v>
+        <v>0.96902889013290405</v>
       </c>
       <c r="X37" s="4">
-        <v>0.9983586072921753</v>
+        <v>0.99835860729217529</v>
       </c>
       <c r="Y37" s="4">
-        <v>1.023493051528931</v>
+        <v>1.0234930515289311</v>
       </c>
       <c r="Z37" s="4">
         <v>1.046672463417053</v>
@@ -2770,16 +3101,16 @@
         <v>1.067095875740051</v>
       </c>
       <c r="AB37" s="4">
-        <v>1.085416555404663</v>
+        <v>1.0854165554046631</v>
       </c>
       <c r="AC37" s="4">
-        <v>1.102266550064087</v>
+        <v>1.1022665500640869</v>
       </c>
       <c r="AD37" s="4">
-        <v>0.1696032039626418</v>
-      </c>
-    </row>
-    <row r="38" spans="1:30" s="4" customFormat="1">
+        <v>0.16960320396264181</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>17</v>
       </c>
@@ -2790,22 +3121,22 @@
         <v>0.1417428404092789</v>
       </c>
       <c r="D38" s="4">
-        <v>0.1586653888225555</v>
+        <v>0.15866538882255549</v>
       </c>
       <c r="E38" s="4">
-        <v>0.1751562505960464</v>
+        <v>0.17515625059604639</v>
       </c>
       <c r="F38" s="4">
-        <v>0.1821672022342682</v>
+        <v>0.18216720223426819</v>
       </c>
       <c r="G38" s="4">
-        <v>0.1895016580820084</v>
+        <v>0.18950165808200839</v>
       </c>
       <c r="H38" s="4">
-        <v>0.1993240267038345</v>
+        <v>0.19932402670383451</v>
       </c>
       <c r="I38" s="4">
-        <v>0.2111417055130005</v>
+        <v>0.21114170551300049</v>
       </c>
       <c r="J38" s="4">
         <v>0.2262821048498154</v>
@@ -2814,64 +3145,64 @@
         <v>0.2380215525627136</v>
       </c>
       <c r="L38" s="4">
-        <v>0.2538630664348602</v>
+        <v>0.25386306643486017</v>
       </c>
       <c r="M38" s="4">
-        <v>0.2636756598949432</v>
+        <v>0.26367565989494318</v>
       </c>
       <c r="N38" s="4">
-        <v>0.2719502449035645</v>
+        <v>0.27195024490356451</v>
       </c>
       <c r="O38" s="4">
-        <v>0.2785964906215668</v>
+        <v>0.27859649062156677</v>
       </c>
       <c r="P38" s="4">
         <v>0.2867908775806427</v>
       </c>
       <c r="Q38" s="4">
-        <v>0.2923144996166229</v>
+        <v>0.29231449961662292</v>
       </c>
       <c r="R38" s="4">
-        <v>0.2951976954936981</v>
+        <v>0.29519769549369812</v>
       </c>
       <c r="S38" s="4">
-        <v>0.3008307218551636</v>
+        <v>0.30083072185516357</v>
       </c>
       <c r="T38" s="4">
-        <v>0.3085992038249969</v>
+        <v>0.30859920382499689</v>
       </c>
       <c r="U38" s="4">
-        <v>0.317820280790329</v>
+        <v>0.31782028079032898</v>
       </c>
       <c r="V38" s="4">
-        <v>0.3278141021728516</v>
+        <v>0.32781410217285162</v>
       </c>
       <c r="W38" s="4">
-        <v>0.3383373320102692</v>
+        <v>0.33833733201026922</v>
       </c>
       <c r="X38" s="4">
-        <v>0.3482779562473297</v>
+        <v>0.34827795624732971</v>
       </c>
       <c r="Y38" s="4">
         <v>0.35950967669487</v>
       </c>
       <c r="Z38" s="4">
-        <v>0.3691576421260834</v>
+        <v>0.36915764212608337</v>
       </c>
       <c r="AA38" s="4">
-        <v>0.3785410821437836</v>
+        <v>0.37854108214378362</v>
       </c>
       <c r="AB38" s="4">
-        <v>0.3858913481235504</v>
+        <v>0.38589134812355042</v>
       </c>
       <c r="AC38" s="4">
-        <v>0.392189234495163</v>
+        <v>0.39218923449516302</v>
       </c>
       <c r="AD38" s="4">
-        <v>0.03991966268814529</v>
-      </c>
-    </row>
-    <row r="39" spans="1:30" s="6" customFormat="1">
+        <v>3.9919662688145292E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:30" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
         <v>18</v>
       </c>
@@ -2879,25 +3210,25 @@
         <v>112</v>
       </c>
       <c r="C39" s="6">
-        <v>4.768100261688232</v>
+        <v>4.7681002616882324</v>
       </c>
       <c r="D39" s="6">
-        <v>4.849862098693848</v>
+        <v>4.8498620986938477</v>
       </c>
       <c r="E39" s="6">
-        <v>4.823996543884277</v>
+        <v>4.8239965438842773</v>
       </c>
       <c r="F39" s="6">
-        <v>4.888659477233887</v>
+        <v>4.8886594772338867</v>
       </c>
       <c r="G39" s="6">
         <v>4.947394847869873</v>
       </c>
       <c r="H39" s="6">
-        <v>5.044981479644775</v>
+        <v>5.0449814796447754</v>
       </c>
       <c r="I39" s="6">
-        <v>5.127879619598389</v>
+        <v>5.1278796195983887</v>
       </c>
       <c r="J39" s="6">
         <v>5.218900203704834</v>
@@ -2909,67 +3240,67 @@
         <v>5.454709529876709</v>
       </c>
       <c r="M39" s="6">
-        <v>5.584336757659912</v>
+        <v>5.5843367576599121</v>
       </c>
       <c r="N39" s="6">
-        <v>5.722048759460449</v>
+        <v>5.7220487594604492</v>
       </c>
       <c r="O39" s="6">
-        <v>5.867860794067383</v>
+        <v>5.8678607940673828</v>
       </c>
       <c r="P39" s="6">
-        <v>6.013473987579346</v>
+        <v>6.0134739875793457</v>
       </c>
       <c r="Q39" s="6">
-        <v>6.159296035766602</v>
+        <v>6.1592960357666016</v>
       </c>
       <c r="R39" s="6">
-        <v>6.307599544525146</v>
+        <v>6.3075995445251456</v>
       </c>
       <c r="S39" s="6">
-        <v>6.448112487792969</v>
+        <v>6.4481124877929688</v>
       </c>
       <c r="T39" s="6">
-        <v>6.583240509033203</v>
+        <v>6.5832405090332031</v>
       </c>
       <c r="U39" s="6">
-        <v>6.710281372070312</v>
+        <v>6.7102813720703116</v>
       </c>
       <c r="V39" s="6">
-        <v>6.832162857055664</v>
+        <v>6.8321628570556641</v>
       </c>
       <c r="W39" s="6">
-        <v>6.951010704040527</v>
+        <v>6.9510107040405273</v>
       </c>
       <c r="X39" s="6">
         <v>7.069582462310791</v>
       </c>
       <c r="Y39" s="6">
-        <v>7.18415355682373</v>
+        <v>7.1841535568237296</v>
       </c>
       <c r="Z39" s="6">
-        <v>7.303359508514404</v>
+        <v>7.3033595085144043</v>
       </c>
       <c r="AA39" s="6">
-        <v>7.425993919372559</v>
+        <v>7.4259939193725586</v>
       </c>
       <c r="AB39" s="6">
-        <v>7.554428577423096</v>
+        <v>7.5544285774230957</v>
       </c>
       <c r="AC39" s="6">
-        <v>7.690512180328369</v>
+        <v>7.6905121803283691</v>
       </c>
       <c r="AD39" s="6">
-        <v>0.01855619741867165</v>
-      </c>
-    </row>
-    <row r="40" spans="1:30" s="4" customFormat="1"/>
-    <row r="41" spans="1:30" s="6" customFormat="1">
+        <v>1.8556197418671649E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="1:30" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B41" s="6" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="42" spans="1:30" s="4" customFormat="1">
+    <row r="42" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>19</v>
       </c>
@@ -2977,25 +3308,25 @@
         <v>99</v>
       </c>
       <c r="C42" s="4">
-        <v>1.537412405014038</v>
+        <v>1.5374124050140381</v>
       </c>
       <c r="D42" s="4">
         <v>1.696070194244385</v>
       </c>
       <c r="E42" s="4">
-        <v>1.715485453605652</v>
+        <v>1.7154854536056521</v>
       </c>
       <c r="F42" s="4">
         <v>1.720562815666199</v>
       </c>
       <c r="G42" s="4">
-        <v>1.717478513717651</v>
+        <v>1.7174785137176509</v>
       </c>
       <c r="H42" s="4">
-        <v>1.709206461906433</v>
+        <v>1.7092064619064331</v>
       </c>
       <c r="I42" s="4">
-        <v>1.697413086891174</v>
+        <v>1.6974130868911741</v>
       </c>
       <c r="J42" s="4">
         <v>1.688198447227478</v>
@@ -3025,13 +3356,13 @@
         <v>1.632508397102356</v>
       </c>
       <c r="S42" s="4">
-        <v>1.631180167198181</v>
+        <v>1.6311801671981809</v>
       </c>
       <c r="T42" s="4">
-        <v>1.627330303192139</v>
+        <v>1.6273303031921389</v>
       </c>
       <c r="U42" s="4">
-        <v>1.621919870376587</v>
+        <v>1.6219198703765869</v>
       </c>
       <c r="V42" s="4">
         <v>1.615662574768066</v>
@@ -3040,7 +3371,7 @@
         <v>1.610578656196594</v>
       </c>
       <c r="X42" s="4">
-        <v>1.605665564537048</v>
+        <v>1.6056655645370479</v>
       </c>
       <c r="Y42" s="4">
         <v>1.600350975990295</v>
@@ -3055,13 +3386,13 @@
         <v>1.592765331268311</v>
       </c>
       <c r="AC42" s="4">
-        <v>1.592218995094299</v>
+        <v>1.5922189950942991</v>
       </c>
       <c r="AD42" s="4">
-        <v>0.001348134493068587</v>
-      </c>
-    </row>
-    <row r="43" spans="1:30" s="4" customFormat="1">
+        <v>1.348134493068587E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>20</v>
       </c>
@@ -3069,91 +3400,91 @@
         <v>114</v>
       </c>
       <c r="C43" s="4">
-        <v>0.01832026243209839</v>
+        <v>1.8320262432098389E-2</v>
       </c>
       <c r="D43" s="4">
-        <v>0.01757954061031342</v>
+        <v>1.7579540610313419E-2</v>
       </c>
       <c r="E43" s="4">
-        <v>0.01781555823981762</v>
+        <v>1.7815558239817619E-2</v>
       </c>
       <c r="F43" s="4">
-        <v>0.01795352436602116</v>
+        <v>1.795352436602116E-2</v>
       </c>
       <c r="G43" s="4">
-        <v>0.01800577342510223</v>
+        <v>1.800577342510223E-2</v>
       </c>
       <c r="H43" s="4">
-        <v>0.01802670583128929</v>
+        <v>1.8026705831289291E-2</v>
       </c>
       <c r="I43" s="4">
-        <v>0.01802902296185493</v>
+        <v>1.8029022961854931E-2</v>
       </c>
       <c r="J43" s="4">
-        <v>0.01804065890610218</v>
+        <v>1.804065890610218E-2</v>
       </c>
       <c r="K43" s="4">
-        <v>0.01800160855054855</v>
+        <v>1.800160855054855E-2</v>
       </c>
       <c r="L43" s="4">
-        <v>0.01794629171490669</v>
+        <v>1.7946291714906689E-2</v>
       </c>
       <c r="M43" s="4">
-        <v>0.01791862398386002</v>
+        <v>1.7918623983860019E-2</v>
       </c>
       <c r="N43" s="4">
-        <v>0.01796292886137962</v>
+        <v>1.796292886137962E-2</v>
       </c>
       <c r="O43" s="4">
-        <v>0.01805680245161057</v>
+        <v>1.8056802451610569E-2</v>
       </c>
       <c r="P43" s="4">
-        <v>0.01819243654608727</v>
+        <v>1.8192436546087268E-2</v>
       </c>
       <c r="Q43" s="4">
-        <v>0.01835783012211323</v>
+        <v>1.8357830122113231E-2</v>
       </c>
       <c r="R43" s="4">
-        <v>0.01854315213859081</v>
+        <v>1.8543152138590809E-2</v>
       </c>
       <c r="S43" s="4">
-        <v>0.01872028037905693</v>
+        <v>1.8720280379056931E-2</v>
       </c>
       <c r="T43" s="4">
-        <v>0.01887697167694569</v>
+        <v>1.887697167694569E-2</v>
       </c>
       <c r="U43" s="4">
-        <v>0.01900096610188484</v>
+        <v>1.9000966101884838E-2</v>
       </c>
       <c r="V43" s="4">
-        <v>0.01913193427026272</v>
+        <v>1.9131934270262722E-2</v>
       </c>
       <c r="W43" s="4">
-        <v>0.01928924024105072</v>
+        <v>1.928924024105072E-2</v>
       </c>
       <c r="X43" s="4">
-        <v>0.01945429854094982</v>
+        <v>1.9454298540949821E-2</v>
       </c>
       <c r="Y43" s="4">
-        <v>0.01962479390203953</v>
+        <v>1.9624793902039531E-2</v>
       </c>
       <c r="Z43" s="4">
-        <v>0.01982053928077221</v>
+        <v>1.9820539280772209E-2</v>
       </c>
       <c r="AA43" s="4">
-        <v>0.02004244178533554</v>
+        <v>2.0042441785335541E-2</v>
       </c>
       <c r="AB43" s="4">
-        <v>0.0202792901545763</v>
+        <v>2.0279290154576302E-2</v>
       </c>
       <c r="AC43" s="4">
-        <v>0.0205532182008028</v>
+        <v>2.05532182008028E-2</v>
       </c>
       <c r="AD43" s="4">
-        <v>0.004433253617363908</v>
-      </c>
-    </row>
-    <row r="44" spans="1:30" s="4" customFormat="1">
+        <v>4.4332536173639081E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>21</v>
       </c>
@@ -3161,91 +3492,91 @@
         <v>101</v>
       </c>
       <c r="C44" s="4">
-        <v>0.2699450552463531</v>
+        <v>0.26994505524635309</v>
       </c>
       <c r="D44" s="4">
-        <v>0.2823971509933472</v>
+        <v>0.28239715099334722</v>
       </c>
       <c r="E44" s="4">
-        <v>0.2901692390441895</v>
+        <v>0.29016923904418951</v>
       </c>
       <c r="F44" s="4">
         <v>0.2947026789188385</v>
       </c>
       <c r="G44" s="4">
-        <v>0.2981769442558289</v>
+        <v>0.29817694425582891</v>
       </c>
       <c r="H44" s="4">
-        <v>0.3011065423488617</v>
+        <v>0.30110654234886169</v>
       </c>
       <c r="I44" s="4">
-        <v>0.3036274909973145</v>
+        <v>0.30362749099731451</v>
       </c>
       <c r="J44" s="4">
-        <v>0.3063525855541229</v>
+        <v>0.30635258555412292</v>
       </c>
       <c r="K44" s="4">
-        <v>0.3082503974437714</v>
+        <v>0.30825039744377142</v>
       </c>
       <c r="L44" s="4">
-        <v>0.3099270164966583</v>
+        <v>0.30992701649665833</v>
       </c>
       <c r="M44" s="4">
-        <v>0.3120135068893433</v>
+        <v>0.31201350688934332</v>
       </c>
       <c r="N44" s="4">
-        <v>0.3149681687355042</v>
+        <v>0.31496816873550421</v>
       </c>
       <c r="O44" s="4">
-        <v>0.3187451064586639</v>
+        <v>0.31874510645866388</v>
       </c>
       <c r="P44" s="4">
-        <v>0.3230606317520142</v>
+        <v>0.32306063175201422</v>
       </c>
       <c r="Q44" s="4">
-        <v>0.3276787996292114</v>
+        <v>0.32767879962921143</v>
       </c>
       <c r="R44" s="4">
-        <v>0.3322950303554535</v>
+        <v>0.33229503035545349</v>
       </c>
       <c r="S44" s="4">
-        <v>0.3366337716579437</v>
+        <v>0.33663377165794373</v>
       </c>
       <c r="T44" s="4">
-        <v>0.3405329883098602</v>
+        <v>0.34053298830986017</v>
       </c>
       <c r="U44" s="4">
-        <v>0.3441019952297211</v>
+        <v>0.34410199522972112</v>
       </c>
       <c r="V44" s="4">
-        <v>0.3474909663200378</v>
+        <v>0.34749096632003779</v>
       </c>
       <c r="W44" s="4">
-        <v>0.3511286675930023</v>
+        <v>0.35112866759300232</v>
       </c>
       <c r="X44" s="4">
-        <v>0.3547749817371368</v>
+        <v>0.35477498173713679</v>
       </c>
       <c r="Y44" s="4">
-        <v>0.3583259582519531</v>
+        <v>0.35832595825195313</v>
       </c>
       <c r="Z44" s="4">
-        <v>0.3621355593204498</v>
+        <v>0.36213555932044977</v>
       </c>
       <c r="AA44" s="4">
-        <v>0.3663064539432526</v>
+        <v>0.36630645394325262</v>
       </c>
       <c r="AB44" s="4">
         <v>0.3706614077091217</v>
       </c>
       <c r="AC44" s="4">
-        <v>0.3751522302627563</v>
+        <v>0.37515223026275629</v>
       </c>
       <c r="AD44" s="4">
-        <v>0.01273866392983813</v>
-      </c>
-    </row>
-    <row r="45" spans="1:30" s="4" customFormat="1">
+        <v>1.2738663929838131E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>22</v>
       </c>
@@ -3253,37 +3584,37 @@
         <v>103</v>
       </c>
       <c r="C45" s="4">
-        <v>0.4008831977844238</v>
+        <v>0.40088319778442377</v>
       </c>
       <c r="D45" s="4">
-        <v>0.4179143607616425</v>
+        <v>0.41791436076164251</v>
       </c>
       <c r="E45" s="4">
-        <v>0.4274516403675079</v>
+        <v>0.42745164036750788</v>
       </c>
       <c r="F45" s="4">
-        <v>0.4339378774166107</v>
+        <v>0.43393787741661072</v>
       </c>
       <c r="G45" s="4">
-        <v>0.438655823469162</v>
+        <v>0.43865582346916199</v>
       </c>
       <c r="H45" s="4">
-        <v>0.4424798786640167</v>
+        <v>0.44247987866401672</v>
       </c>
       <c r="I45" s="4">
-        <v>0.4456451535224915</v>
+        <v>0.44564515352249151</v>
       </c>
       <c r="J45" s="4">
         <v>0.4493083655834198</v>
       </c>
       <c r="K45" s="4">
-        <v>0.4518794119358063</v>
+        <v>0.45187941193580627</v>
       </c>
       <c r="L45" s="4">
-        <v>0.4541521668434143</v>
+        <v>0.45415216684341431</v>
       </c>
       <c r="M45" s="4">
-        <v>0.4569697082042694</v>
+        <v>0.45696970820426941</v>
       </c>
       <c r="N45" s="4">
         <v>0.4609740674495697</v>
@@ -3298,46 +3629,46 @@
         <v>0.4781709611415863</v>
       </c>
       <c r="R45" s="4">
-        <v>0.4843262135982513</v>
+        <v>0.48432621359825129</v>
       </c>
       <c r="S45" s="4">
         <v>0.4900367259979248</v>
       </c>
       <c r="T45" s="4">
-        <v>0.4952158331871033</v>
+        <v>0.49521583318710333</v>
       </c>
       <c r="U45" s="4">
-        <v>0.499917060136795</v>
+        <v>0.49991706013679499</v>
       </c>
       <c r="V45" s="4">
-        <v>0.5043496489524841</v>
+        <v>0.50434964895248413</v>
       </c>
       <c r="W45" s="4">
-        <v>0.5091049671173096</v>
+        <v>0.50910496711730957</v>
       </c>
       <c r="X45" s="4">
-        <v>0.513834536075592</v>
+        <v>0.51383453607559204</v>
       </c>
       <c r="Y45" s="4">
         <v>0.5183982253074646</v>
       </c>
       <c r="Z45" s="4">
-        <v>0.5233038663864136</v>
+        <v>0.52330386638641357</v>
       </c>
       <c r="AA45" s="4">
-        <v>0.5287091135978699</v>
+        <v>0.52870911359786987</v>
       </c>
       <c r="AB45" s="4">
-        <v>0.5343351364135742</v>
+        <v>0.53433513641357422</v>
       </c>
       <c r="AC45" s="4">
         <v>0.5400998592376709</v>
       </c>
       <c r="AD45" s="4">
-        <v>0.01153073921979542</v>
-      </c>
-    </row>
-    <row r="46" spans="1:30" s="4" customFormat="1">
+        <v>1.153073921979542E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>23</v>
       </c>
@@ -3348,22 +3679,22 @@
         <v>1.200143098831177</v>
       </c>
       <c r="D46" s="4">
-        <v>1.196090221405029</v>
+        <v>1.1960902214050291</v>
       </c>
       <c r="E46" s="4">
-        <v>1.192237138748169</v>
+        <v>1.1922371387481689</v>
       </c>
       <c r="F46" s="4">
         <v>1.184520959854126</v>
       </c>
       <c r="G46" s="4">
-        <v>1.172419786453247</v>
+        <v>1.1724197864532471</v>
       </c>
       <c r="H46" s="4">
-        <v>1.174673080444336</v>
+        <v>1.1746730804443359</v>
       </c>
       <c r="I46" s="4">
-        <v>1.175276756286621</v>
+        <v>1.1752767562866211</v>
       </c>
       <c r="J46" s="4">
         <v>1.175642728805542</v>
@@ -3375,19 +3706,19 @@
         <v>1.168512344360352</v>
       </c>
       <c r="M46" s="4">
-        <v>1.16554594039917</v>
+        <v>1.1655459403991699</v>
       </c>
       <c r="N46" s="4">
-        <v>1.165394306182861</v>
+        <v>1.1653943061828611</v>
       </c>
       <c r="O46" s="4">
-        <v>1.167917251586914</v>
+        <v>1.1679172515869141</v>
       </c>
       <c r="P46" s="4">
-        <v>1.172311782836914</v>
+        <v>1.1723117828369141</v>
       </c>
       <c r="Q46" s="4">
-        <v>1.177850246429443</v>
+        <v>1.1778502464294429</v>
       </c>
       <c r="R46" s="4">
         <v>1.183558464050293</v>
@@ -3402,16 +3733,16 @@
         <v>1.19348669052124</v>
       </c>
       <c r="V46" s="4">
-        <v>1.194862127304077</v>
+        <v>1.1948621273040769</v>
       </c>
       <c r="W46" s="4">
-        <v>1.197102069854736</v>
+        <v>1.1971020698547361</v>
       </c>
       <c r="X46" s="4">
-        <v>1.199375629425049</v>
+        <v>1.1993756294250491</v>
       </c>
       <c r="Y46" s="4">
-        <v>1.201416254043579</v>
+        <v>1.2014162540435791</v>
       </c>
       <c r="Z46" s="4">
         <v>1.204267024993896</v>
@@ -3426,10 +3757,10 @@
         <v>1.217421770095825</v>
       </c>
       <c r="AD46" s="4">
-        <v>0.0005499404179081235</v>
-      </c>
-    </row>
-    <row r="47" spans="1:30" s="6" customFormat="1">
+        <v>5.4994041790812354E-4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:30" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>24</v>
       </c>
@@ -3437,25 +3768,25 @@
         <v>116</v>
       </c>
       <c r="C47" s="6">
-        <v>3.426704168319702</v>
+        <v>3.4267041683197021</v>
       </c>
       <c r="D47" s="6">
-        <v>3.610051393508911</v>
+        <v>3.6100513935089111</v>
       </c>
       <c r="E47" s="6">
         <v>3.643159151077271</v>
       </c>
       <c r="F47" s="6">
-        <v>3.651677846908569</v>
+        <v>3.6516778469085689</v>
       </c>
       <c r="G47" s="6">
         <v>3.644736766815186</v>
       </c>
       <c r="H47" s="6">
-        <v>3.645492553710938</v>
+        <v>3.6454925537109379</v>
       </c>
       <c r="I47" s="6">
-        <v>3.639991521835327</v>
+        <v>3.6399915218353271</v>
       </c>
       <c r="J47" s="6">
         <v>3.637542724609375</v>
@@ -3464,10 +3795,10 @@
         <v>3.625333309173584</v>
       </c>
       <c r="L47" s="6">
-        <v>3.609777927398682</v>
+        <v>3.6097779273986821</v>
       </c>
       <c r="M47" s="6">
-        <v>3.598366975784302</v>
+        <v>3.5983669757843022</v>
       </c>
       <c r="N47" s="6">
         <v>3.596980094909668</v>
@@ -3476,58 +3807,58 @@
         <v>3.60443115234375</v>
       </c>
       <c r="P47" s="6">
-        <v>3.617715358734131</v>
+        <v>3.6177153587341309</v>
       </c>
       <c r="Q47" s="6">
         <v>3.634445428848267</v>
       </c>
       <c r="R47" s="6">
-        <v>3.651231288909912</v>
+        <v>3.6512312889099121</v>
       </c>
       <c r="S47" s="6">
-        <v>3.665134429931641</v>
+        <v>3.6651344299316411</v>
       </c>
       <c r="T47" s="6">
         <v>3.673481702804565</v>
       </c>
       <c r="U47" s="6">
-        <v>3.678426742553711</v>
+        <v>3.6784267425537109</v>
       </c>
       <c r="V47" s="6">
         <v>3.68149733543396</v>
       </c>
       <c r="W47" s="6">
-        <v>3.687203645706177</v>
+        <v>3.6872036457061772</v>
       </c>
       <c r="X47" s="6">
-        <v>3.693104982376099</v>
+        <v>3.6931049823760991</v>
       </c>
       <c r="Y47" s="6">
-        <v>3.698116302490234</v>
+        <v>3.6981163024902339</v>
       </c>
       <c r="Z47" s="6">
         <v>3.705870389938354</v>
       </c>
       <c r="AA47" s="6">
-        <v>3.717107534408569</v>
+        <v>3.7171075344085689</v>
       </c>
       <c r="AB47" s="6">
-        <v>3.730535984039307</v>
+        <v>3.7305359840393071</v>
       </c>
       <c r="AC47" s="6">
-        <v>3.745445966720581</v>
+        <v>3.7454459667205811</v>
       </c>
       <c r="AD47" s="6">
-        <v>0.003426695348467179</v>
-      </c>
-    </row>
-    <row r="48" spans="1:30" s="4" customFormat="1"/>
-    <row r="49" spans="1:30" s="6" customFormat="1">
+        <v>3.4266953484671792E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="49" spans="1:30" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B49" s="6" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="50" spans="1:30" s="4" customFormat="1">
+    <row r="50" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>25</v>
       </c>
@@ -3535,91 +3866,91 @@
         <v>99</v>
       </c>
       <c r="C50" s="4">
-        <v>0.06926900893449783</v>
+        <v>6.9269008934497833E-2</v>
       </c>
       <c r="D50" s="4">
-        <v>0.07407147437334061</v>
+        <v>7.4071474373340607E-2</v>
       </c>
       <c r="E50" s="4">
-        <v>0.0740261897444725</v>
+        <v>7.4026189744472504E-2</v>
       </c>
       <c r="F50" s="4">
-        <v>0.07362744957208633</v>
+        <v>7.3627449572086334E-2</v>
       </c>
       <c r="G50" s="4">
-        <v>0.07298292219638824</v>
+        <v>7.2982922196388245E-2</v>
       </c>
       <c r="H50" s="4">
-        <v>0.07203175872564316</v>
+        <v>7.2031758725643158E-2</v>
       </c>
       <c r="I50" s="4">
-        <v>0.07102862000465393</v>
+        <v>7.1028620004653931E-2</v>
       </c>
       <c r="J50" s="4">
-        <v>0.06999889016151428</v>
+        <v>6.9998890161514282E-2</v>
       </c>
       <c r="K50" s="4">
-        <v>0.06894790381193161</v>
+        <v>6.894790381193161E-2</v>
       </c>
       <c r="L50" s="4">
-        <v>0.06781431287527084</v>
+        <v>6.7814312875270844E-2</v>
       </c>
       <c r="M50" s="4">
-        <v>0.06667188555002213</v>
+        <v>6.6671885550022125E-2</v>
       </c>
       <c r="N50" s="4">
-        <v>0.06552590429782867</v>
+        <v>6.5525904297828674E-2</v>
       </c>
       <c r="O50" s="4">
-        <v>0.06442824006080627</v>
+        <v>6.4428240060806274E-2</v>
       </c>
       <c r="P50" s="4">
-        <v>0.0633414089679718</v>
+        <v>6.3341408967971802E-2</v>
       </c>
       <c r="Q50" s="4">
-        <v>0.06227519363164902</v>
+        <v>6.2275193631649017E-2</v>
       </c>
       <c r="R50" s="4">
-        <v>0.06122281774878502</v>
+        <v>6.1222817748785019E-2</v>
       </c>
       <c r="S50" s="4">
-        <v>0.06014952063560486</v>
+        <v>6.0149520635604858E-2</v>
       </c>
       <c r="T50" s="4">
-        <v>0.05910560488700867</v>
+        <v>5.9105604887008667E-2</v>
       </c>
       <c r="U50" s="4">
-        <v>0.05811000987887383</v>
+        <v>5.8110009878873832E-2</v>
       </c>
       <c r="V50" s="4">
-        <v>0.05711971595883369</v>
+        <v>5.7119715958833688E-2</v>
       </c>
       <c r="W50" s="4">
-        <v>0.056142657995224</v>
+        <v>5.6142657995223999E-2</v>
       </c>
       <c r="X50" s="4">
-        <v>0.05523353442549706</v>
+        <v>5.5233534425497062E-2</v>
       </c>
       <c r="Y50" s="4">
-        <v>0.05431413650512695</v>
+        <v>5.4314136505126953E-2</v>
       </c>
       <c r="Z50" s="4">
-        <v>0.05335766449570656</v>
+        <v>5.3357664495706558E-2</v>
       </c>
       <c r="AA50" s="4">
-        <v>0.05247814580798149</v>
+        <v>5.2478145807981491E-2</v>
       </c>
       <c r="AB50" s="4">
-        <v>0.05168719962239265</v>
+        <v>5.1687199622392647E-2</v>
       </c>
       <c r="AC50" s="4">
-        <v>0.05090616643428802</v>
+        <v>5.0906166434288018E-2</v>
       </c>
       <c r="AD50" s="4">
-        <v>-0.01177677906349206</v>
-      </c>
-    </row>
-    <row r="51" spans="1:30" s="4" customFormat="1">
+        <v>-1.177677906349206E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>26</v>
       </c>
@@ -3627,91 +3958,91 @@
         <v>101</v>
       </c>
       <c r="C51" s="4">
-        <v>0.003746373578906059</v>
+        <v>3.7463735789060588E-3</v>
       </c>
       <c r="D51" s="4">
-        <v>0.003810880240052938</v>
+        <v>3.810880240052938E-3</v>
       </c>
       <c r="E51" s="4">
-        <v>0.003830209607258439</v>
+        <v>3.8302096072584391E-3</v>
       </c>
       <c r="F51" s="4">
-        <v>0.003835398238152266</v>
+        <v>3.835398238152266E-3</v>
       </c>
       <c r="G51" s="4">
-        <v>0.003831216366961598</v>
+        <v>3.831216366961598E-3</v>
       </c>
       <c r="H51" s="4">
-        <v>0.0038222367875278</v>
+        <v>3.8222367875278E-3</v>
       </c>
       <c r="I51" s="4">
-        <v>0.003812081646174192</v>
+        <v>3.812081646174192E-3</v>
       </c>
       <c r="J51" s="4">
-        <v>0.003798464545980096</v>
+        <v>3.7984645459800959E-3</v>
       </c>
       <c r="K51" s="4">
-        <v>0.00378446327522397</v>
+        <v>3.78446327522397E-3</v>
       </c>
       <c r="L51" s="4">
-        <v>0.00376658421009779</v>
+        <v>3.7665842100977902E-3</v>
       </c>
       <c r="M51" s="4">
-        <v>0.003748617600649595</v>
+        <v>3.7486176006495948E-3</v>
       </c>
       <c r="N51" s="4">
-        <v>0.003730543190613389</v>
+        <v>3.730543190613389E-3</v>
       </c>
       <c r="O51" s="4">
-        <v>0.003714844351634383</v>
+        <v>3.7148443516343832E-3</v>
       </c>
       <c r="P51" s="4">
-        <v>0.00369906984269619</v>
+        <v>3.6990698426961899E-3</v>
       </c>
       <c r="Q51" s="4">
-        <v>0.003684292314574122</v>
+        <v>3.684292314574122E-3</v>
       </c>
       <c r="R51" s="4">
-        <v>0.003669783240184188</v>
+        <v>3.6697832401841879E-3</v>
       </c>
       <c r="S51" s="4">
-        <v>0.003653629682958126</v>
+        <v>3.6536296829581261E-3</v>
       </c>
       <c r="T51" s="4">
-        <v>0.003637934103608131</v>
+        <v>3.637934103608131E-3</v>
       </c>
       <c r="U51" s="4">
-        <v>0.003624342381954193</v>
+        <v>3.6243423819541931E-3</v>
       </c>
       <c r="V51" s="4">
-        <v>0.003610231215134263</v>
+        <v>3.610231215134263E-3</v>
       </c>
       <c r="W51" s="4">
-        <v>0.003596448106691241</v>
+        <v>3.5964481066912408E-3</v>
       </c>
       <c r="X51" s="4">
-        <v>0.003585981437936425</v>
+        <v>3.5859814379364252E-3</v>
       </c>
       <c r="Y51" s="4">
-        <v>0.003574461676180363</v>
+        <v>3.5744616761803631E-3</v>
       </c>
       <c r="Z51" s="4">
-        <v>0.003559408476576209</v>
+        <v>3.5594084765762091E-3</v>
       </c>
       <c r="AA51" s="4">
-        <v>0.003548542037606239</v>
+        <v>3.5485420376062389E-3</v>
       </c>
       <c r="AB51" s="4">
-        <v>0.003542301710695028</v>
+        <v>3.5423017106950279E-3</v>
       </c>
       <c r="AC51" s="4">
-        <v>0.003536348231136799</v>
+        <v>3.5363482311367989E-3</v>
       </c>
       <c r="AD51" s="4">
-        <v>-0.002216528514088156</v>
-      </c>
-    </row>
-    <row r="52" spans="1:30" s="4" customFormat="1">
+        <v>-2.2165285140881559E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>27</v>
       </c>
@@ -3719,16 +4050,16 @@
         <v>118</v>
       </c>
       <c r="C52" s="4">
-        <v>0.2352688759565353</v>
+        <v>0.23526887595653531</v>
       </c>
       <c r="D52" s="4">
-        <v>0.238648384809494</v>
+        <v>0.23864838480949399</v>
       </c>
       <c r="E52" s="4">
-        <v>0.242406353354454</v>
+        <v>0.24240635335445401</v>
       </c>
       <c r="F52" s="4">
-        <v>0.2447528690099716</v>
+        <v>0.24475286900997159</v>
       </c>
       <c r="G52" s="4">
         <v>0.2462078183889389</v>
@@ -3737,73 +4068,73 @@
         <v>0.2472800016403198</v>
       </c>
       <c r="I52" s="4">
-        <v>0.2482092380523682</v>
+        <v>0.24820923805236819</v>
       </c>
       <c r="J52" s="4">
-        <v>0.2487268894910812</v>
+        <v>0.24872688949108121</v>
       </c>
       <c r="K52" s="4">
-        <v>0.2491224855184555</v>
+        <v>0.24912248551845551</v>
       </c>
       <c r="L52" s="4">
         <v>0.2490738183259964</v>
       </c>
       <c r="M52" s="4">
-        <v>0.2488996237516403</v>
+        <v>0.24889962375164029</v>
       </c>
       <c r="N52" s="4">
-        <v>0.2486098855733871</v>
+        <v>0.24860988557338709</v>
       </c>
       <c r="O52" s="4">
-        <v>0.2484423071146011</v>
+        <v>0.24844230711460111</v>
       </c>
       <c r="P52" s="4">
-        <v>0.2482651472091675</v>
+        <v>0.24826514720916751</v>
       </c>
       <c r="Q52" s="4">
-        <v>0.2481396049261093</v>
+        <v>0.24813960492610929</v>
       </c>
       <c r="R52" s="4">
-        <v>0.2480211108922958</v>
+        <v>0.24802111089229581</v>
       </c>
       <c r="S52" s="4">
-        <v>0.2477563768625259</v>
+        <v>0.24775637686252591</v>
       </c>
       <c r="T52" s="4">
-        <v>0.2473904192447662</v>
+        <v>0.24739041924476621</v>
       </c>
       <c r="U52" s="4">
-        <v>0.2471460700035095</v>
+        <v>0.24714607000350949</v>
       </c>
       <c r="V52" s="4">
         <v>0.2468131631612778</v>
       </c>
       <c r="W52" s="4">
-        <v>0.2464736104011536</v>
+        <v>0.24647361040115359</v>
       </c>
       <c r="X52" s="4">
-        <v>0.246346578001976</v>
+        <v>0.24634657800197601</v>
       </c>
       <c r="Y52" s="4">
-        <v>0.2461045682430267</v>
+        <v>0.24610456824302671</v>
       </c>
       <c r="Z52" s="4">
-        <v>0.245555967092514</v>
+        <v>0.24555596709251401</v>
       </c>
       <c r="AA52" s="4">
-        <v>0.2452813684940338</v>
+        <v>0.24528136849403381</v>
       </c>
       <c r="AB52" s="4">
-        <v>0.2453174442052841</v>
+        <v>0.24531744420528409</v>
       </c>
       <c r="AC52" s="4">
-        <v>0.2453433126211166</v>
+        <v>0.24534331262111661</v>
       </c>
       <c r="AD52" s="4">
-        <v>0.00161397384728712</v>
-      </c>
-    </row>
-    <row r="53" spans="1:30" s="6" customFormat="1">
+        <v>1.6139738472871199E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:30" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
         <v>28</v>
       </c>
@@ -3811,92 +4142,92 @@
         <v>116</v>
       </c>
       <c r="C53" s="6">
-        <v>0.3082842528820038</v>
+        <v>0.30828425288200378</v>
       </c>
       <c r="D53" s="6">
         <v>0.3165307343006134</v>
       </c>
       <c r="E53" s="6">
-        <v>0.3202627599239349</v>
+        <v>0.32026275992393488</v>
       </c>
       <c r="F53" s="6">
-        <v>0.3222157061100006</v>
+        <v>0.32221570611000061</v>
       </c>
       <c r="G53" s="6">
-        <v>0.3230219781398773</v>
+        <v>0.32302197813987732</v>
       </c>
       <c r="H53" s="6">
-        <v>0.3231340050697327</v>
+        <v>0.32313400506973272</v>
       </c>
       <c r="I53" s="6">
-        <v>0.323049932718277</v>
+        <v>0.32304993271827698</v>
       </c>
       <c r="J53" s="6">
-        <v>0.3225242495536804</v>
+        <v>0.32252424955368042</v>
       </c>
       <c r="K53" s="6">
         <v>0.3218548595905304</v>
       </c>
       <c r="L53" s="6">
-        <v>0.3206547200679779</v>
+        <v>0.32065472006797791</v>
       </c>
       <c r="M53" s="6">
-        <v>0.3193201124668121</v>
+        <v>0.31932011246681208</v>
       </c>
       <c r="N53" s="6">
-        <v>0.3178663551807404</v>
+        <v>0.31786635518074041</v>
       </c>
       <c r="O53" s="6">
-        <v>0.3165853917598724</v>
+        <v>0.31658539175987238</v>
       </c>
       <c r="P53" s="6">
-        <v>0.3153056204319</v>
+        <v>0.31530562043190002</v>
       </c>
       <c r="Q53" s="6">
-        <v>0.3140991032123566</v>
+        <v>0.31409910321235662</v>
       </c>
       <c r="R53" s="6">
-        <v>0.312913715839386</v>
+        <v>0.31291371583938599</v>
       </c>
       <c r="S53" s="6">
         <v>0.3115595281124115</v>
       </c>
       <c r="T53" s="6">
-        <v>0.3101339638233185</v>
+        <v>0.31013396382331848</v>
       </c>
       <c r="U53" s="6">
-        <v>0.3088804185390472</v>
+        <v>0.30888041853904719</v>
       </c>
       <c r="V53" s="6">
-        <v>0.3075431287288666</v>
+        <v>0.30754312872886658</v>
       </c>
       <c r="W53" s="6">
-        <v>0.3062127232551575</v>
+        <v>0.30621272325515753</v>
       </c>
       <c r="X53" s="6">
         <v>0.305166095495224</v>
       </c>
       <c r="Y53" s="6">
-        <v>0.3039931654930115</v>
+        <v>0.30399316549301147</v>
       </c>
       <c r="Z53" s="6">
         <v>0.3024730384349823</v>
       </c>
       <c r="AA53" s="6">
-        <v>0.3013080656528473</v>
+        <v>0.30130806565284729</v>
       </c>
       <c r="AB53" s="6">
-        <v>0.3005469441413879</v>
+        <v>0.30054694414138788</v>
       </c>
       <c r="AC53" s="6">
-        <v>0.2997858226299286</v>
+        <v>0.29978582262992859</v>
       </c>
       <c r="AD53" s="6">
-        <v>-0.001074574584940091</v>
-      </c>
-    </row>
-    <row r="54" spans="1:30" s="4" customFormat="1"/>
-    <row r="55" spans="1:30" s="4" customFormat="1">
+        <v>-1.074574584940091E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="55" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>29</v>
       </c>
@@ -3904,91 +4235,91 @@
         <v>119</v>
       </c>
       <c r="C55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="D55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="E55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="F55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="G55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="H55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="I55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="J55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="K55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="L55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="M55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="N55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="O55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="P55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="Q55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="R55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="S55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="T55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="U55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="V55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="W55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="X55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="Y55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="Z55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="AA55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="AB55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="AC55" s="4">
-        <v>0.1581040173768997</v>
+        <v>0.15810401737689969</v>
       </c>
       <c r="AD55" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:30" s="4" customFormat="1">
+    <row r="56" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>30</v>
       </c>
@@ -3996,97 +4327,97 @@
         <v>120</v>
       </c>
       <c r="C56" s="4">
-        <v>0.6534112691879272</v>
+        <v>0.65341126918792725</v>
       </c>
       <c r="D56" s="4">
-        <v>0.6648083925247192</v>
+        <v>0.66480839252471924</v>
       </c>
       <c r="E56" s="4">
         <v>0.6779143214225769</v>
       </c>
       <c r="F56" s="4">
-        <v>0.6909120082855225</v>
+        <v>0.69091200828552246</v>
       </c>
       <c r="G56" s="4">
-        <v>0.705056369304657</v>
+        <v>0.70505636930465698</v>
       </c>
       <c r="H56" s="4">
         <v>0.7167046070098877</v>
       </c>
       <c r="I56" s="4">
-        <v>0.7288600206375122</v>
+        <v>0.72886002063751221</v>
       </c>
       <c r="J56" s="4">
-        <v>0.742013692855835</v>
+        <v>0.74201369285583496</v>
       </c>
       <c r="K56" s="4">
-        <v>0.754895031452179</v>
+        <v>0.75489503145217896</v>
       </c>
       <c r="L56" s="4">
         <v>0.7669951319694519</v>
       </c>
       <c r="M56" s="4">
-        <v>0.7802096605300903</v>
+        <v>0.78020966053009033</v>
       </c>
       <c r="N56" s="4">
-        <v>0.7931988835334778</v>
+        <v>0.79319888353347778</v>
       </c>
       <c r="O56" s="4">
-        <v>0.805317759513855</v>
+        <v>0.80531775951385498</v>
       </c>
       <c r="P56" s="4">
-        <v>0.8169849514961243</v>
+        <v>0.81698495149612427</v>
       </c>
       <c r="Q56" s="4">
-        <v>0.8283050060272217</v>
+        <v>0.82830500602722168</v>
       </c>
       <c r="R56" s="4">
-        <v>0.8403613567352295</v>
+        <v>0.84036135673522949</v>
       </c>
       <c r="S56" s="4">
-        <v>0.8516795635223389</v>
+        <v>0.85167956352233887</v>
       </c>
       <c r="T56" s="4">
         <v>0.8624190092086792</v>
       </c>
       <c r="U56" s="4">
-        <v>0.8733571171760559</v>
+        <v>0.87335711717605591</v>
       </c>
       <c r="V56" s="4">
         <v>0.8842119574546814</v>
       </c>
       <c r="W56" s="4">
-        <v>0.8949315547943115</v>
+        <v>0.89493155479431152</v>
       </c>
       <c r="X56" s="4">
-        <v>0.9058852791786194</v>
+        <v>0.90588527917861938</v>
       </c>
       <c r="Y56" s="4">
-        <v>0.9164712429046631</v>
+        <v>0.91647124290466309</v>
       </c>
       <c r="Z56" s="4">
-        <v>0.927485466003418</v>
+        <v>0.92748546600341797</v>
       </c>
       <c r="AA56" s="4">
-        <v>0.9386535286903381</v>
+        <v>0.93865352869033813</v>
       </c>
       <c r="AB56" s="4">
-        <v>0.9499249458312988</v>
+        <v>0.94992494583129883</v>
       </c>
       <c r="AC56" s="4">
-        <v>0.9611791372299194</v>
+        <v>0.96117913722991943</v>
       </c>
       <c r="AD56" s="4">
-        <v>0.01495511175302711</v>
-      </c>
-    </row>
-    <row r="57" spans="1:30" s="4" customFormat="1"/>
-    <row r="58" spans="1:30" s="6" customFormat="1">
+        <v>1.495511175302711E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="58" spans="1:30" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B58" s="6" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="59" spans="1:30" s="4" customFormat="1">
+    <row r="59" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>31</v>
       </c>
@@ -4109,7 +4440,7 @@
         <v>1.989543557167053</v>
       </c>
       <c r="H59" s="4">
-        <v>1.979185581207275</v>
+        <v>1.9791855812072749</v>
       </c>
       <c r="I59" s="4">
         <v>1.964890599250793</v>
@@ -4118,31 +4449,31 @@
         <v>1.95296323299408</v>
       </c>
       <c r="K59" s="4">
-        <v>1.936760902404785</v>
+        <v>1.9367609024047849</v>
       </c>
       <c r="L59" s="4">
         <v>1.917664647102356</v>
       </c>
       <c r="M59" s="4">
-        <v>1.900959134101868</v>
+        <v>1.9009591341018679</v>
       </c>
       <c r="N59" s="4">
-        <v>1.890418767929077</v>
+        <v>1.8904187679290769</v>
       </c>
       <c r="O59" s="4">
         <v>1.884477853775024</v>
       </c>
       <c r="P59" s="4">
-        <v>1.881182670593262</v>
+        <v>1.8811826705932619</v>
       </c>
       <c r="Q59" s="4">
         <v>1.879382848739624</v>
       </c>
       <c r="R59" s="4">
-        <v>1.877498626708984</v>
+        <v>1.8774986267089839</v>
       </c>
       <c r="S59" s="4">
-        <v>1.873950362205505</v>
+        <v>1.8739503622055049</v>
       </c>
       <c r="T59" s="4">
         <v>1.867707490921021</v>
@@ -4151,19 +4482,19 @@
         <v>1.859633684158325</v>
       </c>
       <c r="V59" s="4">
-        <v>1.850535750389099</v>
+        <v>1.8505357503890989</v>
       </c>
       <c r="W59" s="4">
-        <v>1.842466115951538</v>
+        <v>1.8424661159515381</v>
       </c>
       <c r="X59" s="4">
         <v>1.834600448608398</v>
       </c>
       <c r="Y59" s="4">
-        <v>1.826247215270996</v>
+        <v>1.8262472152709961</v>
       </c>
       <c r="Z59" s="4">
-        <v>1.819222807884216</v>
+        <v>1.8192228078842161</v>
       </c>
       <c r="AA59" s="4">
         <v>1.81401002407074</v>
@@ -4172,13 +4503,13 @@
         <v>1.810238838195801</v>
       </c>
       <c r="AC59" s="4">
-        <v>1.807237267494202</v>
+        <v>1.8072372674942021</v>
       </c>
       <c r="AD59" s="4">
-        <v>0.0002998515904593102</v>
-      </c>
-    </row>
-    <row r="60" spans="1:30" s="4" customFormat="1">
+        <v>2.998515904593102E-4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>32</v>
       </c>
@@ -4189,88 +4520,88 @@
         <v>0.5911526083946228</v>
       </c>
       <c r="D60" s="4">
-        <v>0.5729323625564575</v>
+        <v>0.57293236255645752</v>
       </c>
       <c r="E60" s="4">
         <v>0.5846707820892334</v>
       </c>
       <c r="F60" s="4">
-        <v>0.5993650555610657</v>
+        <v>0.59936505556106567</v>
       </c>
       <c r="G60" s="4">
-        <v>0.6110865473747253</v>
+        <v>0.61108654737472534</v>
       </c>
       <c r="H60" s="4">
-        <v>0.618757426738739</v>
+        <v>0.61875742673873901</v>
       </c>
       <c r="I60" s="4">
-        <v>0.6241035461425781</v>
+        <v>0.62410354614257813</v>
       </c>
       <c r="J60" s="4">
-        <v>0.6292652487754822</v>
+        <v>0.62926524877548218</v>
       </c>
       <c r="K60" s="4">
-        <v>0.6353371739387512</v>
+        <v>0.63533717393875122</v>
       </c>
       <c r="L60" s="4">
-        <v>0.6405924558639526</v>
+        <v>0.64059245586395264</v>
       </c>
       <c r="M60" s="4">
-        <v>0.6469764709472656</v>
+        <v>0.64697647094726563</v>
       </c>
       <c r="N60" s="4">
-        <v>0.6550318598747253</v>
+        <v>0.65503185987472534</v>
       </c>
       <c r="O60" s="4">
-        <v>0.6647192239761353</v>
+        <v>0.66471922397613525</v>
       </c>
       <c r="P60" s="4">
-        <v>0.675117015838623</v>
+        <v>0.67511701583862305</v>
       </c>
       <c r="Q60" s="4">
-        <v>0.6854830980300903</v>
+        <v>0.68548309803009033</v>
       </c>
       <c r="R60" s="4">
-        <v>0.6963836550712585</v>
+        <v>0.69638365507125854</v>
       </c>
       <c r="S60" s="4">
-        <v>0.7067157626152039</v>
+        <v>0.70671576261520386</v>
       </c>
       <c r="T60" s="4">
-        <v>0.7168050408363342</v>
+        <v>0.71680504083633423</v>
       </c>
       <c r="U60" s="4">
-        <v>0.7258920073509216</v>
+        <v>0.72589200735092163</v>
       </c>
       <c r="V60" s="4">
-        <v>0.7350201606750488</v>
+        <v>0.73502016067504883</v>
       </c>
       <c r="W60" s="4">
-        <v>0.7440880537033081</v>
+        <v>0.74408805370330811</v>
       </c>
       <c r="X60" s="4">
-        <v>0.7531695961952209</v>
+        <v>0.75316959619522095</v>
       </c>
       <c r="Y60" s="4">
-        <v>0.7621986269950867</v>
+        <v>0.76219862699508667</v>
       </c>
       <c r="Z60" s="4">
-        <v>0.771777868270874</v>
+        <v>0.77177786827087402</v>
       </c>
       <c r="AA60" s="4">
-        <v>0.7821990251541138</v>
+        <v>0.78219902515411377</v>
       </c>
       <c r="AB60" s="4">
-        <v>0.7938435077667236</v>
+        <v>0.79384350776672363</v>
       </c>
       <c r="AC60" s="4">
-        <v>0.8066538572311401</v>
+        <v>0.80665385723114014</v>
       </c>
       <c r="AD60" s="4">
-        <v>0.01202637476412116</v>
-      </c>
-    </row>
-    <row r="61" spans="1:30" s="4" customFormat="1">
+        <v>1.202637476412116E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>33</v>
       </c>
@@ -4278,91 +4609,91 @@
         <v>101</v>
       </c>
       <c r="C61" s="4">
-        <v>0.3481809794902802</v>
+        <v>0.34818097949028021</v>
       </c>
       <c r="D61" s="4">
-        <v>0.3602658808231354</v>
+        <v>0.36026588082313538</v>
       </c>
       <c r="E61" s="4">
-        <v>0.3681590259075165</v>
+        <v>0.36815902590751648</v>
       </c>
       <c r="F61" s="4">
-        <v>0.373233437538147</v>
+        <v>0.37323343753814697</v>
       </c>
       <c r="G61" s="4">
-        <v>0.3768399655818939</v>
+        <v>0.37683996558189392</v>
       </c>
       <c r="H61" s="4">
         <v>0.3793962299823761</v>
       </c>
       <c r="I61" s="4">
-        <v>0.3812530338764191</v>
+        <v>0.38125303387641912</v>
       </c>
       <c r="J61" s="4">
-        <v>0.3831798434257507</v>
+        <v>0.38317984342575068</v>
       </c>
       <c r="K61" s="4">
-        <v>0.3843502998352051</v>
+        <v>0.38435029983520508</v>
       </c>
       <c r="L61" s="4">
-        <v>0.3851632177829742</v>
+        <v>0.38516321778297419</v>
       </c>
       <c r="M61" s="4">
-        <v>0.3864753544330597</v>
+        <v>0.38647535443305969</v>
       </c>
       <c r="N61" s="4">
         <v>0.388785719871521</v>
       </c>
       <c r="O61" s="4">
-        <v>0.3920733332633972</v>
+        <v>0.39207333326339722</v>
       </c>
       <c r="P61" s="4">
-        <v>0.3959358930587769</v>
+        <v>0.39593589305877691</v>
       </c>
       <c r="Q61" s="4">
-        <v>0.4000773429870605</v>
+        <v>0.40007734298706049</v>
       </c>
       <c r="R61" s="4">
-        <v>0.4042268395423889</v>
+        <v>0.40422683954238892</v>
       </c>
       <c r="S61" s="4">
-        <v>0.4080361723899841</v>
+        <v>0.40803617238998408</v>
       </c>
       <c r="T61" s="4">
-        <v>0.4113389551639557</v>
+        <v>0.41133895516395569</v>
       </c>
       <c r="U61" s="4">
-        <v>0.4141987264156342</v>
+        <v>0.41419872641563421</v>
       </c>
       <c r="V61" s="4">
-        <v>0.4168368279933929</v>
+        <v>0.41683682799339289</v>
       </c>
       <c r="W61" s="4">
-        <v>0.4196972548961639</v>
+        <v>0.41969725489616388</v>
       </c>
       <c r="X61" s="4">
-        <v>0.4225606322288513</v>
+        <v>0.42256063222885132</v>
       </c>
       <c r="Y61" s="4">
-        <v>0.4253160059452057</v>
+        <v>0.42531600594520569</v>
       </c>
       <c r="Z61" s="4">
-        <v>0.4283616244792938</v>
+        <v>0.42836162447929382</v>
       </c>
       <c r="AA61" s="4">
-        <v>0.4318211078643799</v>
+        <v>0.43182110786437988</v>
       </c>
       <c r="AB61" s="4">
-        <v>0.4355317950248718</v>
+        <v>0.43553179502487183</v>
       </c>
       <c r="AC61" s="4">
-        <v>0.4394381642341614</v>
+        <v>0.43943816423416138</v>
       </c>
       <c r="AD61" s="4">
-        <v>0.008993066457437804</v>
-      </c>
-    </row>
-    <row r="62" spans="1:30" s="4" customFormat="1">
+        <v>8.9930664574378039E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>34</v>
       </c>
@@ -4370,91 +4701,91 @@
         <v>102</v>
       </c>
       <c r="C62" s="4">
-        <v>0.7446191310882568</v>
+        <v>0.74461913108825684</v>
       </c>
       <c r="D62" s="4">
-        <v>0.7564954161643982</v>
+        <v>0.75649541616439819</v>
       </c>
       <c r="E62" s="4">
         <v>0.7730255126953125</v>
       </c>
       <c r="F62" s="4">
-        <v>0.7947636842727661</v>
+        <v>0.79476368427276611</v>
       </c>
       <c r="G62" s="4">
-        <v>0.8128076195716858</v>
+        <v>0.81280761957168579</v>
       </c>
       <c r="H62" s="4">
-        <v>0.8256902098655701</v>
+        <v>0.82569020986557007</v>
       </c>
       <c r="I62" s="4">
-        <v>0.8330134153366089</v>
+        <v>0.83301341533660889</v>
       </c>
       <c r="J62" s="4">
-        <v>0.8399519920349121</v>
+        <v>0.83995199203491211</v>
       </c>
       <c r="K62" s="4">
-        <v>0.8478609323501587</v>
+        <v>0.84786093235015869</v>
       </c>
       <c r="L62" s="4">
-        <v>0.8551452159881592</v>
+        <v>0.85514521598815918</v>
       </c>
       <c r="M62" s="4">
-        <v>0.8636964559555054</v>
+        <v>0.86369645595550537</v>
       </c>
       <c r="N62" s="4">
-        <v>0.8739328980445862</v>
+        <v>0.87393289804458618</v>
       </c>
       <c r="O62" s="4">
-        <v>0.8862233757972717</v>
+        <v>0.88622337579727173</v>
       </c>
       <c r="P62" s="4">
-        <v>0.8987996578216553</v>
+        <v>0.89879965782165527</v>
       </c>
       <c r="Q62" s="4">
-        <v>0.9113155007362366</v>
+        <v>0.91131550073623657</v>
       </c>
       <c r="R62" s="4">
-        <v>0.9241510033607483</v>
+        <v>0.92415100336074829</v>
       </c>
       <c r="S62" s="4">
-        <v>0.9365066289901733</v>
+        <v>0.93650662899017334</v>
       </c>
       <c r="T62" s="4">
-        <v>0.9482896327972412</v>
+        <v>0.94828963279724121</v>
       </c>
       <c r="U62" s="4">
-        <v>0.9588725566864014</v>
+        <v>0.95887255668640137</v>
       </c>
       <c r="V62" s="4">
-        <v>0.968958854675293</v>
+        <v>0.96895885467529297</v>
       </c>
       <c r="W62" s="4">
-        <v>0.9787622690200806</v>
+        <v>0.97876226902008057</v>
       </c>
       <c r="X62" s="4">
-        <v>0.9886872172355652</v>
+        <v>0.98868721723556519</v>
       </c>
       <c r="Y62" s="4">
-        <v>0.9984681606292725</v>
+        <v>0.99846816062927246</v>
       </c>
       <c r="Z62" s="4">
         <v>1.008850574493408</v>
       </c>
       <c r="AA62" s="4">
-        <v>1.020036816596985</v>
+        <v>1.0200368165969851</v>
       </c>
       <c r="AB62" s="4">
-        <v>1.032297134399414</v>
+        <v>1.0322971343994141</v>
       </c>
       <c r="AC62" s="4">
-        <v>1.045639514923096</v>
+        <v>1.0456395149230959</v>
       </c>
       <c r="AD62" s="4">
-        <v>0.01314374874526014</v>
-      </c>
-    </row>
-    <row r="63" spans="1:30" s="4" customFormat="1">
+        <v>1.314374874526014E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>35</v>
       </c>
@@ -4465,88 +4796,88 @@
         <v>0.4852403998374939</v>
       </c>
       <c r="D63" s="4">
-        <v>0.5024849772453308</v>
+        <v>0.50248497724533081</v>
       </c>
       <c r="E63" s="4">
-        <v>0.5124850273132324</v>
+        <v>0.51248502731323242</v>
       </c>
       <c r="F63" s="4">
-        <v>0.5198961496353149</v>
+        <v>0.51989614963531494</v>
       </c>
       <c r="G63" s="4">
-        <v>0.5250965356826782</v>
+        <v>0.52509653568267822</v>
       </c>
       <c r="H63" s="4">
-        <v>0.5288273096084595</v>
+        <v>0.52882730960845947</v>
       </c>
       <c r="I63" s="4">
-        <v>0.5315682888031006</v>
+        <v>0.53156828880310059</v>
       </c>
       <c r="J63" s="4">
         <v>0.534706711769104</v>
       </c>
       <c r="K63" s="4">
-        <v>0.5368260145187378</v>
+        <v>0.53682601451873779</v>
       </c>
       <c r="L63" s="4">
-        <v>0.5385550260543823</v>
+        <v>0.53855502605438232</v>
       </c>
       <c r="M63" s="4">
-        <v>0.5409257411956787</v>
+        <v>0.54092574119567871</v>
       </c>
       <c r="N63" s="4">
-        <v>0.5446266531944275</v>
+        <v>0.54462665319442749</v>
       </c>
       <c r="O63" s="4">
-        <v>0.549626350402832</v>
+        <v>0.54962635040283203</v>
       </c>
       <c r="P63" s="4">
-        <v>0.5553494691848755</v>
+        <v>0.55534946918487549</v>
       </c>
       <c r="Q63" s="4">
         <v>0.5613827109336853</v>
       </c>
       <c r="R63" s="4">
-        <v>0.5673300623893738</v>
+        <v>0.56733006238937378</v>
       </c>
       <c r="S63" s="4">
-        <v>0.5727502107620239</v>
+        <v>0.57275021076202393</v>
       </c>
       <c r="T63" s="4">
-        <v>0.5775822401046753</v>
+        <v>0.57758224010467529</v>
       </c>
       <c r="U63" s="4">
-        <v>0.581812858581543</v>
+        <v>0.58181285858154297</v>
       </c>
       <c r="V63" s="4">
-        <v>0.5857148766517639</v>
+        <v>0.58571487665176392</v>
       </c>
       <c r="W63" s="4">
-        <v>0.5898987650871277</v>
+        <v>0.58989876508712769</v>
       </c>
       <c r="X63" s="4">
-        <v>0.594043493270874</v>
+        <v>0.59404349327087402</v>
       </c>
       <c r="Y63" s="4">
-        <v>0.5979878902435303</v>
+        <v>0.59798789024353027</v>
       </c>
       <c r="Z63" s="4">
-        <v>0.6023037433624268</v>
+        <v>0.60230374336242676</v>
       </c>
       <c r="AA63" s="4">
-        <v>0.6071649789810181</v>
+        <v>0.60716497898101807</v>
       </c>
       <c r="AB63" s="4">
-        <v>0.6123083829879761</v>
+        <v>0.61230838298797607</v>
       </c>
       <c r="AC63" s="4">
-        <v>0.6176539063453674</v>
+        <v>0.61765390634536743</v>
       </c>
       <c r="AD63" s="4">
-        <v>0.009323341798237017</v>
-      </c>
-    </row>
-    <row r="64" spans="1:30" s="4" customFormat="1">
+        <v>9.323341798237017E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>36</v>
       </c>
@@ -4554,7 +4885,7 @@
         <v>104</v>
       </c>
       <c r="C64" s="4">
-        <v>0.5755947232246399</v>
+        <v>0.57559472322463989</v>
       </c>
       <c r="D64" s="4">
         <v>0.5640031099319458</v>
@@ -4563,82 +4894,82 @@
         <v>0.5612906813621521</v>
       </c>
       <c r="F64" s="4">
-        <v>0.5649812817573547</v>
+        <v>0.56498128175735474</v>
       </c>
       <c r="G64" s="4">
-        <v>0.5679190754890442</v>
+        <v>0.56791907548904419</v>
       </c>
       <c r="H64" s="4">
-        <v>0.5683069229125977</v>
+        <v>0.56830692291259766</v>
       </c>
       <c r="I64" s="4">
-        <v>0.5582931637763977</v>
+        <v>0.55829316377639771</v>
       </c>
       <c r="J64" s="4">
-        <v>0.5493459105491638</v>
+        <v>0.54934591054916382</v>
       </c>
       <c r="K64" s="4">
-        <v>0.5419877767562866</v>
+        <v>0.54198777675628662</v>
       </c>
       <c r="L64" s="4">
-        <v>0.5346543788909912</v>
+        <v>0.53465437889099121</v>
       </c>
       <c r="M64" s="4">
-        <v>0.5281133651733398</v>
+        <v>0.52811336517333984</v>
       </c>
       <c r="N64" s="4">
-        <v>0.5227332711219788</v>
+        <v>0.52273327112197876</v>
       </c>
       <c r="O64" s="4">
-        <v>0.5190929174423218</v>
+        <v>0.51909291744232178</v>
       </c>
       <c r="P64" s="4">
-        <v>0.5165110230445862</v>
+        <v>0.51651102304458618</v>
       </c>
       <c r="Q64" s="4">
-        <v>0.5145660042762756</v>
+        <v>0.51456600427627563</v>
       </c>
       <c r="R64" s="4">
-        <v>0.51337069272995</v>
+        <v>0.51337069272994995</v>
       </c>
       <c r="S64" s="4">
-        <v>0.5109866857528687</v>
+        <v>0.51098668575286865</v>
       </c>
       <c r="T64" s="4">
-        <v>0.5093018412590027</v>
+        <v>0.50930184125900269</v>
       </c>
       <c r="U64" s="4">
-        <v>0.5074021220207214</v>
+        <v>0.50740212202072144</v>
       </c>
       <c r="V64" s="4">
-        <v>0.5057253837585449</v>
+        <v>0.50572538375854492</v>
       </c>
       <c r="W64" s="4">
-        <v>0.5042718648910522</v>
+        <v>0.50427186489105225</v>
       </c>
       <c r="X64" s="4">
         <v>0.5030590295791626</v>
       </c>
       <c r="Y64" s="4">
-        <v>0.5016676187515259</v>
+        <v>0.50166761875152588</v>
       </c>
       <c r="Z64" s="4">
-        <v>0.5007129907608032</v>
+        <v>0.50071299076080322</v>
       </c>
       <c r="AA64" s="4">
         <v>0.5003892183303833</v>
       </c>
       <c r="AB64" s="4">
-        <v>0.5006906390190125</v>
+        <v>0.50069063901901245</v>
       </c>
       <c r="AC64" s="4">
-        <v>0.5018773674964905</v>
+        <v>0.50187736749649048</v>
       </c>
       <c r="AD64" s="4">
-        <v>-0.005257209385896688</v>
-      </c>
-    </row>
-    <row r="65" spans="1:30" s="4" customFormat="1">
+        <v>-5.2572093858966884E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>37</v>
       </c>
@@ -4646,10 +4977,10 @@
         <v>105</v>
       </c>
       <c r="C65" s="4">
-        <v>0.3673001527786255</v>
+        <v>0.36730015277862549</v>
       </c>
       <c r="D65" s="4">
-        <v>0.3686024844646454</v>
+        <v>0.36860248446464539</v>
       </c>
       <c r="E65" s="4">
         <v>0.3707335889339447</v>
@@ -4658,79 +4989,79 @@
         <v>0.3743739128112793</v>
       </c>
       <c r="G65" s="4">
-        <v>0.3776519894599915</v>
+        <v>0.37765198945999151</v>
       </c>
       <c r="H65" s="4">
-        <v>0.3800609707832336</v>
+        <v>0.38006097078323359</v>
       </c>
       <c r="I65" s="4">
-        <v>0.3808006942272186</v>
+        <v>0.38080069422721857</v>
       </c>
       <c r="J65" s="4">
-        <v>0.3818013370037079</v>
+        <v>0.38180133700370789</v>
       </c>
       <c r="K65" s="4">
-        <v>0.3831851482391357</v>
+        <v>0.38318514823913569</v>
       </c>
       <c r="L65" s="4">
-        <v>0.3846486806869507</v>
+        <v>0.38464868068695068</v>
       </c>
       <c r="M65" s="4">
-        <v>0.3864732086658478</v>
+        <v>0.38647320866584778</v>
       </c>
       <c r="N65" s="4">
-        <v>0.3886882364749908</v>
+        <v>0.38868823647499079</v>
       </c>
       <c r="O65" s="4">
-        <v>0.3912994265556335</v>
+        <v>0.39129942655563349</v>
       </c>
       <c r="P65" s="4">
         <v>0.393959641456604</v>
       </c>
       <c r="Q65" s="4">
-        <v>0.3965804278850555</v>
+        <v>0.39658042788505549</v>
       </c>
       <c r="R65" s="4">
-        <v>0.3992148637771606</v>
+        <v>0.39921486377716059</v>
       </c>
       <c r="S65" s="4">
-        <v>0.4017241299152374</v>
+        <v>0.40172412991523743</v>
       </c>
       <c r="T65" s="4">
-        <v>0.4043815433979034</v>
+        <v>0.40438154339790339</v>
       </c>
       <c r="U65" s="4">
-        <v>0.4068149924278259</v>
+        <v>0.40681499242782593</v>
       </c>
       <c r="V65" s="4">
-        <v>0.4091392755508423</v>
+        <v>0.40913927555084229</v>
       </c>
       <c r="W65" s="4">
-        <v>0.4113937616348267</v>
+        <v>0.41139376163482672</v>
       </c>
       <c r="X65" s="4">
-        <v>0.4136457741260529</v>
+        <v>0.41364577412605291</v>
       </c>
       <c r="Y65" s="4">
-        <v>0.4158335328102112</v>
+        <v>0.41583353281021118</v>
       </c>
       <c r="Z65" s="4">
-        <v>0.4180770814418793</v>
+        <v>0.41807708144187927</v>
       </c>
       <c r="AA65" s="4">
-        <v>0.4204134047031403</v>
+        <v>0.42041340470314031</v>
       </c>
       <c r="AB65" s="4">
-        <v>0.4228944480419159</v>
+        <v>0.42289444804191589</v>
       </c>
       <c r="AC65" s="4">
-        <v>0.4255006313323975</v>
+        <v>0.42550063133239752</v>
       </c>
       <c r="AD65" s="4">
-        <v>0.00567322687411842</v>
-      </c>
-    </row>
-    <row r="66" spans="1:30" s="4" customFormat="1">
+        <v>5.67322687411842E-3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>38</v>
       </c>
@@ -4738,70 +5069,70 @@
         <v>106</v>
       </c>
       <c r="C66" s="4">
-        <v>0.3410233557224274</v>
+        <v>0.34102335572242742</v>
       </c>
       <c r="D66" s="4">
-        <v>0.3573471009731293</v>
+        <v>0.35734710097312927</v>
       </c>
       <c r="E66" s="4">
-        <v>0.3753615021705627</v>
+        <v>0.37536150217056269</v>
       </c>
       <c r="F66" s="4">
-        <v>0.3948878943920135</v>
+        <v>0.39488789439201349</v>
       </c>
       <c r="G66" s="4">
-        <v>0.4153228402137756</v>
+        <v>0.41532284021377558</v>
       </c>
       <c r="H66" s="4">
-        <v>0.4354186654090881</v>
+        <v>0.43541866540908808</v>
       </c>
       <c r="I66" s="4">
-        <v>0.4556160271167755</v>
+        <v>0.45561602711677551</v>
       </c>
       <c r="J66" s="4">
-        <v>0.4765667021274567</v>
+        <v>0.47656670212745672</v>
       </c>
       <c r="K66" s="4">
-        <v>0.498712956905365</v>
+        <v>0.49871295690536499</v>
       </c>
       <c r="L66" s="4">
-        <v>0.5220028162002563</v>
+        <v>0.52200281620025635</v>
       </c>
       <c r="M66" s="4">
-        <v>0.5467246770858765</v>
+        <v>0.54672467708587646</v>
       </c>
       <c r="N66" s="4">
-        <v>0.5729601979255676</v>
+        <v>0.57296019792556763</v>
       </c>
       <c r="O66" s="4">
         <v>0.6007838249206543</v>
       </c>
       <c r="P66" s="4">
-        <v>0.6306106448173523</v>
+        <v>0.63061064481735229</v>
       </c>
       <c r="Q66" s="4">
-        <v>0.6613415479660034</v>
+        <v>0.66134154796600342</v>
       </c>
       <c r="R66" s="4">
-        <v>0.6936936974525452</v>
+        <v>0.69369369745254517</v>
       </c>
       <c r="S66" s="4">
-        <v>0.7276855111122131</v>
+        <v>0.72768551111221313</v>
       </c>
       <c r="T66" s="4">
-        <v>0.7633203268051147</v>
+        <v>0.76332032680511475</v>
       </c>
       <c r="U66" s="4">
         <v>0.7999948263168335</v>
       </c>
       <c r="V66" s="4">
-        <v>0.8378559350967407</v>
+        <v>0.83785593509674072</v>
       </c>
       <c r="W66" s="4">
-        <v>0.8777375817298889</v>
+        <v>0.87773758172988892</v>
       </c>
       <c r="X66" s="4">
-        <v>0.9190672636032104</v>
+        <v>0.91906726360321045</v>
       </c>
       <c r="Y66" s="4">
         <v>0.9618690013885498</v>
@@ -4810,19 +5141,19 @@
         <v>1.007150530815125</v>
       </c>
       <c r="AA66" s="4">
-        <v>1.054268836975098</v>
+        <v>1.0542688369750981</v>
       </c>
       <c r="AB66" s="4">
         <v>1.102479934692383</v>
       </c>
       <c r="AC66" s="4">
-        <v>1.153587460517883</v>
+        <v>1.1535874605178831</v>
       </c>
       <c r="AD66" s="4">
-        <v>0.0479882179842217</v>
-      </c>
-    </row>
-    <row r="67" spans="1:30" s="4" customFormat="1">
+        <v>4.7988217984221697E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>39</v>
       </c>
@@ -4830,91 +5161,91 @@
         <v>107</v>
       </c>
       <c r="C67" s="4">
-        <v>0.04323187842965126</v>
+        <v>4.323187842965126E-2</v>
       </c>
       <c r="D67" s="4">
-        <v>0.043303232640028</v>
+        <v>4.3303232640028E-2</v>
       </c>
       <c r="E67" s="4">
-        <v>0.04352026432752609</v>
+        <v>4.3520264327526093E-2</v>
       </c>
       <c r="F67" s="4">
-        <v>0.04388755932450294</v>
+        <v>4.3887559324502938E-2</v>
       </c>
       <c r="G67" s="4">
-        <v>0.04433385282754898</v>
+        <v>4.4333852827548981E-2</v>
       </c>
       <c r="H67" s="4">
-        <v>0.04471053555607796</v>
+        <v>4.4710535556077957E-2</v>
       </c>
       <c r="I67" s="4">
-        <v>0.04503057524561882</v>
+        <v>4.503057524561882E-2</v>
       </c>
       <c r="J67" s="4">
-        <v>0.04537007585167885</v>
+        <v>4.5370075851678848E-2</v>
       </c>
       <c r="K67" s="4">
-        <v>0.04571310058236122</v>
+        <v>4.5713100582361221E-2</v>
       </c>
       <c r="L67" s="4">
-        <v>0.04610182344913483</v>
+        <v>4.6101823449134827E-2</v>
       </c>
       <c r="M67" s="4">
-        <v>0.04655520617961884</v>
+        <v>4.6555206179618842E-2</v>
       </c>
       <c r="N67" s="4">
-        <v>0.04701841622591019</v>
+        <v>4.7018416225910187E-2</v>
       </c>
       <c r="O67" s="4">
-        <v>0.04749026149511337</v>
+        <v>4.7490261495113373E-2</v>
       </c>
       <c r="P67" s="4">
-        <v>0.04795121029019356</v>
+        <v>4.7951210290193558E-2</v>
       </c>
       <c r="Q67" s="4">
-        <v>0.04833761230111122</v>
+        <v>4.8337612301111221E-2</v>
       </c>
       <c r="R67" s="4">
-        <v>0.04871273040771484</v>
+        <v>4.8712730407714837E-2</v>
       </c>
       <c r="S67" s="4">
-        <v>0.04900911450386047</v>
+        <v>4.9009114503860467E-2</v>
       </c>
       <c r="T67" s="4">
-        <v>0.04915787652134895</v>
+        <v>4.9157876521348953E-2</v>
       </c>
       <c r="U67" s="4">
-        <v>0.04921872913837433</v>
+        <v>4.9218729138374329E-2</v>
       </c>
       <c r="V67" s="4">
-        <v>0.04919819161295891</v>
+        <v>4.9198191612958908E-2</v>
       </c>
       <c r="W67" s="4">
-        <v>0.04903504624962807</v>
+        <v>4.9035046249628067E-2</v>
       </c>
       <c r="X67" s="4">
-        <v>0.04866769164800644</v>
+        <v>4.8667691648006439E-2</v>
       </c>
       <c r="Y67" s="4">
-        <v>0.04821724072098732</v>
+        <v>4.821724072098732E-2</v>
       </c>
       <c r="Z67" s="4">
-        <v>0.04755975306034088</v>
+        <v>4.7559753060340881E-2</v>
       </c>
       <c r="AA67" s="4">
-        <v>0.04669306799769402</v>
+        <v>4.6693067997694022E-2</v>
       </c>
       <c r="AB67" s="4">
-        <v>0.045680221170187</v>
+        <v>4.5680221170187003E-2</v>
       </c>
       <c r="AC67" s="4">
-        <v>0.04444917663931847</v>
+        <v>4.4449176639318473E-2</v>
       </c>
       <c r="AD67" s="4">
-        <v>0.001068581633108634</v>
-      </c>
-    </row>
-    <row r="68" spans="1:30" s="4" customFormat="1">
+        <v>1.068581633108634E-3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
         <v>40</v>
       </c>
@@ -4925,88 +5256,88 @@
         <v>4.148036003112793</v>
       </c>
       <c r="D68" s="4">
-        <v>4.236347675323486</v>
+        <v>4.2363476753234863</v>
       </c>
       <c r="E68" s="4">
-        <v>4.17954683303833</v>
+        <v>4.1795468330383301</v>
       </c>
       <c r="F68" s="4">
-        <v>4.173418521881104</v>
+        <v>4.1734185218811044</v>
       </c>
       <c r="G68" s="4">
-        <v>4.161029815673828</v>
+        <v>4.1610298156738281</v>
       </c>
       <c r="H68" s="4">
-        <v>4.210443496704102</v>
+        <v>4.2104434967041016</v>
       </c>
       <c r="I68" s="4">
-        <v>4.255163669586182</v>
+        <v>4.2551636695861816</v>
       </c>
       <c r="J68" s="4">
-        <v>4.299385547637939</v>
+        <v>4.2993855476379386</v>
       </c>
       <c r="K68" s="4">
         <v>4.340360164642334</v>
       </c>
       <c r="L68" s="4">
-        <v>4.379752635955811</v>
+        <v>4.3797526359558114</v>
       </c>
       <c r="M68" s="4">
-        <v>4.422580718994141</v>
+        <v>4.4225807189941406</v>
       </c>
       <c r="N68" s="4">
-        <v>4.469513416290283</v>
+        <v>4.4695134162902832</v>
       </c>
       <c r="O68" s="4">
-        <v>4.520428657531738</v>
+        <v>4.5204286575317383</v>
       </c>
       <c r="P68" s="4">
         <v>4.573509693145752</v>
       </c>
       <c r="Q68" s="4">
-        <v>4.628166198730469</v>
+        <v>4.6281661987304688</v>
       </c>
       <c r="R68" s="4">
-        <v>4.684449195861816</v>
+        <v>4.6844491958618164</v>
       </c>
       <c r="S68" s="4">
         <v>4.739593505859375</v>
       </c>
       <c r="T68" s="4">
-        <v>4.79218053817749</v>
+        <v>4.7921805381774902</v>
       </c>
       <c r="U68" s="4">
-        <v>4.844249248504639</v>
+        <v>4.8442492485046387</v>
       </c>
       <c r="V68" s="4">
-        <v>4.896039962768555</v>
+        <v>4.8960399627685547</v>
       </c>
       <c r="W68" s="4">
-        <v>4.949419975280762</v>
+        <v>4.9494199752807617</v>
       </c>
       <c r="X68" s="4">
-        <v>5.004261016845703</v>
+        <v>5.0042610168457031</v>
       </c>
       <c r="Y68" s="4">
         <v>5.059049129486084</v>
       </c>
       <c r="Z68" s="4">
-        <v>5.115761756896973</v>
+        <v>5.1157617568969727</v>
       </c>
       <c r="AA68" s="4">
-        <v>5.175616264343262</v>
+        <v>5.1756162643432617</v>
       </c>
       <c r="AB68" s="4">
-        <v>5.238050937652588</v>
+        <v>5.2380509376525879</v>
       </c>
       <c r="AC68" s="4">
         <v>5.302912712097168</v>
       </c>
       <c r="AD68" s="4">
-        <v>0.00949173533187353</v>
-      </c>
-    </row>
-    <row r="69" spans="1:30" s="6" customFormat="1">
+        <v>9.4917353318735298E-3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:30" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
         <v>41</v>
       </c>
@@ -5014,34 +5345,34 @@
         <v>123</v>
       </c>
       <c r="C69" s="6">
-        <v>9.43758487701416</v>
+        <v>9.4375848770141602</v>
       </c>
       <c r="D69" s="6">
-        <v>9.729910850524902</v>
+        <v>9.7299108505249023</v>
       </c>
       <c r="E69" s="6">
-        <v>9.756376266479492</v>
+        <v>9.7563762664794922</v>
       </c>
       <c r="F69" s="6">
-        <v>9.832100868225098</v>
+        <v>9.8321008682250977</v>
       </c>
       <c r="G69" s="6">
-        <v>9.881631851196289</v>
+        <v>9.8816318511962891</v>
       </c>
       <c r="H69" s="6">
-        <v>9.970797538757324</v>
+        <v>9.9707975387573242</v>
       </c>
       <c r="I69" s="6">
-        <v>10.0297327041626</v>
+        <v>10.029732704162599</v>
       </c>
       <c r="J69" s="6">
-        <v>10.09253692626953</v>
+        <v>10.092536926269529</v>
       </c>
       <c r="K69" s="6">
         <v>10.15109443664551</v>
       </c>
       <c r="L69" s="6">
-        <v>10.2042818069458</v>
+        <v>10.204281806945801</v>
       </c>
       <c r="M69" s="6">
         <v>10.26948070526123</v>
@@ -5059,46 +5390,46 @@
         <v>10.68663215637207</v>
       </c>
       <c r="R69" s="6">
-        <v>10.80903053283691</v>
+        <v>10.809030532836911</v>
       </c>
       <c r="S69" s="6">
-        <v>10.92695808410645</v>
+        <v>10.926958084106451</v>
       </c>
       <c r="T69" s="6">
-        <v>11.04006671905518</v>
+        <v>11.040066719055179</v>
       </c>
       <c r="U69" s="6">
         <v>11.14809036254883</v>
       </c>
       <c r="V69" s="6">
-        <v>11.25502490997314</v>
+        <v>11.255024909973139</v>
       </c>
       <c r="W69" s="6">
-        <v>11.36676979064941</v>
+        <v>11.366769790649411</v>
       </c>
       <c r="X69" s="6">
         <v>11.48176288604736</v>
       </c>
       <c r="Y69" s="6">
-        <v>11.59685516357422</v>
+        <v>11.596855163574221</v>
       </c>
       <c r="Z69" s="6">
-        <v>11.71977806091309</v>
+        <v>11.719778060913089</v>
       </c>
       <c r="AA69" s="6">
         <v>11.85261249542236</v>
       </c>
       <c r="AB69" s="6">
-        <v>11.99401569366455</v>
+        <v>11.994015693664551</v>
       </c>
       <c r="AC69" s="6">
-        <v>12.14494895935059</v>
+        <v>12.144948959350589</v>
       </c>
       <c r="AD69" s="6">
-        <v>0.009747712131148445</v>
-      </c>
-    </row>
-    <row r="70" spans="1:30" s="4" customFormat="1">
+        <v>9.7477121311484449E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>42</v>
       </c>
@@ -5106,19 +5437,19 @@
         <v>124</v>
       </c>
       <c r="C70" s="4">
-        <v>0.01876222528517246</v>
+        <v>1.8762225285172459E-2</v>
       </c>
       <c r="D70" s="4">
-        <v>0.02811118774116039</v>
+        <v>2.8111187741160389E-2</v>
       </c>
       <c r="E70" s="4">
-        <v>0.0422167144715786</v>
+        <v>4.2216714471578598E-2</v>
       </c>
       <c r="F70" s="4">
-        <v>0.06163442134857178</v>
+        <v>6.1634421348571777E-2</v>
       </c>
       <c r="G70" s="4">
-        <v>0.086184062063694</v>
+        <v>8.6184062063694E-2</v>
       </c>
       <c r="H70" s="4">
         <v>0.1169434636831284</v>
@@ -5127,16 +5458,16 @@
         <v>0.1592939347028732</v>
       </c>
       <c r="J70" s="4">
-        <v>0.2128296792507172</v>
+        <v>0.21282967925071719</v>
       </c>
       <c r="K70" s="4">
-        <v>0.2839672565460205</v>
+        <v>0.28396725654602051</v>
       </c>
       <c r="L70" s="4">
-        <v>0.3598229885101318</v>
+        <v>0.35982298851013178</v>
       </c>
       <c r="M70" s="4">
-        <v>0.4345318377017975</v>
+        <v>0.43453183770179749</v>
       </c>
       <c r="N70" s="4">
         <v>0.5064389705657959</v>
@@ -5145,34 +5476,34 @@
         <v>0.5746803879737854</v>
       </c>
       <c r="P70" s="4">
-        <v>0.6394470930099487</v>
+        <v>0.63944709300994873</v>
       </c>
       <c r="Q70" s="4">
-        <v>0.6999316215515137</v>
+        <v>0.69993162155151367</v>
       </c>
       <c r="R70" s="4">
-        <v>0.7563762068748474</v>
+        <v>0.75637620687484741</v>
       </c>
       <c r="S70" s="4">
-        <v>0.8084619641304016</v>
+        <v>0.80846196413040161</v>
       </c>
       <c r="T70" s="4">
-        <v>0.8559121489524841</v>
+        <v>0.85591214895248413</v>
       </c>
       <c r="U70" s="4">
         <v>0.8987807035446167</v>
       </c>
       <c r="V70" s="4">
-        <v>0.9363086819648743</v>
+        <v>0.93630868196487427</v>
       </c>
       <c r="W70" s="4">
-        <v>0.9690288901329041</v>
+        <v>0.96902889013290405</v>
       </c>
       <c r="X70" s="4">
-        <v>0.9983586072921753</v>
+        <v>0.99835860729217529</v>
       </c>
       <c r="Y70" s="4">
-        <v>1.023493051528931</v>
+        <v>1.0234930515289311</v>
       </c>
       <c r="Z70" s="4">
         <v>1.046672463417053</v>
@@ -5181,16 +5512,16 @@
         <v>1.067095875740051</v>
       </c>
       <c r="AB70" s="4">
-        <v>1.085416555404663</v>
+        <v>1.0854165554046631</v>
       </c>
       <c r="AC70" s="4">
-        <v>1.102266550064087</v>
+        <v>1.1022665500640869</v>
       </c>
       <c r="AD70" s="4">
-        <v>0.1696032039626418</v>
-      </c>
-    </row>
-    <row r="71" spans="1:30" s="4" customFormat="1">
+        <v>0.16960320396264181</v>
+      </c>
+    </row>
+    <row r="71" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>43</v>
       </c>
@@ -5201,22 +5532,22 @@
         <v>0.1417428404092789</v>
       </c>
       <c r="D71" s="4">
-        <v>0.1586653888225555</v>
+        <v>0.15866538882255549</v>
       </c>
       <c r="E71" s="4">
-        <v>0.1751562505960464</v>
+        <v>0.17515625059604639</v>
       </c>
       <c r="F71" s="4">
-        <v>0.1821672022342682</v>
+        <v>0.18216720223426819</v>
       </c>
       <c r="G71" s="4">
-        <v>0.1895016580820084</v>
+        <v>0.18950165808200839</v>
       </c>
       <c r="H71" s="4">
-        <v>0.1993240267038345</v>
+        <v>0.19932402670383451</v>
       </c>
       <c r="I71" s="4">
-        <v>0.2111417055130005</v>
+        <v>0.21114170551300049</v>
       </c>
       <c r="J71" s="4">
         <v>0.2262821048498154</v>
@@ -5225,93 +5556,93 @@
         <v>0.2380215525627136</v>
       </c>
       <c r="L71" s="4">
-        <v>0.2538630664348602</v>
+        <v>0.25386306643486017</v>
       </c>
       <c r="M71" s="4">
-        <v>0.2636756598949432</v>
+        <v>0.26367565989494318</v>
       </c>
       <c r="N71" s="4">
-        <v>0.2719502449035645</v>
+        <v>0.27195024490356451</v>
       </c>
       <c r="O71" s="4">
-        <v>0.2785964906215668</v>
+        <v>0.27859649062156677</v>
       </c>
       <c r="P71" s="4">
         <v>0.2867908775806427</v>
       </c>
       <c r="Q71" s="4">
-        <v>0.2923144996166229</v>
+        <v>0.29231449961662292</v>
       </c>
       <c r="R71" s="4">
-        <v>0.2951976954936981</v>
+        <v>0.29519769549369812</v>
       </c>
       <c r="S71" s="4">
-        <v>0.3008307218551636</v>
+        <v>0.30083072185516357</v>
       </c>
       <c r="T71" s="4">
-        <v>0.3085992038249969</v>
+        <v>0.30859920382499689</v>
       </c>
       <c r="U71" s="4">
-        <v>0.317820280790329</v>
+        <v>0.31782028079032898</v>
       </c>
       <c r="V71" s="4">
-        <v>0.3278141021728516</v>
+        <v>0.32781410217285162</v>
       </c>
       <c r="W71" s="4">
-        <v>0.3383373320102692</v>
+        <v>0.33833733201026922</v>
       </c>
       <c r="X71" s="4">
-        <v>0.3482779562473297</v>
+        <v>0.34827795624732971</v>
       </c>
       <c r="Y71" s="4">
         <v>0.35950967669487</v>
       </c>
       <c r="Z71" s="4">
-        <v>0.3691576421260834</v>
+        <v>0.36915764212608337</v>
       </c>
       <c r="AA71" s="4">
-        <v>0.3785410821437836</v>
+        <v>0.37854108214378362</v>
       </c>
       <c r="AB71" s="4">
-        <v>0.3858913481235504</v>
+        <v>0.38589134812355042</v>
       </c>
       <c r="AC71" s="4">
-        <v>0.392189234495163</v>
+        <v>0.39218923449516302</v>
       </c>
       <c r="AD71" s="4">
-        <v>0.03991966268814529</v>
-      </c>
-    </row>
-    <row r="72" spans="1:30" s="6" customFormat="1">
+        <v>3.9919662688145292E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:30" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="B72" s="11" t="s">
         <v>126</v>
       </c>
       <c r="C72" s="6">
-        <v>9.314604759216309</v>
+        <v>9.3146047592163086</v>
       </c>
       <c r="D72" s="6">
-        <v>9.599356651306152</v>
+        <v>9.5993566513061523</v>
       </c>
       <c r="E72" s="6">
-        <v>9.623435974121094</v>
+        <v>9.6234359741210938</v>
       </c>
       <c r="F72" s="6">
-        <v>9.711567878723145</v>
+        <v>9.7115678787231445</v>
       </c>
       <c r="G72" s="6">
-        <v>9.778314590454102</v>
+        <v>9.7783145904541016</v>
       </c>
       <c r="H72" s="6">
-        <v>9.88841724395752</v>
+        <v>9.8884172439575195</v>
       </c>
       <c r="I72" s="6">
-        <v>9.977885246276855</v>
+        <v>9.9778852462768555</v>
       </c>
       <c r="J72" s="6">
-        <v>10.0790843963623</v>
+        <v>10.079084396362299</v>
       </c>
       <c r="K72" s="6">
         <v>10.19703960418701</v>
@@ -5323,10 +5654,10 @@
         <v>10.44033718109131</v>
       </c>
       <c r="N72" s="6">
-        <v>10.58819961547852</v>
+        <v>10.588199615478519</v>
       </c>
       <c r="O72" s="6">
-        <v>10.75229835510254</v>
+        <v>10.752298355102541</v>
       </c>
       <c r="P72" s="6">
         <v>10.9215841293335</v>
@@ -5353,13 +5684,13 @@
         <v>11.99746131896973</v>
       </c>
       <c r="X72" s="6">
-        <v>12.13184356689453</v>
+        <v>12.131843566894529</v>
       </c>
       <c r="Y72" s="6">
-        <v>12.26083850860596</v>
+        <v>12.260838508605961</v>
       </c>
       <c r="Z72" s="6">
-        <v>12.39729309082031</v>
+        <v>12.397293090820311</v>
       </c>
       <c r="AA72" s="6">
         <v>12.54116725921631</v>
@@ -5368,14 +5699,14 @@
         <v>12.69354152679443</v>
       </c>
       <c r="AC72" s="6">
-        <v>12.85502624511719</v>
+        <v>12.855026245117189</v>
       </c>
       <c r="AD72" s="6">
-        <v>0.0124675144508517</v>
-      </c>
-    </row>
-    <row r="73" spans="1:30" s="4" customFormat="1"/>
-    <row r="74" spans="1:30" s="6" customFormat="1">
+        <v>1.24675144508517E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="74" spans="1:30" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A74" s="6" t="s">
         <v>45</v>
       </c>
@@ -5383,97 +5714,97 @@
         <v>127</v>
       </c>
       <c r="C74" s="6">
-        <v>6.777269840240479</v>
+        <v>6.7772698402404794</v>
       </c>
       <c r="D74" s="6">
         <v>6.702521800994873</v>
       </c>
       <c r="E74" s="6">
-        <v>6.252915859222412</v>
+        <v>6.2529158592224121</v>
       </c>
       <c r="F74" s="6">
         <v>6.097465991973877</v>
       </c>
       <c r="G74" s="6">
-        <v>6.01649284362793</v>
+        <v>6.0164928436279297</v>
       </c>
       <c r="H74" s="6">
-        <v>5.971189498901367</v>
+        <v>5.9711894989013672</v>
       </c>
       <c r="I74" s="6">
-        <v>5.80098295211792</v>
+        <v>5.8009829521179199</v>
       </c>
       <c r="J74" s="6">
-        <v>5.651239395141602</v>
+        <v>5.6512393951416016</v>
       </c>
       <c r="K74" s="6">
         <v>5.319979190826416</v>
       </c>
       <c r="L74" s="6">
-        <v>5.143497467041016</v>
+        <v>5.1434974670410156</v>
       </c>
       <c r="M74" s="6">
-        <v>4.961966037750244</v>
+        <v>4.9619660377502441</v>
       </c>
       <c r="N74" s="6">
-        <v>4.831106185913086</v>
+        <v>4.8311061859130859</v>
       </c>
       <c r="O74" s="6">
-        <v>4.674430847167969</v>
+        <v>4.6744308471679688</v>
       </c>
       <c r="P74" s="6">
-        <v>4.508033752441406</v>
+        <v>4.5080337524414063</v>
       </c>
       <c r="Q74" s="6">
-        <v>4.399783611297607</v>
+        <v>4.3997836112976074</v>
       </c>
       <c r="R74" s="6">
-        <v>4.307811260223389</v>
+        <v>4.3078112602233887</v>
       </c>
       <c r="S74" s="6">
-        <v>4.326752662658691</v>
+        <v>4.3267526626586914</v>
       </c>
       <c r="T74" s="6">
-        <v>4.365115642547607</v>
+        <v>4.3651156425476074</v>
       </c>
       <c r="U74" s="6">
-        <v>4.383301258087158</v>
+        <v>4.3833012580871582</v>
       </c>
       <c r="V74" s="6">
-        <v>4.441843032836914</v>
+        <v>4.4418430328369141</v>
       </c>
       <c r="W74" s="6">
-        <v>4.48249340057373</v>
+        <v>4.4824934005737296</v>
       </c>
       <c r="X74" s="6">
-        <v>4.510602951049805</v>
+        <v>4.5106029510498047</v>
       </c>
       <c r="Y74" s="6">
-        <v>4.511162757873535</v>
+        <v>4.5111627578735352</v>
       </c>
       <c r="Z74" s="6">
-        <v>4.522827625274658</v>
+        <v>4.5228276252746582</v>
       </c>
       <c r="AA74" s="6">
-        <v>4.563576221466064</v>
+        <v>4.5635762214660636</v>
       </c>
       <c r="AB74" s="6">
-        <v>4.58096981048584</v>
+        <v>4.5809698104858398</v>
       </c>
       <c r="AC74" s="6">
-        <v>4.5998215675354</v>
+        <v>4.5998215675354004</v>
       </c>
       <c r="AD74" s="6">
-        <v>-0.01479548694832566</v>
-      </c>
-    </row>
-    <row r="75" spans="1:30" s="4" customFormat="1"/>
-    <row r="76" spans="1:30" s="6" customFormat="1">
+        <v>-1.4795486948325659E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="76" spans="1:30" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B76" s="6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="77" spans="1:30" s="4" customFormat="1">
+    <row r="77" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>46</v>
       </c>
@@ -5481,13 +5812,13 @@
         <v>99</v>
       </c>
       <c r="C77" s="4">
-        <v>2.050641298294067</v>
+        <v>2.0506412982940669</v>
       </c>
       <c r="D77" s="4">
         <v>2.233028650283813</v>
       </c>
       <c r="E77" s="4">
-        <v>2.235251188278198</v>
+        <v>2.2352511882781978</v>
       </c>
       <c r="F77" s="4">
         <v>2.232596874237061</v>
@@ -5496,22 +5827,22 @@
         <v>2.222562313079834</v>
       </c>
       <c r="H77" s="4">
-        <v>2.204366207122803</v>
+        <v>2.2043662071228032</v>
       </c>
       <c r="I77" s="4">
-        <v>2.178066968917847</v>
+        <v>2.1780669689178471</v>
       </c>
       <c r="J77" s="4">
         <v>2.154742956161499</v>
       </c>
       <c r="K77" s="4">
-        <v>2.12064790725708</v>
+        <v>2.1206479072570801</v>
       </c>
       <c r="L77" s="4">
-        <v>2.088869094848633</v>
+        <v>2.0888690948486328</v>
       </c>
       <c r="M77" s="4">
-        <v>2.060181379318237</v>
+        <v>2.0601813793182369</v>
       </c>
       <c r="N77" s="4">
         <v>2.040648221969604</v>
@@ -5526,19 +5857,19 @@
         <v>2.00462818145752</v>
       </c>
       <c r="R77" s="4">
-        <v>1.996666669845581</v>
+        <v>1.9966666698455811</v>
       </c>
       <c r="S77" s="4">
-        <v>1.990285158157349</v>
+        <v>1.9902851581573491</v>
       </c>
       <c r="T77" s="4">
-        <v>1.981757164001465</v>
+        <v>1.9817571640014651</v>
       </c>
       <c r="U77" s="4">
-        <v>1.970871448516846</v>
+        <v>1.9708714485168459</v>
       </c>
       <c r="V77" s="4">
-        <v>1.960012912750244</v>
+        <v>1.9600129127502439</v>
       </c>
       <c r="W77" s="4">
         <v>1.949731588363647</v>
@@ -5547,10 +5878,10 @@
         <v>1.939414381980896</v>
       </c>
       <c r="Y77" s="4">
-        <v>1.928048491477966</v>
+        <v>1.9280484914779661</v>
       </c>
       <c r="Z77" s="4">
-        <v>1.918355226516724</v>
+        <v>1.9183552265167241</v>
       </c>
       <c r="AA77" s="4">
         <v>1.911205053329468</v>
@@ -5559,13 +5890,13 @@
         <v>1.90511155128479</v>
       </c>
       <c r="AC77" s="4">
-        <v>1.899880409240723</v>
+        <v>1.8998804092407231</v>
       </c>
       <c r="AD77" s="4">
-        <v>-0.00293267708333278</v>
-      </c>
-    </row>
-    <row r="78" spans="1:30" s="4" customFormat="1">
+        <v>-2.9326770833327802E-3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
         <v>47</v>
       </c>
@@ -5573,19 +5904,19 @@
         <v>100</v>
       </c>
       <c r="C78" s="4">
-        <v>1.381767868995667</v>
+        <v>1.3817678689956669</v>
       </c>
       <c r="D78" s="4">
-        <v>1.315980434417725</v>
+        <v>1.3159804344177251</v>
       </c>
       <c r="E78" s="4">
-        <v>1.293471336364746</v>
+        <v>1.2934713363647461</v>
       </c>
       <c r="F78" s="4">
-        <v>1.298168659210205</v>
+        <v>1.2981686592102051</v>
       </c>
       <c r="G78" s="4">
-        <v>1.305267095565796</v>
+        <v>1.3052670955657959</v>
       </c>
       <c r="H78" s="4">
         <v>1.302135705947876</v>
@@ -5597,16 +5928,16 @@
         <v>1.262501120567322</v>
       </c>
       <c r="K78" s="4">
-        <v>1.223036766052246</v>
+        <v>1.2230367660522461</v>
       </c>
       <c r="L78" s="4">
-        <v>1.199848175048828</v>
+        <v>1.1998481750488279</v>
       </c>
       <c r="M78" s="4">
-        <v>1.178701281547546</v>
+        <v>1.1787012815475459</v>
       </c>
       <c r="N78" s="4">
-        <v>1.166251182556152</v>
+        <v>1.1662511825561519</v>
       </c>
       <c r="O78" s="4">
         <v>1.15410304069519</v>
@@ -5621,16 +5952,16 @@
         <v>1.135944247245789</v>
       </c>
       <c r="S78" s="4">
-        <v>1.144989728927612</v>
+        <v>1.1449897289276121</v>
       </c>
       <c r="T78" s="4">
-        <v>1.155916452407837</v>
+        <v>1.1559164524078369</v>
       </c>
       <c r="U78" s="4">
-        <v>1.163705348968506</v>
+        <v>1.1637053489685061</v>
       </c>
       <c r="V78" s="4">
-        <v>1.175930738449097</v>
+        <v>1.1759307384490969</v>
       </c>
       <c r="W78" s="4">
         <v>1.18646776676178</v>
@@ -5651,13 +5982,13 @@
         <v>1.236522436141968</v>
       </c>
       <c r="AC78" s="4">
-        <v>1.250416994094849</v>
+        <v>1.2504169940948491</v>
       </c>
       <c r="AD78" s="4">
-        <v>-0.003834424089328103</v>
-      </c>
-    </row>
-    <row r="79" spans="1:30" s="4" customFormat="1">
+        <v>-3.834424089328103E-3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>48</v>
       </c>
@@ -5665,91 +5996,91 @@
         <v>101</v>
       </c>
       <c r="C79" s="4">
-        <v>0.4509904384613037</v>
+        <v>0.45099043846130371</v>
       </c>
       <c r="D79" s="4">
-        <v>0.4593534171581268</v>
+        <v>0.45935341715812678</v>
       </c>
       <c r="E79" s="4">
-        <v>0.4608887732028961</v>
+        <v>0.46088877320289612</v>
       </c>
       <c r="F79" s="4">
-        <v>0.4630104303359985</v>
+        <v>0.46301043033599848</v>
       </c>
       <c r="G79" s="4">
-        <v>0.464428037405014</v>
+        <v>0.46442803740501398</v>
       </c>
       <c r="H79" s="4">
-        <v>0.464108794927597</v>
+        <v>0.46410879492759699</v>
       </c>
       <c r="I79" s="4">
-        <v>0.4613516926765442</v>
+        <v>0.46135169267654419</v>
       </c>
       <c r="J79" s="4">
-        <v>0.458838552236557</v>
+        <v>0.45883855223655701</v>
       </c>
       <c r="K79" s="4">
-        <v>0.4531941413879395</v>
+        <v>0.45319414138793951</v>
       </c>
       <c r="L79" s="4">
-        <v>0.4493566453456879</v>
+        <v>0.44935664534568792</v>
       </c>
       <c r="M79" s="4">
-        <v>0.4462472498416901</v>
+        <v>0.44624724984169012</v>
       </c>
       <c r="N79" s="4">
-        <v>0.4450274407863617</v>
+        <v>0.44502744078636169</v>
       </c>
       <c r="O79" s="4">
-        <v>0.4447556138038635</v>
+        <v>0.44475561380386353</v>
       </c>
       <c r="P79" s="4">
         <v>0.4451669454574585</v>
       </c>
       <c r="Q79" s="4">
-        <v>0.4466675519943237</v>
+        <v>0.44666755199432367</v>
       </c>
       <c r="R79" s="4">
-        <v>0.4484928548336029</v>
+        <v>0.44849285483360291</v>
       </c>
       <c r="S79" s="4">
-        <v>0.4511941969394684</v>
+        <v>0.45119419693946838</v>
       </c>
       <c r="T79" s="4">
-        <v>0.45359867811203</v>
+        <v>0.45359867811202997</v>
       </c>
       <c r="U79" s="4">
-        <v>0.4553684294223785</v>
+        <v>0.45536842942237848</v>
       </c>
       <c r="V79" s="4">
-        <v>0.4573229551315308</v>
+        <v>0.45732295513153082</v>
       </c>
       <c r="W79" s="4">
-        <v>0.4593528807163239</v>
+        <v>0.45935288071632391</v>
       </c>
       <c r="X79" s="4">
-        <v>0.4612996578216553</v>
+        <v>0.46129965782165527</v>
       </c>
       <c r="Y79" s="4">
-        <v>0.4629410803318024</v>
+        <v>0.46294108033180242</v>
       </c>
       <c r="Z79" s="4">
-        <v>0.4650076627731323</v>
+        <v>0.46500766277313232</v>
       </c>
       <c r="AA79" s="4">
-        <v>0.4677622616291046</v>
+        <v>0.46776226162910461</v>
       </c>
       <c r="AB79" s="4">
         <v>0.4706273078918457</v>
       </c>
       <c r="AC79" s="4">
-        <v>0.4737320244312286</v>
+        <v>0.47373202443122858</v>
       </c>
       <c r="AD79" s="4">
-        <v>0.001893932536505716</v>
-      </c>
-    </row>
-    <row r="80" spans="1:30" s="4" customFormat="1">
+        <v>1.893932536505716E-3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
         <v>49</v>
       </c>
@@ -5772,10 +6103,10 @@
         <v>1.76417088508606</v>
       </c>
       <c r="H80" s="4">
-        <v>1.76497757434845</v>
+        <v>1.7649775743484499</v>
       </c>
       <c r="I80" s="4">
-        <v>1.736957669258118</v>
+        <v>1.7369576692581179</v>
       </c>
       <c r="J80" s="4">
         <v>1.710152149200439</v>
@@ -5784,7 +6115,7 @@
         <v>1.655019164085388</v>
       </c>
       <c r="L80" s="4">
-        <v>1.623229742050171</v>
+        <v>1.6232297420501709</v>
       </c>
       <c r="M80" s="4">
         <v>1.593754768371582</v>
@@ -5796,7 +6127,7 @@
         <v>1.556903004646301</v>
       </c>
       <c r="P80" s="4">
-        <v>1.538453817367554</v>
+        <v>1.5384538173675539</v>
       </c>
       <c r="Q80" s="4">
         <v>1.529212951660156</v>
@@ -5805,10 +6136,10 @@
         <v>1.523437023162842</v>
       </c>
       <c r="S80" s="4">
-        <v>1.533089637756348</v>
+        <v>1.5330896377563481</v>
       </c>
       <c r="T80" s="4">
-        <v>1.544919729232788</v>
+        <v>1.5449197292327881</v>
       </c>
       <c r="U80" s="4">
         <v>1.552750825881958</v>
@@ -5817,16 +6148,16 @@
         <v>1.565733909606934</v>
       </c>
       <c r="W80" s="4">
-        <v>1.576148271560669</v>
+        <v>1.5761482715606689</v>
       </c>
       <c r="X80" s="4">
         <v>1.585275411605835</v>
       </c>
       <c r="Y80" s="4">
-        <v>1.590868711471558</v>
+        <v>1.5908687114715581</v>
       </c>
       <c r="Z80" s="4">
-        <v>1.598803520202637</v>
+        <v>1.5988035202026369</v>
       </c>
       <c r="AA80" s="4">
         <v>1.611671447753906</v>
@@ -5838,10 +6169,10 @@
         <v>1.635915279388428</v>
       </c>
       <c r="AD80" s="4">
-        <v>-0.003075790139249301</v>
-      </c>
-    </row>
-    <row r="81" spans="1:30" s="4" customFormat="1">
+        <v>-3.075790139249301E-3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>50</v>
       </c>
@@ -5852,88 +6183,88 @@
         <v>0.6016690731048584</v>
       </c>
       <c r="D81" s="4">
-        <v>0.6156383156776428</v>
+        <v>0.61563831567764282</v>
       </c>
       <c r="E81" s="4">
-        <v>0.6188114881515503</v>
+        <v>0.61881148815155029</v>
       </c>
       <c r="F81" s="4">
-        <v>0.6232101321220398</v>
+        <v>0.62321013212203979</v>
       </c>
       <c r="G81" s="4">
-        <v>0.6262723803520203</v>
+        <v>0.62627238035202026</v>
       </c>
       <c r="H81" s="4">
-        <v>0.6270543336868286</v>
+        <v>0.62705433368682861</v>
       </c>
       <c r="I81" s="4">
-        <v>0.6248077154159546</v>
+        <v>0.62480771541595459</v>
       </c>
       <c r="J81" s="4">
-        <v>0.6231804490089417</v>
+        <v>0.62318044900894165</v>
       </c>
       <c r="K81" s="4">
-        <v>0.617694616317749</v>
+        <v>0.61769461631774902</v>
       </c>
       <c r="L81" s="4">
-        <v>0.6143649816513062</v>
+        <v>0.61436498165130615</v>
       </c>
       <c r="M81" s="4">
-        <v>0.6118913888931274</v>
+        <v>0.61189138889312744</v>
       </c>
       <c r="N81" s="4">
-        <v>0.6117541193962097</v>
+        <v>0.61175411939620972</v>
       </c>
       <c r="O81" s="4">
-        <v>0.6128360629081726</v>
+        <v>0.61283606290817261</v>
       </c>
       <c r="P81" s="4">
-        <v>0.6147006750106812</v>
+        <v>0.61470067501068115</v>
       </c>
       <c r="Q81" s="4">
-        <v>0.617802619934082</v>
+        <v>0.61780261993408203</v>
       </c>
       <c r="R81" s="4">
-        <v>0.6211557388305664</v>
+        <v>0.62115573883056641</v>
       </c>
       <c r="S81" s="4">
-        <v>0.6254411935806274</v>
+        <v>0.62544119358062744</v>
       </c>
       <c r="T81" s="4">
-        <v>0.6294042468070984</v>
+        <v>0.62940424680709839</v>
       </c>
       <c r="U81" s="4">
-        <v>0.6325350999832153</v>
+        <v>0.63253509998321533</v>
       </c>
       <c r="V81" s="4">
-        <v>0.6358271241188049</v>
+        <v>0.63582712411880493</v>
       </c>
       <c r="W81" s="4">
-        <v>0.639211118221283</v>
+        <v>0.63921111822128296</v>
       </c>
       <c r="X81" s="4">
-        <v>0.6424427628517151</v>
+        <v>0.64244276285171509</v>
       </c>
       <c r="Y81" s="4">
-        <v>0.6452091932296753</v>
+        <v>0.64520919322967529</v>
       </c>
       <c r="Z81" s="4">
-        <v>0.6485010981559753</v>
+        <v>0.64850109815597534</v>
       </c>
       <c r="AA81" s="4">
-        <v>0.6526703834533691</v>
+        <v>0.65267038345336914</v>
       </c>
       <c r="AB81" s="4">
-        <v>0.6569292545318604</v>
+        <v>0.65692925453186035</v>
       </c>
       <c r="AC81" s="4">
-        <v>0.6614340543746948</v>
+        <v>0.66143405437469482</v>
       </c>
       <c r="AD81" s="4">
-        <v>0.003649053405867519</v>
-      </c>
-    </row>
-    <row r="82" spans="1:30" s="4" customFormat="1">
+        <v>3.649053405867519E-3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
         <v>51</v>
       </c>
@@ -5941,7 +6272,7 @@
         <v>104</v>
       </c>
       <c r="C82" s="4">
-        <v>1.370022535324097</v>
+        <v>1.3700225353240969</v>
       </c>
       <c r="D82" s="4">
         <v>1.318625211715698</v>
@@ -5950,82 +6281,82 @@
         <v>1.26313328742981</v>
       </c>
       <c r="F82" s="4">
-        <v>1.24403715133667</v>
+        <v>1.2440371513366699</v>
       </c>
       <c r="G82" s="4">
-        <v>1.232648849487305</v>
+        <v>1.2326488494873049</v>
       </c>
       <c r="H82" s="4">
-        <v>1.214800596237183</v>
+        <v>1.2148005962371831</v>
       </c>
       <c r="I82" s="4">
         <v>1.164124727249146</v>
       </c>
       <c r="J82" s="4">
-        <v>1.118474721908569</v>
+        <v>1.1184747219085689</v>
       </c>
       <c r="K82" s="4">
-        <v>1.057956695556641</v>
+        <v>1.0579566955566411</v>
       </c>
       <c r="L82" s="4">
         <v>1.0148766040802</v>
       </c>
       <c r="M82" s="4">
-        <v>0.9745126962661743</v>
+        <v>0.97451269626617432</v>
       </c>
       <c r="N82" s="4">
         <v>0.9422033429145813</v>
       </c>
       <c r="O82" s="4">
-        <v>0.9119340777397156</v>
+        <v>0.91193407773971558</v>
       </c>
       <c r="P82" s="4">
-        <v>0.884099543094635</v>
+        <v>0.88409954309463501</v>
       </c>
       <c r="Q82" s="4">
-        <v>0.8634561896324158</v>
+        <v>0.86345618963241577</v>
       </c>
       <c r="R82" s="4">
-        <v>0.8462771773338318</v>
+        <v>0.84627717733383179</v>
       </c>
       <c r="S82" s="4">
-        <v>0.8365006446838379</v>
+        <v>0.83650064468383789</v>
       </c>
       <c r="T82" s="4">
-        <v>0.8297364115715027</v>
+        <v>0.82973641157150269</v>
       </c>
       <c r="U82" s="4">
-        <v>0.8216618895530701</v>
+        <v>0.82166188955307007</v>
       </c>
       <c r="V82" s="4">
-        <v>0.8171981573104858</v>
+        <v>0.81719815731048584</v>
       </c>
       <c r="W82" s="4">
-        <v>0.8120533227920532</v>
+        <v>0.81205332279205322</v>
       </c>
       <c r="X82" s="4">
-        <v>0.8066121339797974</v>
+        <v>0.80661213397979736</v>
       </c>
       <c r="Y82" s="4">
-        <v>0.7993117570877075</v>
+        <v>0.79931175708770752</v>
       </c>
       <c r="Z82" s="4">
         <v>0.7935185432434082</v>
       </c>
       <c r="AA82" s="4">
-        <v>0.7906215190887451</v>
+        <v>0.79062151908874512</v>
       </c>
       <c r="AB82" s="4">
-        <v>0.7872152328491211</v>
+        <v>0.78721523284912109</v>
       </c>
       <c r="AC82" s="4">
-        <v>0.7851930856704712</v>
+        <v>0.78519308567047119</v>
       </c>
       <c r="AD82" s="4">
-        <v>-0.02118216228152647</v>
-      </c>
-    </row>
-    <row r="83" spans="1:30" s="4" customFormat="1">
+        <v>-2.118216228152647E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
         <v>52</v>
       </c>
@@ -6033,91 +6364,91 @@
         <v>105</v>
       </c>
       <c r="C83" s="4">
-        <v>0.8742426633834839</v>
+        <v>0.87424266338348389</v>
       </c>
       <c r="D83" s="4">
-        <v>0.8617833852767944</v>
+        <v>0.86178338527679443</v>
       </c>
       <c r="E83" s="4">
-        <v>0.8343019485473633</v>
+        <v>0.83430194854736328</v>
       </c>
       <c r="F83" s="4">
-        <v>0.8243371248245239</v>
+        <v>0.82433712482452393</v>
       </c>
       <c r="G83" s="4">
-        <v>0.8196806907653809</v>
+        <v>0.81968069076538086</v>
       </c>
       <c r="H83" s="4">
-        <v>0.8124101161956787</v>
+        <v>0.81241011619567871</v>
       </c>
       <c r="I83" s="4">
-        <v>0.7940264344215393</v>
+        <v>0.79402643442153931</v>
       </c>
       <c r="J83" s="4">
         <v>0.777351975440979</v>
       </c>
       <c r="K83" s="4">
-        <v>0.7479749917984009</v>
+        <v>0.74797499179840088</v>
       </c>
       <c r="L83" s="4">
-        <v>0.7301369905471802</v>
+        <v>0.73013699054718018</v>
       </c>
       <c r="M83" s="4">
-        <v>0.7131481170654297</v>
+        <v>0.71314811706542969</v>
       </c>
       <c r="N83" s="4">
-        <v>0.7005931735038757</v>
+        <v>0.70059317350387573</v>
       </c>
       <c r="O83" s="4">
-        <v>0.6874285936355591</v>
+        <v>0.68742859363555908</v>
       </c>
       <c r="P83" s="4">
-        <v>0.6743313074111938</v>
+        <v>0.67433130741119385</v>
       </c>
       <c r="Q83" s="4">
-        <v>0.6654731035232544</v>
+        <v>0.66547310352325439</v>
       </c>
       <c r="R83" s="4">
-        <v>0.6580945253372192</v>
+        <v>0.65809452533721924</v>
       </c>
       <c r="S83" s="4">
-        <v>0.6576344966888428</v>
+        <v>0.65763449668884277</v>
       </c>
       <c r="T83" s="4">
-        <v>0.6588039994239807</v>
+        <v>0.65880399942398071</v>
       </c>
       <c r="U83" s="4">
-        <v>0.6587760448455811</v>
+        <v>0.65877604484558105</v>
       </c>
       <c r="V83" s="4">
         <v>0.6611253023147583</v>
       </c>
       <c r="W83" s="4">
-        <v>0.662487268447876</v>
+        <v>0.66248726844787598</v>
       </c>
       <c r="X83" s="4">
-        <v>0.663245677947998</v>
+        <v>0.66324567794799805</v>
       </c>
       <c r="Y83" s="4">
-        <v>0.6625514626502991</v>
+        <v>0.66255146265029907</v>
       </c>
       <c r="Z83" s="4">
-        <v>0.6625590920448303</v>
+        <v>0.66255909204483032</v>
       </c>
       <c r="AA83" s="4">
-        <v>0.6642586588859558</v>
+        <v>0.66425865888595581</v>
       </c>
       <c r="AB83" s="4">
-        <v>0.664899468421936</v>
+        <v>0.66489946842193604</v>
       </c>
       <c r="AC83" s="4">
-        <v>0.6657007336616516</v>
+        <v>0.66570073366165161</v>
       </c>
       <c r="AD83" s="4">
-        <v>-0.01042671342761226</v>
-      </c>
-    </row>
-    <row r="84" spans="1:30" s="4" customFormat="1">
+        <v>-1.042671342761226E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
         <v>53</v>
       </c>
@@ -6128,46 +6459,46 @@
         <v>0.8116990327835083</v>
       </c>
       <c r="D84" s="4">
-        <v>0.8354686498641968</v>
+        <v>0.83546864986419678</v>
       </c>
       <c r="E84" s="4">
-        <v>0.8447166681289673</v>
+        <v>0.84471666812896729</v>
       </c>
       <c r="F84" s="4">
         <v>0.8695070743560791</v>
       </c>
       <c r="G84" s="4">
-        <v>0.9014438986778259</v>
+        <v>0.90144389867782593</v>
       </c>
       <c r="H84" s="4">
-        <v>0.930741548538208</v>
+        <v>0.93074154853820801</v>
       </c>
       <c r="I84" s="4">
-        <v>0.9500276446342468</v>
+        <v>0.95002764463424683</v>
       </c>
       <c r="J84" s="4">
-        <v>0.9702953696250916</v>
+        <v>0.97029536962509155</v>
       </c>
       <c r="K84" s="4">
-        <v>0.9734845161437988</v>
+        <v>0.97348451614379883</v>
       </c>
       <c r="L84" s="4">
-        <v>0.9908615350723267</v>
+        <v>0.99086153507232666</v>
       </c>
       <c r="M84" s="4">
-        <v>1.008855581283569</v>
+        <v>1.0088555812835689</v>
       </c>
       <c r="N84" s="4">
-        <v>1.032735109329224</v>
+        <v>1.0327351093292241</v>
       </c>
       <c r="O84" s="4">
-        <v>1.055447340011597</v>
+        <v>1.0554473400115969</v>
       </c>
       <c r="P84" s="4">
-        <v>1.079401135444641</v>
+        <v>1.0794011354446409</v>
       </c>
       <c r="Q84" s="4">
-        <v>1.109749674797058</v>
+        <v>1.1097496747970581</v>
       </c>
       <c r="R84" s="4">
         <v>1.143534660339355</v>
@@ -6179,10 +6510,10 @@
         <v>1.243574261665344</v>
       </c>
       <c r="U84" s="4">
-        <v>1.295472025871277</v>
+        <v>1.2954720258712771</v>
       </c>
       <c r="V84" s="4">
-        <v>1.353885650634766</v>
+        <v>1.3538856506347661</v>
       </c>
       <c r="W84" s="4">
         <v>1.413463234901428</v>
@@ -6191,25 +6522,25 @@
         <v>1.473645806312561</v>
       </c>
       <c r="Y84" s="4">
-        <v>1.532554864883423</v>
+        <v>1.5325548648834231</v>
       </c>
       <c r="Z84" s="4">
-        <v>1.596109390258789</v>
+        <v>1.5961093902587891</v>
       </c>
       <c r="AA84" s="4">
         <v>1.665758490562439</v>
       </c>
       <c r="AB84" s="4">
-        <v>1.733383655548096</v>
+        <v>1.7333836555480959</v>
       </c>
       <c r="AC84" s="4">
         <v>1.804801225662231</v>
       </c>
       <c r="AD84" s="4">
-        <v>0.03121085262520773</v>
-      </c>
-    </row>
-    <row r="85" spans="1:30" s="4" customFormat="1">
+        <v>3.121085262520773E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
         <v>54</v>
       </c>
@@ -6220,88 +6551,88 @@
         <v>0.1028999164700508</v>
       </c>
       <c r="D85" s="4">
-        <v>0.101241871714592</v>
+        <v>0.10124187171459199</v>
       </c>
       <c r="E85" s="4">
-        <v>0.09793837368488312</v>
+        <v>9.7938373684883118E-2</v>
       </c>
       <c r="F85" s="4">
-        <v>0.09663639962673187</v>
+        <v>9.6636399626731873E-2</v>
       </c>
       <c r="G85" s="4">
-        <v>0.09622509777545929</v>
+        <v>9.622509777545929E-2</v>
       </c>
       <c r="H85" s="4">
-        <v>0.09557227045297623</v>
+        <v>9.5572270452976227E-2</v>
       </c>
       <c r="I85" s="4">
-        <v>0.09389549493789673</v>
+        <v>9.3895494937896729E-2</v>
       </c>
       <c r="J85" s="4">
-        <v>0.09237399697303772</v>
+        <v>9.237399697303772E-2</v>
       </c>
       <c r="K85" s="4">
-        <v>0.08923168480396271</v>
+        <v>8.9231684803962708E-2</v>
       </c>
       <c r="L85" s="4">
-        <v>0.08751010894775391</v>
+        <v>8.7510108947753906E-2</v>
       </c>
       <c r="M85" s="4">
-        <v>0.08590701222419739</v>
+        <v>8.5907012224197388E-2</v>
       </c>
       <c r="N85" s="4">
-        <v>0.08474859595298767</v>
+        <v>8.4748595952987671E-2</v>
       </c>
       <c r="O85" s="4">
-        <v>0.08343012630939484</v>
+        <v>8.3430126309394836E-2</v>
       </c>
       <c r="P85" s="4">
-        <v>0.08207693696022034</v>
+        <v>8.2076936960220337E-2</v>
       </c>
       <c r="Q85" s="4">
-        <v>0.08111187070608139</v>
+        <v>8.111187070608139E-2</v>
       </c>
       <c r="R85" s="4">
-        <v>0.08030156791210175</v>
+        <v>8.0301567912101746E-2</v>
       </c>
       <c r="S85" s="4">
-        <v>0.08022940158843994</v>
+        <v>8.0229401588439941E-2</v>
       </c>
       <c r="T85" s="4">
-        <v>0.08008626103401184</v>
+        <v>8.0086261034011841E-2</v>
       </c>
       <c r="U85" s="4">
-        <v>0.07970237731933594</v>
+        <v>7.9702377319335938E-2</v>
       </c>
       <c r="V85" s="4">
-        <v>0.0794990137219429</v>
+        <v>7.9499013721942902E-2</v>
       </c>
       <c r="W85" s="4">
-        <v>0.078963503241539</v>
+        <v>7.8963503241539001E-2</v>
       </c>
       <c r="X85" s="4">
-        <v>0.07803448289632797</v>
+        <v>7.8034482896327972E-2</v>
       </c>
       <c r="Y85" s="4">
-        <v>0.07682498544454575</v>
+        <v>7.6824985444545746E-2</v>
       </c>
       <c r="Z85" s="4">
-        <v>0.07537162303924561</v>
+        <v>7.5371623039245605E-2</v>
       </c>
       <c r="AA85" s="4">
-        <v>0.07377565652132034</v>
+        <v>7.3775656521320343E-2</v>
       </c>
       <c r="AB85" s="4">
-        <v>0.07182112336158752</v>
+        <v>7.1821123361587524E-2</v>
       </c>
       <c r="AC85" s="4">
-        <v>0.06954126060009003</v>
+        <v>6.9541260600090027E-2</v>
       </c>
       <c r="AD85" s="4">
-        <v>-0.01495764385851095</v>
-      </c>
-    </row>
-    <row r="86" spans="1:30" s="4" customFormat="1">
+        <v>-1.4957643858510949E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
         <v>55</v>
       </c>
@@ -6309,91 +6640,91 @@
         <v>122</v>
       </c>
       <c r="C86" s="4">
-        <v>6.771921157836914</v>
+        <v>6.7719211578369141</v>
       </c>
       <c r="D86" s="4">
-        <v>6.883794784545898</v>
+        <v>6.8837947845458984</v>
       </c>
       <c r="E86" s="4">
-        <v>6.566432952880859</v>
+        <v>6.5664329528808594</v>
       </c>
       <c r="F86" s="4">
-        <v>6.45119047164917</v>
+        <v>6.4511904716491699</v>
       </c>
       <c r="G86" s="4">
-        <v>6.360617160797119</v>
+        <v>6.3606171607971191</v>
       </c>
       <c r="H86" s="4">
-        <v>6.387406349182129</v>
+        <v>6.3874063491821289</v>
       </c>
       <c r="I86" s="4">
-        <v>6.365468978881836</v>
+        <v>6.3654689788818359</v>
       </c>
       <c r="J86" s="4">
-        <v>6.345403671264648</v>
+        <v>6.3454036712646484</v>
       </c>
       <c r="K86" s="4">
-        <v>6.249764442443848</v>
+        <v>6.2497644424438477</v>
       </c>
       <c r="L86" s="4">
-        <v>6.209431171417236</v>
+        <v>6.2094311714172363</v>
       </c>
       <c r="M86" s="4">
-        <v>6.172143936157227</v>
+        <v>6.1721439361572266</v>
       </c>
       <c r="N86" s="4">
-        <v>6.158044815063477</v>
+        <v>6.1580448150634766</v>
       </c>
       <c r="O86" s="4">
-        <v>6.140436172485352</v>
+        <v>6.1404361724853516</v>
       </c>
       <c r="P86" s="4">
-        <v>6.123429298400879</v>
+        <v>6.1234292984008789</v>
       </c>
       <c r="Q86" s="4">
-        <v>6.130517959594727</v>
+        <v>6.1305179595947266</v>
       </c>
       <c r="R86" s="4">
         <v>6.146367073059082</v>
       </c>
       <c r="S86" s="4">
-        <v>6.200616836547852</v>
+        <v>6.2006168365478516</v>
       </c>
       <c r="T86" s="4">
-        <v>6.259859085083008</v>
+        <v>6.2598590850830078</v>
       </c>
       <c r="U86" s="4">
-        <v>6.3134446144104</v>
+        <v>6.3134446144104004</v>
       </c>
       <c r="V86" s="4">
-        <v>6.381604194641113</v>
+        <v>6.3816041946411133</v>
       </c>
       <c r="W86" s="4">
-        <v>6.446488380432129</v>
+        <v>6.4464883804321289</v>
       </c>
       <c r="X86" s="4">
-        <v>6.509508609771729</v>
+        <v>6.5095086097717294</v>
       </c>
       <c r="Y86" s="4">
-        <v>6.564247608184814</v>
+        <v>6.5642476081848136</v>
       </c>
       <c r="Z86" s="4">
-        <v>6.624691009521484</v>
+        <v>6.6246910095214844</v>
       </c>
       <c r="AA86" s="4">
-        <v>6.698431968688965</v>
+        <v>6.6984319686889648</v>
       </c>
       <c r="AB86" s="4">
-        <v>6.767246246337891</v>
+        <v>6.7672462463378906</v>
       </c>
       <c r="AC86" s="4">
-        <v>6.83887243270874</v>
+        <v>6.8388724327087402</v>
       </c>
       <c r="AD86" s="4">
-        <v>0.0003784580278678451</v>
-      </c>
-    </row>
-    <row r="87" spans="1:30" s="6" customFormat="1">
+        <v>3.784580278678451E-4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:30" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A87" s="6" t="s">
         <v>56</v>
       </c>
@@ -6401,13 +6732,13 @@
         <v>129</v>
       </c>
       <c r="C87" s="6">
-        <v>16.18818664550781</v>
+        <v>16.188186645507809</v>
       </c>
       <c r="D87" s="6">
-        <v>16.39358139038086</v>
+        <v>16.393581390380859</v>
       </c>
       <c r="E87" s="6">
-        <v>15.95456981658936</v>
+        <v>15.954569816589361</v>
       </c>
       <c r="F87" s="6">
         <v>15.85269165039062</v>
@@ -6416,19 +6747,19 @@
         <v>15.79331588745117</v>
       </c>
       <c r="H87" s="6">
-        <v>15.80357360839844</v>
+        <v>15.803573608398439</v>
       </c>
       <c r="I87" s="6">
         <v>15.6505126953125</v>
       </c>
       <c r="J87" s="6">
-        <v>15.51331424713135</v>
+        <v>15.513314247131349</v>
       </c>
       <c r="K87" s="6">
-        <v>15.18800449371338</v>
+        <v>15.188004493713381</v>
       </c>
       <c r="L87" s="6">
-        <v>15.00848579406738</v>
+        <v>15.008485794067379</v>
       </c>
       <c r="M87" s="6">
         <v>14.84534358978271</v>
@@ -6446,7 +6777,7 @@
         <v>14.58643245697021</v>
       </c>
       <c r="R87" s="6">
-        <v>14.60027122497559</v>
+        <v>14.600271224975589</v>
       </c>
       <c r="S87" s="6">
         <v>14.71122455596924</v>
@@ -6461,13 +6792,13 @@
         <v>15.0881404876709</v>
       </c>
       <c r="W87" s="6">
-        <v>15.22436714172363</v>
+        <v>15.224367141723629</v>
       </c>
       <c r="X87" s="6">
         <v>15.35538291931152</v>
       </c>
       <c r="Y87" s="6">
-        <v>15.46533393859863</v>
+        <v>15.465333938598629</v>
       </c>
       <c r="Z87" s="6">
         <v>15.59442234039307</v>
@@ -6482,10 +6813,10 @@
         <v>16.08548736572266</v>
       </c>
       <c r="AD87" s="6">
-        <v>-0.0002447507048628506</v>
-      </c>
-    </row>
-    <row r="88" spans="1:30" s="4" customFormat="1">
+        <v>-2.4475070486285061E-4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
         <v>57</v>
       </c>
@@ -6493,16 +6824,16 @@
         <v>124</v>
       </c>
       <c r="C88" s="4">
-        <v>0.04543042927980423</v>
+        <v>4.543042927980423E-2</v>
       </c>
       <c r="D88" s="4">
-        <v>0.06696092337369919</v>
+        <v>6.6960923373699188E-2</v>
       </c>
       <c r="E88" s="4">
-        <v>0.09693847596645355</v>
+        <v>9.6938475966453552E-2</v>
       </c>
       <c r="F88" s="4">
-        <v>0.1385090351104736</v>
+        <v>0.13850903511047361</v>
       </c>
       <c r="G88" s="4">
         <v>0.1909919083118439</v>
@@ -6511,22 +6842,22 @@
         <v>0.2553565502166748</v>
       </c>
       <c r="I88" s="4">
-        <v>0.3394973278045654</v>
+        <v>0.33949732780456537</v>
       </c>
       <c r="J88" s="4">
-        <v>0.4432904124259949</v>
+        <v>0.44329041242599487</v>
       </c>
       <c r="K88" s="4">
-        <v>0.5670366883277893</v>
+        <v>0.56703668832778931</v>
       </c>
       <c r="L88" s="4">
-        <v>0.6991167068481445</v>
+        <v>0.69911670684814453</v>
       </c>
       <c r="M88" s="4">
-        <v>0.8206353783607483</v>
+        <v>0.82063537836074829</v>
       </c>
       <c r="N88" s="4">
-        <v>0.9340236783027649</v>
+        <v>0.93402367830276489</v>
       </c>
       <c r="O88" s="4">
         <v>1.032479882240295</v>
@@ -6538,46 +6869,46 @@
         <v>1.199915289878845</v>
       </c>
       <c r="R88" s="4">
-        <v>1.272947669029236</v>
+        <v>1.2729476690292361</v>
       </c>
       <c r="S88" s="4">
         <v>1.350948572158813</v>
       </c>
       <c r="T88" s="4">
-        <v>1.423437476158142</v>
+        <v>1.4234374761581421</v>
       </c>
       <c r="U88" s="4">
-        <v>1.485883712768555</v>
+        <v>1.4858837127685549</v>
       </c>
       <c r="V88" s="4">
-        <v>1.545037746429443</v>
+        <v>1.5450377464294429</v>
       </c>
       <c r="W88" s="4">
         <v>1.593925952911377</v>
       </c>
       <c r="X88" s="4">
-        <v>1.635340929031372</v>
+        <v>1.6353409290313721</v>
       </c>
       <c r="Y88" s="4">
         <v>1.66617751121521</v>
       </c>
       <c r="Z88" s="4">
-        <v>1.6948561668396</v>
+        <v>1.6948561668396001</v>
       </c>
       <c r="AA88" s="4">
         <v>1.722869753837585</v>
       </c>
       <c r="AB88" s="4">
-        <v>1.743607997894287</v>
+        <v>1.7436079978942871</v>
       </c>
       <c r="AC88" s="4">
         <v>1.761550188064575</v>
       </c>
       <c r="AD88" s="4">
-        <v>0.1510601186019156</v>
-      </c>
-    </row>
-    <row r="89" spans="1:30" s="4" customFormat="1">
+        <v>0.15106011860191559</v>
+      </c>
+    </row>
+    <row r="89" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
         <v>58</v>
       </c>
@@ -6588,22 +6919,22 @@
         <v>0.1417428404092789</v>
       </c>
       <c r="D89" s="4">
-        <v>0.1586653888225555</v>
+        <v>0.15866538882255549</v>
       </c>
       <c r="E89" s="4">
-        <v>0.1751562505960464</v>
+        <v>0.17515625059604639</v>
       </c>
       <c r="F89" s="4">
-        <v>0.1821672022342682</v>
+        <v>0.18216720223426819</v>
       </c>
       <c r="G89" s="4">
-        <v>0.1895016580820084</v>
+        <v>0.18950165808200839</v>
       </c>
       <c r="H89" s="4">
-        <v>0.1993240267038345</v>
+        <v>0.19932402670383451</v>
       </c>
       <c r="I89" s="4">
-        <v>0.2111417055130005</v>
+        <v>0.21114170551300049</v>
       </c>
       <c r="J89" s="4">
         <v>0.2262821048498154</v>
@@ -6612,64 +6943,64 @@
         <v>0.2380215525627136</v>
       </c>
       <c r="L89" s="4">
-        <v>0.2538630664348602</v>
+        <v>0.25386306643486017</v>
       </c>
       <c r="M89" s="4">
-        <v>0.2636756598949432</v>
+        <v>0.26367565989494318</v>
       </c>
       <c r="N89" s="4">
-        <v>0.2719502449035645</v>
+        <v>0.27195024490356451</v>
       </c>
       <c r="O89" s="4">
-        <v>0.2785964906215668</v>
+        <v>0.27859649062156677</v>
       </c>
       <c r="P89" s="4">
         <v>0.2867908775806427</v>
       </c>
       <c r="Q89" s="4">
-        <v>0.2923144996166229</v>
+        <v>0.29231449961662292</v>
       </c>
       <c r="R89" s="4">
-        <v>0.2951976954936981</v>
+        <v>0.29519769549369812</v>
       </c>
       <c r="S89" s="4">
-        <v>0.3008307218551636</v>
+        <v>0.30083072185516357</v>
       </c>
       <c r="T89" s="4">
-        <v>0.3085992038249969</v>
+        <v>0.30859920382499689</v>
       </c>
       <c r="U89" s="4">
-        <v>0.317820280790329</v>
+        <v>0.31782028079032898</v>
       </c>
       <c r="V89" s="4">
-        <v>0.3278141021728516</v>
+        <v>0.32781410217285162</v>
       </c>
       <c r="W89" s="4">
-        <v>0.3383373320102692</v>
+        <v>0.33833733201026922</v>
       </c>
       <c r="X89" s="4">
-        <v>0.3482779562473297</v>
+        <v>0.34827795624732971</v>
       </c>
       <c r="Y89" s="4">
         <v>0.35950967669487</v>
       </c>
       <c r="Z89" s="4">
-        <v>0.3691576421260834</v>
+        <v>0.36915764212608337</v>
       </c>
       <c r="AA89" s="4">
-        <v>0.3785410821437836</v>
+        <v>0.37854108214378362</v>
       </c>
       <c r="AB89" s="4">
-        <v>0.3858913481235504</v>
+        <v>0.38589134812355042</v>
       </c>
       <c r="AC89" s="4">
-        <v>0.392189234495163</v>
+        <v>0.39218923449516302</v>
       </c>
       <c r="AD89" s="4">
-        <v>0.03991966268814529</v>
-      </c>
-    </row>
-    <row r="90" spans="1:30" s="6" customFormat="1">
+        <v>3.9919662688145292E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:30" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A90" s="6" t="s">
         <v>59</v>
       </c>
@@ -6677,13 +7008,13 @@
         <v>130</v>
       </c>
       <c r="C90" s="6">
-        <v>16.09187507629395</v>
+        <v>16.091875076293949</v>
       </c>
       <c r="D90" s="6">
-        <v>16.30187797546387</v>
+        <v>16.301877975463871</v>
       </c>
       <c r="E90" s="6">
-        <v>15.87635135650635</v>
+        <v>15.876351356506349</v>
       </c>
       <c r="F90" s="6">
         <v>15.80903339385986</v>
@@ -6701,22 +7032,22 @@
         <v>15.73032283782959</v>
       </c>
       <c r="K90" s="6">
-        <v>15.51701927185059</v>
+        <v>15.517019271850589</v>
       </c>
       <c r="L90" s="6">
-        <v>15.45373916625977</v>
+        <v>15.453739166259769</v>
       </c>
       <c r="M90" s="6">
-        <v>15.40230369567871</v>
+        <v>15.402303695678709</v>
       </c>
       <c r="N90" s="6">
-        <v>15.41930389404297</v>
+        <v>15.419303894042971</v>
       </c>
       <c r="O90" s="6">
         <v>15.42672920227051</v>
       </c>
       <c r="P90" s="6">
-        <v>15.42961692810059</v>
+        <v>15.429616928100589</v>
       </c>
       <c r="Q90" s="6">
         <v>15.49403285980225</v>
@@ -6725,7 +7056,7 @@
         <v>15.57802104949951</v>
       </c>
       <c r="S90" s="6">
-        <v>15.76134300231934</v>
+        <v>15.761343002319339</v>
       </c>
       <c r="T90" s="6">
         <v>15.95249557495117</v>
@@ -6734,40 +7065,40 @@
         <v>16.11235237121582</v>
       </c>
       <c r="V90" s="6">
-        <v>16.30536460876465</v>
+        <v>16.305364608764648</v>
       </c>
       <c r="W90" s="6">
         <v>16.47995567321777</v>
       </c>
       <c r="X90" s="6">
-        <v>16.64244651794434</v>
+        <v>16.642446517944339</v>
       </c>
       <c r="Y90" s="6">
-        <v>16.77200126647949</v>
+        <v>16.772001266479489</v>
       </c>
       <c r="Z90" s="6">
-        <v>16.92012023925781</v>
+        <v>16.920120239257809</v>
       </c>
       <c r="AA90" s="6">
-        <v>17.1047420501709</v>
+        <v>17.104742050170898</v>
       </c>
       <c r="AB90" s="6">
         <v>17.27451133728027</v>
       </c>
       <c r="AC90" s="6">
-        <v>17.45484924316406</v>
+        <v>17.454849243164059</v>
       </c>
       <c r="AD90" s="6">
-        <v>0.003131933235377193</v>
-      </c>
-    </row>
-    <row r="91" spans="1:30" s="4" customFormat="1"/>
-    <row r="92" spans="1:30" s="6" customFormat="1">
+        <v>3.1319332353771929E-3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="92" spans="1:30" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B92" s="6" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="93" spans="1:30" s="4" customFormat="1">
+    <row r="93" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
         <v>60</v>
       </c>
@@ -6775,91 +7106,91 @@
         <v>132</v>
       </c>
       <c r="C93" s="4">
-        <v>0.06597012281417847</v>
+        <v>6.5970122814178467E-2</v>
       </c>
       <c r="D93" s="4">
-        <v>0.06352324783802032</v>
+        <v>6.3523247838020325E-2</v>
       </c>
       <c r="E93" s="4">
-        <v>0.06351419538259506</v>
+        <v>6.3514195382595062E-2</v>
       </c>
       <c r="F93" s="4">
-        <v>0.06252173334360123</v>
+        <v>6.2521733343601227E-2</v>
       </c>
       <c r="G93" s="4">
-        <v>0.06195297464728355</v>
+        <v>6.1952974647283547E-2</v>
       </c>
       <c r="H93" s="4">
-        <v>0.06150408089160919</v>
+        <v>6.1504080891609192E-2</v>
       </c>
       <c r="I93" s="4">
-        <v>0.06157387048006058</v>
+        <v>6.1573870480060577E-2</v>
       </c>
       <c r="J93" s="4">
-        <v>0.06102314218878746</v>
+        <v>6.102314218878746E-2</v>
       </c>
       <c r="K93" s="4">
-        <v>0.06068139895796776</v>
+        <v>6.0681398957967758E-2</v>
       </c>
       <c r="L93" s="4">
-        <v>0.05831166729331017</v>
+        <v>5.8311667293310172E-2</v>
       </c>
       <c r="M93" s="4">
-        <v>0.05820932984352112</v>
+        <v>5.8209329843521118E-2</v>
       </c>
       <c r="N93" s="4">
-        <v>0.05819565430283546</v>
+        <v>5.8195654302835458E-2</v>
       </c>
       <c r="O93" s="4">
-        <v>0.05814528837800026</v>
+        <v>5.8145288378000259E-2</v>
       </c>
       <c r="P93" s="4">
-        <v>0.05800811201334</v>
+        <v>5.8008112013340003E-2</v>
       </c>
       <c r="Q93" s="4">
-        <v>0.05785718932747841</v>
+        <v>5.7857189327478409E-2</v>
       </c>
       <c r="R93" s="4">
-        <v>0.05789716169238091</v>
+        <v>5.7897161692380912E-2</v>
       </c>
       <c r="S93" s="4">
-        <v>0.05640879273414612</v>
+        <v>5.6408792734146118E-2</v>
       </c>
       <c r="T93" s="4">
-        <v>0.05651281401515007</v>
+        <v>5.651281401515007E-2</v>
       </c>
       <c r="U93" s="4">
-        <v>0.05655308067798615</v>
+        <v>5.6553080677986152E-2</v>
       </c>
       <c r="V93" s="4">
-        <v>0.05667461454868317</v>
+        <v>5.6674614548683173E-2</v>
       </c>
       <c r="W93" s="4">
-        <v>0.05672367662191391</v>
+        <v>5.672367662191391E-2</v>
       </c>
       <c r="X93" s="4">
-        <v>0.05665647983551025</v>
+        <v>5.6656479835510247E-2</v>
       </c>
       <c r="Y93" s="4">
-        <v>0.05685508996248245</v>
+        <v>5.6855089962482452E-2</v>
       </c>
       <c r="Z93" s="4">
-        <v>0.05664582177996635</v>
+        <v>5.6645821779966347E-2</v>
       </c>
       <c r="AA93" s="4">
-        <v>0.05637205019593239</v>
+        <v>5.6372050195932388E-2</v>
       </c>
       <c r="AB93" s="4">
-        <v>0.05636471137404442</v>
+        <v>5.6364711374044418E-2</v>
       </c>
       <c r="AC93" s="4">
-        <v>0.05628681555390358</v>
+        <v>5.628681555390358E-2</v>
       </c>
       <c r="AD93" s="4">
-        <v>-0.006086846906344423</v>
-      </c>
-    </row>
-    <row r="94" spans="1:30" s="4" customFormat="1">
+        <v>-6.086846906344423E-3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
         <v>61</v>
       </c>
@@ -6870,88 +7201,88 @@
         <v>0.1396878510713577</v>
       </c>
       <c r="D94" s="4">
-        <v>0.1565688252449036</v>
+        <v>0.15656882524490359</v>
       </c>
       <c r="E94" s="4">
-        <v>0.1730439513921738</v>
+        <v>0.17304395139217379</v>
       </c>
       <c r="F94" s="4">
-        <v>0.1800356805324554</v>
+        <v>0.18003568053245539</v>
       </c>
       <c r="G94" s="4">
-        <v>0.1873117089271545</v>
+        <v>0.18731170892715451</v>
       </c>
       <c r="H94" s="4">
-        <v>0.197086289525032</v>
+        <v>0.19708628952503199</v>
       </c>
       <c r="I94" s="4">
-        <v>0.2088402211666107</v>
+        <v>0.20884022116661069</v>
       </c>
       <c r="J94" s="4">
         <v>0.2239131033420563</v>
       </c>
       <c r="K94" s="4">
-        <v>0.2356197685003281</v>
+        <v>0.23561976850032809</v>
       </c>
       <c r="L94" s="4">
-        <v>0.2513954937458038</v>
+        <v>0.25139549374580378</v>
       </c>
       <c r="M94" s="4">
         <v>0.2611687183380127</v>
       </c>
       <c r="N94" s="4">
-        <v>0.269414484500885</v>
+        <v>0.26941448450088501</v>
       </c>
       <c r="O94" s="4">
-        <v>0.276037722826004</v>
+        <v>0.27603772282600397</v>
       </c>
       <c r="P94" s="4">
-        <v>0.284198671579361</v>
+        <v>0.28419867157936102</v>
       </c>
       <c r="Q94" s="4">
-        <v>0.2896981835365295</v>
+        <v>0.28969818353652949</v>
       </c>
       <c r="R94" s="4">
-        <v>0.2925624251365662</v>
+        <v>0.29256242513656622</v>
       </c>
       <c r="S94" s="4">
-        <v>0.2981704771518707</v>
+        <v>0.29817047715187073</v>
       </c>
       <c r="T94" s="4">
-        <v>0.3059065341949463</v>
+        <v>0.30590653419494629</v>
       </c>
       <c r="U94" s="4">
-        <v>0.3150871694087982</v>
+        <v>0.31508716940879822</v>
       </c>
       <c r="V94" s="4">
-        <v>0.3250430822372437</v>
+        <v>0.32504308223724371</v>
       </c>
       <c r="W94" s="4">
-        <v>0.3355275094509125</v>
+        <v>0.33552750945091248</v>
       </c>
       <c r="X94" s="4">
-        <v>0.3454340994358063</v>
+        <v>0.34543409943580627</v>
       </c>
       <c r="Y94" s="4">
-        <v>0.3566293120384216</v>
+        <v>0.35662931203842158</v>
       </c>
       <c r="Z94" s="4">
-        <v>0.366237998008728</v>
+        <v>0.36623799800872803</v>
       </c>
       <c r="AA94" s="4">
-        <v>0.3755843043327332</v>
+        <v>0.37558430433273321</v>
       </c>
       <c r="AB94" s="4">
-        <v>0.3828980922698975</v>
+        <v>0.38289809226989752</v>
       </c>
       <c r="AC94" s="4">
-        <v>0.3891643285751343</v>
+        <v>0.38916432857513428</v>
       </c>
       <c r="AD94" s="4">
-        <v>0.04019413223106505</v>
-      </c>
-    </row>
-    <row r="95" spans="1:30" s="4" customFormat="1">
+        <v>4.019413223106505E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
         <v>62</v>
       </c>
@@ -6959,91 +7290,91 @@
         <v>134</v>
       </c>
       <c r="C95" s="4">
-        <v>0.002528851618990302</v>
+        <v>2.5288516189903021E-3</v>
       </c>
       <c r="D95" s="4">
-        <v>0.002531286329030991</v>
+        <v>2.531286329030991E-3</v>
       </c>
       <c r="E95" s="4">
-        <v>0.002530505647882819</v>
+        <v>2.5305056478828192E-3</v>
       </c>
       <c r="F95" s="4">
-        <v>0.002529725665226579</v>
+        <v>2.5297256652265791E-3</v>
       </c>
       <c r="G95" s="4">
-        <v>0.002530339639633894</v>
+        <v>2.530339639633894E-3</v>
       </c>
       <c r="H95" s="4">
-        <v>0.002535966224968433</v>
+        <v>2.5359662249684329E-3</v>
       </c>
       <c r="I95" s="4">
-        <v>0.002541089663282037</v>
+        <v>2.5410896632820372E-3</v>
       </c>
       <c r="J95" s="4">
-        <v>0.002547831973060966</v>
+        <v>2.547831973060966E-3</v>
       </c>
       <c r="K95" s="4">
-        <v>0.002557637635618448</v>
+        <v>2.5576376356184478E-3</v>
       </c>
       <c r="L95" s="4">
-        <v>0.002566559007391334</v>
+        <v>2.566559007391334E-3</v>
       </c>
       <c r="M95" s="4">
-        <v>0.002571835415437818</v>
+        <v>2.571835415437818E-3</v>
       </c>
       <c r="N95" s="4">
-        <v>0.002572638215497136</v>
+        <v>2.5726382154971361E-3</v>
       </c>
       <c r="O95" s="4">
-        <v>0.002573024015873671</v>
+        <v>2.573024015873671E-3</v>
       </c>
       <c r="P95" s="4">
-        <v>0.002573650563135743</v>
+        <v>2.5736505631357431E-3</v>
       </c>
       <c r="Q95" s="4">
-        <v>0.002574122045189142</v>
+        <v>2.5741220451891418E-3</v>
       </c>
       <c r="R95" s="4">
-        <v>0.002575420774519444</v>
+        <v>2.5754207745194439E-3</v>
       </c>
       <c r="S95" s="4">
-        <v>0.002577264327555895</v>
+        <v>2.5772643275558949E-3</v>
       </c>
       <c r="T95" s="4">
-        <v>0.002581770066171885</v>
+        <v>2.581770066171885E-3</v>
       </c>
       <c r="U95" s="4">
-        <v>0.002586258575320244</v>
+        <v>2.5862585753202438E-3</v>
       </c>
       <c r="V95" s="4">
-        <v>0.002590297488495708</v>
+        <v>2.5902974884957079E-3</v>
       </c>
       <c r="W95" s="4">
-        <v>0.002593752695247531</v>
+        <v>2.5937526952475309E-3</v>
       </c>
       <c r="X95" s="4">
-        <v>0.002597220474854112</v>
+        <v>2.5972204748541121E-3</v>
       </c>
       <c r="Y95" s="4">
-        <v>0.002602219581604004</v>
+        <v>2.6022195816040039E-3</v>
       </c>
       <c r="Z95" s="4">
-        <v>0.002606636844575405</v>
+        <v>2.6066368445754051E-3</v>
       </c>
       <c r="AA95" s="4">
-        <v>0.002609838265925646</v>
+        <v>2.6098382659256458E-3</v>
       </c>
       <c r="AB95" s="4">
-        <v>0.00261105177924037</v>
+        <v>2.6110517792403698E-3</v>
       </c>
       <c r="AC95" s="4">
-        <v>0.002612212672829628</v>
+        <v>2.612212672829628E-3</v>
       </c>
       <c r="AD95" s="4">
-        <v>0.001248175839057675</v>
-      </c>
-    </row>
-    <row r="96" spans="1:30" s="6" customFormat="1">
+        <v>1.2481758390576749E-3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:30" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A96" s="6" t="s">
         <v>63</v>
       </c>
@@ -7051,97 +7382,97 @@
         <v>135</v>
       </c>
       <c r="C96" s="6">
-        <v>0.2081868201494217</v>
+        <v>0.20818682014942169</v>
       </c>
       <c r="D96" s="6">
-        <v>0.2226233631372452</v>
+        <v>0.22262336313724521</v>
       </c>
       <c r="E96" s="6">
-        <v>0.2390886396169662</v>
+        <v>0.23908863961696619</v>
       </c>
       <c r="F96" s="6">
-        <v>0.245087131857872</v>
+        <v>0.24508713185787201</v>
       </c>
       <c r="G96" s="6">
-        <v>0.2517950236797333</v>
+        <v>0.25179502367973328</v>
       </c>
       <c r="H96" s="6">
-        <v>0.2611263394355774</v>
+        <v>0.26112633943557739</v>
       </c>
       <c r="I96" s="6">
-        <v>0.2729551792144775</v>
+        <v>0.27295517921447748</v>
       </c>
       <c r="J96" s="6">
-        <v>0.2874840795993805</v>
+        <v>0.28748407959938049</v>
       </c>
       <c r="K96" s="6">
-        <v>0.2988587915897369</v>
+        <v>0.29885879158973688</v>
       </c>
       <c r="L96" s="6">
-        <v>0.3122737109661102</v>
+        <v>0.31227371096611017</v>
       </c>
       <c r="M96" s="6">
-        <v>0.3219498693943024</v>
+        <v>0.32194986939430242</v>
       </c>
       <c r="N96" s="6">
         <v>0.3301827609539032</v>
       </c>
       <c r="O96" s="6">
-        <v>0.3367560207843781</v>
+        <v>0.33675602078437811</v>
       </c>
       <c r="P96" s="6">
-        <v>0.3447804152965546</v>
+        <v>0.34478041529655462</v>
       </c>
       <c r="Q96" s="6">
-        <v>0.3501294851303101</v>
+        <v>0.35012948513031011</v>
       </c>
       <c r="R96" s="6">
-        <v>0.3530350029468536</v>
+        <v>0.35303500294685358</v>
       </c>
       <c r="S96" s="6">
-        <v>0.3571565449237823</v>
+        <v>0.35715654492378229</v>
       </c>
       <c r="T96" s="6">
-        <v>0.3650011122226715</v>
+        <v>0.36500111222267151</v>
       </c>
       <c r="U96" s="6">
-        <v>0.3742265105247498</v>
+        <v>0.37422651052474981</v>
       </c>
       <c r="V96" s="6">
-        <v>0.3843079805374146</v>
+        <v>0.38430798053741461</v>
       </c>
       <c r="W96" s="6">
-        <v>0.3948449492454529</v>
+        <v>0.39484494924545288</v>
       </c>
       <c r="X96" s="6">
         <v>0.4046877920627594</v>
       </c>
       <c r="Y96" s="6">
-        <v>0.4160866141319275</v>
+        <v>0.41608661413192749</v>
       </c>
       <c r="Z96" s="6">
-        <v>0.4254904389381409</v>
+        <v>0.42549043893814092</v>
       </c>
       <c r="AA96" s="6">
         <v>0.4345661997795105</v>
       </c>
       <c r="AB96" s="6">
-        <v>0.4418738484382629</v>
+        <v>0.44187384843826288</v>
       </c>
       <c r="AC96" s="6">
-        <v>0.4480633437633514</v>
+        <v>0.44806334376335138</v>
       </c>
       <c r="AD96" s="6">
-        <v>0.02991958018855811</v>
-      </c>
-    </row>
-    <row r="97" spans="1:30" s="4" customFormat="1"/>
-    <row r="98" spans="1:30" s="6" customFormat="1">
+        <v>2.9919580188558111E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="98" spans="1:30" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B98" s="6" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="99" spans="1:30" s="2" customFormat="1">
+    <row r="99" spans="1:30" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>64</v>
       </c>
@@ -7230,10 +7561,10 @@
         <v>5348</v>
       </c>
       <c r="AD99" s="2">
-        <v>-0.002062991400027858</v>
-      </c>
-    </row>
-    <row r="100" spans="1:30" s="2" customFormat="1">
+        <v>-2.0629914000278582E-3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:30" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>65</v>
       </c>
@@ -7322,10 +7653,10 @@
         <v>4797</v>
       </c>
       <c r="AD100" s="2">
-        <v>-0.001446643046731699</v>
-      </c>
-    </row>
-    <row r="101" spans="1:30" s="2" customFormat="1">
+        <v>-1.4466430467316991E-3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:30" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>66</v>
       </c>
@@ -7414,10 +7745,10 @@
         <v>5585</v>
       </c>
       <c r="AD101" s="2">
-        <v>0.001972950510931826</v>
-      </c>
-    </row>
-    <row r="102" spans="1:30" s="2" customFormat="1">
+        <v>1.9729505109318262E-3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:30" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>67</v>
       </c>
@@ -7506,10 +7837,10 @@
         <v>6198</v>
       </c>
       <c r="AD102" s="2">
-        <v>0.003118598869744194</v>
-      </c>
-    </row>
-    <row r="103" spans="1:30" s="2" customFormat="1">
+        <v>3.118598869744194E-3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:30" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
         <v>68</v>
       </c>
@@ -7598,10 +7929,10 @@
         <v>1955</v>
       </c>
       <c r="AD103" s="2">
-        <v>-0.005746122510490559</v>
-      </c>
-    </row>
-    <row r="104" spans="1:30" s="2" customFormat="1">
+        <v>-5.7461225104905589E-3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:30" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
         <v>69</v>
       </c>
@@ -7690,10 +8021,10 @@
         <v>2843</v>
       </c>
       <c r="AD104" s="2">
-        <v>-0.002371054815582974</v>
-      </c>
-    </row>
-    <row r="105" spans="1:30" s="2" customFormat="1">
+        <v>-2.371054815582974E-3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:30" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
         <v>70</v>
       </c>
@@ -7782,10 +8113,10 @@
         <v>1778</v>
       </c>
       <c r="AD105" s="2">
-        <v>-0.001400863567258437</v>
-      </c>
-    </row>
-    <row r="106" spans="1:30" s="2" customFormat="1">
+        <v>-1.4008635672584371E-3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:30" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
         <v>71</v>
       </c>
@@ -7874,10 +8205,10 @@
         <v>4712</v>
       </c>
       <c r="AD106" s="2">
-        <v>-0.0003331580014124258</v>
-      </c>
-    </row>
-    <row r="107" spans="1:30" s="2" customFormat="1">
+        <v>-3.331580014124258E-4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:30" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
         <v>72</v>
       </c>
@@ -7966,10 +8297,10 @@
         <v>3104</v>
       </c>
       <c r="AD107" s="2">
-        <v>-0.002952002719077917</v>
-      </c>
-    </row>
-    <row r="108" spans="1:30" s="9" customFormat="1">
+        <v>-2.952002719077917E-3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:30" s="9" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A108" s="9" t="s">
         <v>73</v>
       </c>
@@ -8058,16 +8389,16 @@
         <v>3551.745849609375</v>
       </c>
       <c r="AD108" s="9">
-        <v>-0.002127463607979774</v>
-      </c>
-    </row>
-    <row r="109" spans="1:30" s="4" customFormat="1"/>
-    <row r="110" spans="1:30" s="6" customFormat="1">
+        <v>-2.1274636079797742E-3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="110" spans="1:30" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B110" s="6" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="111" spans="1:30" s="2" customFormat="1">
+    <row r="111" spans="1:30" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
         <v>74</v>
       </c>
@@ -8156,10 +8487,10 @@
         <v>767</v>
       </c>
       <c r="AD111" s="2">
-        <v>0.008216933791928449</v>
-      </c>
-    </row>
-    <row r="112" spans="1:30" s="2" customFormat="1">
+        <v>8.2169337919284491E-3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:30" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
         <v>75</v>
       </c>
@@ -8248,10 +8579,10 @@
         <v>1041</v>
       </c>
       <c r="AD112" s="2">
-        <v>0.007059342503465071</v>
-      </c>
-    </row>
-    <row r="113" spans="1:30" s="2" customFormat="1">
+        <v>7.0593425034650714E-3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:30" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
         <v>76</v>
       </c>
@@ -8340,10 +8671,10 @@
         <v>975</v>
       </c>
       <c r="AD113" s="2">
-        <v>0.003126200887332953</v>
-      </c>
-    </row>
-    <row r="114" spans="1:30" s="2" customFormat="1">
+        <v>3.1262008873329532E-3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:30" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>77</v>
       </c>
@@ -8432,10 +8763,10 @@
         <v>1174</v>
       </c>
       <c r="AD114" s="2">
-        <v>0.004450001046429009</v>
-      </c>
-    </row>
-    <row r="115" spans="1:30" s="2" customFormat="1">
+        <v>4.4500010464290094E-3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:30" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
         <v>78</v>
       </c>
@@ -8524,10 +8855,10 @@
         <v>2790</v>
       </c>
       <c r="AD115" s="2">
-        <v>0.005824187781875212</v>
-      </c>
-    </row>
-    <row r="116" spans="1:30" s="2" customFormat="1">
+        <v>5.8241877818752119E-3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:30" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
         <v>79</v>
       </c>
@@ -8616,10 +8947,10 @@
         <v>1963</v>
       </c>
       <c r="AD116" s="2">
-        <v>0.00209585503079146</v>
-      </c>
-    </row>
-    <row r="117" spans="1:30" s="2" customFormat="1">
+        <v>2.0958550307914599E-3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:30" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
         <v>80</v>
       </c>
@@ -8708,10 +9039,10 @@
         <v>3239</v>
       </c>
       <c r="AD117" s="2">
-        <v>0.002025523878423474</v>
-      </c>
-    </row>
-    <row r="118" spans="1:30" s="2" customFormat="1">
+        <v>2.0255238784234741E-3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:30" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>81</v>
       </c>
@@ -8800,10 +9131,10 @@
         <v>1755</v>
       </c>
       <c r="AD118" s="2">
-        <v>0.0009995563932072571</v>
-      </c>
-    </row>
-    <row r="119" spans="1:30" s="2" customFormat="1">
+        <v>9.9955639320725709E-4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:30" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
         <v>82</v>
       </c>
@@ -8892,10 +9223,10 @@
         <v>1240</v>
       </c>
       <c r="AD119" s="2">
-        <v>0.006196937223997168</v>
-      </c>
-    </row>
-    <row r="120" spans="1:30" s="9" customFormat="1">
+        <v>6.1969372239971676E-3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:30" s="9" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A120" s="9" t="s">
         <v>83</v>
       </c>
@@ -8984,10 +9315,10 @@
         <v>1871.439208984375</v>
       </c>
       <c r="AD120" s="9">
-        <v>0.005638823979331908</v>
-      </c>
-    </row>
-    <row r="121" spans="1:30" s="4" customFormat="1">
+        <v>5.6388239793319084E-3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B121" s="10"/>
       <c r="C121" s="10"/>
       <c r="D121" s="10"/>
@@ -9018,220 +9349,410 @@
       <c r="AC121" s="10"/>
       <c r="AD121" s="10"/>
     </row>
-    <row r="122" spans="1:30" s="4" customFormat="1">
+    <row r="122" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B122" s="4" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="123" spans="1:30" s="4" customFormat="1">
+    <row r="123" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B123" s="4" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="124" spans="1:30" s="4" customFormat="1">
+    <row r="124" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B124" s="4" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="125" spans="1:30" s="4" customFormat="1">
+    <row r="125" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B125" s="4" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="126" spans="1:30" s="4" customFormat="1">
+    <row r="126" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B126" s="4" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="127" spans="1:30" s="4" customFormat="1">
+    <row r="127" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B127" s="4" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="128" spans="1:30" s="4" customFormat="1">
+    <row r="128" spans="1:30" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B128" s="4" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="129" spans="2:2" s="4" customFormat="1">
+    <row r="129" spans="2:2" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B129" s="4" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="130" spans="2:2" s="4" customFormat="1">
+    <row r="130" spans="2:2" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B130" s="4" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="131" spans="2:2" s="4" customFormat="1">
+    <row r="131" spans="2:2" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B131" s="4" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="132" spans="2:2" s="4" customFormat="1">
+    <row r="132" spans="2:2" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B132" s="4" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="133" spans="2:2" s="4" customFormat="1">
+    <row r="133" spans="2:2" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B133" s="4" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="134" spans="2:2" s="4" customFormat="1">
+    <row r="134" spans="2:2" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B134" s="4" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="135" spans="2:2" s="4" customFormat="1">
+    <row r="135" spans="2:2" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B135" s="4" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="136" spans="2:2" s="4" customFormat="1">
+    <row r="136" spans="2:2" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B136" s="4" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="137" spans="2:2" s="4" customFormat="1">
+    <row r="137" spans="2:2" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B137" s="4" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="138" spans="2:2" s="4" customFormat="1">
+    <row r="138" spans="2:2" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B138" s="4" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="139" spans="2:2" s="4" customFormat="1">
+    <row r="139" spans="2:2" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B139" s="4" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="140" spans="2:2" s="4" customFormat="1">
+    <row r="140" spans="2:2" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B140" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="141" spans="2:2" s="4" customFormat="1">
+    <row r="141" spans="2:2" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B141" s="4" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="142" spans="2:2" s="4" customFormat="1">
+    <row r="142" spans="2:2" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B142" s="4" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="143" spans="2:2" s="4" customFormat="1">
+    <row r="143" spans="2:2" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B143" s="4" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="144" spans="2:2" s="4" customFormat="1">
+    <row r="144" spans="2:2" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B144" s="4" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="145" spans="2:2" s="4" customFormat="1">
+    <row r="145" spans="2:2" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B145" s="4" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="146" spans="2:2" s="4" customFormat="1">
+    <row r="146" spans="2:2" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B146" s="4" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="147" spans="2:2" s="4" customFormat="1">
+    <row r="147" spans="2:2" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B147" s="4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="148" spans="2:2" s="4" customFormat="1">
+    <row r="148" spans="2:2" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B148" s="4" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="149" spans="2:2" s="4" customFormat="1">
+    <row r="149" spans="2:2" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B149" s="4" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="150" spans="2:2" s="4" customFormat="1">
+    <row r="150" spans="2:2" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B150" s="4" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="151" spans="2:2" s="4" customFormat="1">
+    <row r="151" spans="2:2" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B151" s="4" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="152" spans="2:2" s="4" customFormat="1">
+    <row r="152" spans="2:2" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B152" s="4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="153" spans="2:2" s="4" customFormat="1">
+    <row r="153" spans="2:2" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="B153" s="4" t="s">
         <v>179</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A10:AD10">
-    <cfRule type="notContainsBlanks" dxfId="3" priority="10">
+    <cfRule type="notContainsBlanks" dxfId="54" priority="10">
       <formula>LEN(TRIM(A10))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1">
-    <cfRule type="notContainsBlanks" dxfId="0" priority="1">
+    <cfRule type="notContainsBlanks" dxfId="53" priority="1">
       <formula>LEN(TRIM(AD1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AD2:AD6">
+    <cfRule type="notContainsBlanks" dxfId="52" priority="2">
+      <formula>LEN(TRIM(AD2))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD7">
+    <cfRule type="notContainsBlanks" dxfId="51" priority="7">
+      <formula>LEN(TRIM(AD7))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD8:AD9">
+    <cfRule type="notContainsBlanks" dxfId="50" priority="8">
+      <formula>LEN(TRIM(AD8))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AD10">
-    <cfRule type="notContainsBlanks" dxfId="4" priority="11">
+    <cfRule type="notContainsBlanks" dxfId="49" priority="11">
       <formula>LEN(TRIM(AD10))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD100">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="101">
-      <formula>LEN(TRIM(AD100))&gt;0</formula>
+  <conditionalFormatting sqref="AD11">
+    <cfRule type="notContainsBlanks" dxfId="48" priority="12">
+      <formula>LEN(TRIM(AD11))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD101">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="102">
-      <formula>LEN(TRIM(AD101))&gt;0</formula>
+  <conditionalFormatting sqref="AD12">
+    <cfRule type="notContainsBlanks" dxfId="47" priority="13">
+      <formula>LEN(TRIM(AD12))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD102">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="103">
-      <formula>LEN(TRIM(AD102))&gt;0</formula>
+  <conditionalFormatting sqref="AD13">
+    <cfRule type="notContainsBlanks" dxfId="46" priority="14">
+      <formula>LEN(TRIM(AD13))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD103">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="104">
-      <formula>LEN(TRIM(AD103))&gt;0</formula>
+  <conditionalFormatting sqref="AD14">
+    <cfRule type="notContainsBlanks" dxfId="45" priority="15">
+      <formula>LEN(TRIM(AD14))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD104">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="105">
-      <formula>LEN(TRIM(AD104))&gt;0</formula>
+  <conditionalFormatting sqref="AD15:AD16">
+    <cfRule type="notContainsBlanks" dxfId="44" priority="16">
+      <formula>LEN(TRIM(AD15))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD105">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="106">
-      <formula>LEN(TRIM(AD105))&gt;0</formula>
+  <conditionalFormatting sqref="AD17">
+    <cfRule type="notContainsBlanks" dxfId="43" priority="18">
+      <formula>LEN(TRIM(AD17))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD106">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="107">
-      <formula>LEN(TRIM(AD106))&gt;0</formula>
+  <conditionalFormatting sqref="AD18">
+    <cfRule type="notContainsBlanks" dxfId="42" priority="19">
+      <formula>LEN(TRIM(AD18))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD107">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="108">
-      <formula>LEN(TRIM(AD107))&gt;0</formula>
+  <conditionalFormatting sqref="AD19:AD20">
+    <cfRule type="notContainsBlanks" dxfId="41" priority="20">
+      <formula>LEN(TRIM(AD19))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD21:AD23">
+    <cfRule type="notContainsBlanks" dxfId="40" priority="22">
+      <formula>LEN(TRIM(AD21))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD24:AD25">
+    <cfRule type="notContainsBlanks" dxfId="39" priority="25">
+      <formula>LEN(TRIM(AD24))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD26:AD35">
+    <cfRule type="notContainsBlanks" dxfId="38" priority="27">
+      <formula>LEN(TRIM(AD26))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD36">
+    <cfRule type="notContainsBlanks" dxfId="37" priority="37">
+      <formula>LEN(TRIM(AD36))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD37:AD38">
+    <cfRule type="notContainsBlanks" dxfId="36" priority="38">
+      <formula>LEN(TRIM(AD37))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD39">
+    <cfRule type="notContainsBlanks" dxfId="35" priority="40">
+      <formula>LEN(TRIM(AD39))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD40">
+    <cfRule type="notContainsBlanks" dxfId="34" priority="41">
+      <formula>LEN(TRIM(AD40))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD41">
+    <cfRule type="notContainsBlanks" dxfId="33" priority="42">
+      <formula>LEN(TRIM(AD41))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD42:AD46">
+    <cfRule type="notContainsBlanks" dxfId="32" priority="43">
+      <formula>LEN(TRIM(AD42))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD47">
+    <cfRule type="notContainsBlanks" dxfId="31" priority="48">
+      <formula>LEN(TRIM(AD47))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD48">
+    <cfRule type="notContainsBlanks" dxfId="30" priority="49">
+      <formula>LEN(TRIM(AD48))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD49">
+    <cfRule type="notContainsBlanks" dxfId="29" priority="50">
+      <formula>LEN(TRIM(AD49))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD50:AD52">
+    <cfRule type="notContainsBlanks" dxfId="28" priority="51">
+      <formula>LEN(TRIM(AD50))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD53">
+    <cfRule type="notContainsBlanks" dxfId="27" priority="54">
+      <formula>LEN(TRIM(AD53))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD54:AD57">
+    <cfRule type="notContainsBlanks" dxfId="26" priority="55">
+      <formula>LEN(TRIM(AD54))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD58">
+    <cfRule type="notContainsBlanks" dxfId="25" priority="59">
+      <formula>LEN(TRIM(AD58))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD59:AD68">
+    <cfRule type="notContainsBlanks" dxfId="24" priority="60">
+      <formula>LEN(TRIM(AD59))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD69">
+    <cfRule type="notContainsBlanks" dxfId="23" priority="70">
+      <formula>LEN(TRIM(AD69))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD70:AD71">
+    <cfRule type="notContainsBlanks" dxfId="22" priority="71">
+      <formula>LEN(TRIM(AD70))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD72">
+    <cfRule type="notContainsBlanks" dxfId="21" priority="73">
+      <formula>LEN(TRIM(AD72))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD73">
+    <cfRule type="notContainsBlanks" dxfId="20" priority="74">
+      <formula>LEN(TRIM(AD73))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD74">
+    <cfRule type="notContainsBlanks" dxfId="19" priority="75">
+      <formula>LEN(TRIM(AD74))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD75">
+    <cfRule type="notContainsBlanks" dxfId="18" priority="76">
+      <formula>LEN(TRIM(AD75))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD76">
+    <cfRule type="notContainsBlanks" dxfId="17" priority="77">
+      <formula>LEN(TRIM(AD76))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD77:AD86">
+    <cfRule type="notContainsBlanks" dxfId="16" priority="78">
+      <formula>LEN(TRIM(AD77))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD87">
+    <cfRule type="notContainsBlanks" dxfId="15" priority="88">
+      <formula>LEN(TRIM(AD87))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD88:AD89">
+    <cfRule type="notContainsBlanks" dxfId="14" priority="89">
+      <formula>LEN(TRIM(AD88))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD90">
+    <cfRule type="notContainsBlanks" dxfId="13" priority="91">
+      <formula>LEN(TRIM(AD90))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD91">
+    <cfRule type="notContainsBlanks" dxfId="12" priority="92">
+      <formula>LEN(TRIM(AD91))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD92">
+    <cfRule type="notContainsBlanks" dxfId="11" priority="93">
+      <formula>LEN(TRIM(AD92))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD93:AD95">
+    <cfRule type="notContainsBlanks" dxfId="10" priority="94">
+      <formula>LEN(TRIM(AD93))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD96">
+    <cfRule type="notContainsBlanks" dxfId="9" priority="97">
+      <formula>LEN(TRIM(AD96))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD97">
+    <cfRule type="notContainsBlanks" dxfId="8" priority="98">
+      <formula>LEN(TRIM(AD97))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD98">
+    <cfRule type="notContainsBlanks" dxfId="7" priority="99">
+      <formula>LEN(TRIM(AD98))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD99:AD107">
+    <cfRule type="notContainsBlanks" dxfId="6" priority="100">
+      <formula>LEN(TRIM(AD99))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD108">
@@ -9240,713 +9761,28 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD109">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="110">
+    <cfRule type="notContainsBlanks" dxfId="4" priority="110">
       <formula>LEN(TRIM(AD109))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD11">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="12">
-      <formula>LEN(TRIM(AD11))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AD110">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="111">
+    <cfRule type="notContainsBlanks" dxfId="3" priority="111">
       <formula>LEN(TRIM(AD110))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD111">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="112">
+  <conditionalFormatting sqref="AD111:AD119">
+    <cfRule type="notContainsBlanks" dxfId="2" priority="112">
       <formula>LEN(TRIM(AD111))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD112">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="113">
-      <formula>LEN(TRIM(AD112))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD113">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="114">
-      <formula>LEN(TRIM(AD113))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD114">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="115">
-      <formula>LEN(TRIM(AD114))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD115">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="116">
-      <formula>LEN(TRIM(AD115))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD116">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="117">
-      <formula>LEN(TRIM(AD116))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD117">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="118">
-      <formula>LEN(TRIM(AD117))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD118">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="119">
-      <formula>LEN(TRIM(AD118))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD119">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="120">
-      <formula>LEN(TRIM(AD119))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD12">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="13">
-      <formula>LEN(TRIM(AD12))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AD120">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="121">
+    <cfRule type="notContainsBlanks" dxfId="1" priority="121">
       <formula>LEN(TRIM(AD120))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD121">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="122">
+  <conditionalFormatting sqref="AD121:AD153">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="122">
       <formula>LEN(TRIM(AD121))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD122">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="123">
-      <formula>LEN(TRIM(AD122))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD123">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="124">
-      <formula>LEN(TRIM(AD123))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD124">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="125">
-      <formula>LEN(TRIM(AD124))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD125">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="126">
-      <formula>LEN(TRIM(AD125))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD126">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="127">
-      <formula>LEN(TRIM(AD126))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD127">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="128">
-      <formula>LEN(TRIM(AD127))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD128">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="129">
-      <formula>LEN(TRIM(AD128))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD129">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="130">
-      <formula>LEN(TRIM(AD129))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD13">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="14">
-      <formula>LEN(TRIM(AD13))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD130">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="131">
-      <formula>LEN(TRIM(AD130))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD131">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="132">
-      <formula>LEN(TRIM(AD131))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD132">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="133">
-      <formula>LEN(TRIM(AD132))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD133">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="134">
-      <formula>LEN(TRIM(AD133))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD134">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="135">
-      <formula>LEN(TRIM(AD134))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD135">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="136">
-      <formula>LEN(TRIM(AD135))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD136">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="137">
-      <formula>LEN(TRIM(AD136))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD137">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="138">
-      <formula>LEN(TRIM(AD137))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD138">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="139">
-      <formula>LEN(TRIM(AD138))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD139">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="140">
-      <formula>LEN(TRIM(AD139))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD14">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="15">
-      <formula>LEN(TRIM(AD14))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD140">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="141">
-      <formula>LEN(TRIM(AD140))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD141">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="142">
-      <formula>LEN(TRIM(AD141))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD142">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="143">
-      <formula>LEN(TRIM(AD142))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD143">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="144">
-      <formula>LEN(TRIM(AD143))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD144">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="145">
-      <formula>LEN(TRIM(AD144))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD145">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="146">
-      <formula>LEN(TRIM(AD145))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD146">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="147">
-      <formula>LEN(TRIM(AD146))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD147">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="148">
-      <formula>LEN(TRIM(AD147))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD148">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="149">
-      <formula>LEN(TRIM(AD148))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD149">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="150">
-      <formula>LEN(TRIM(AD149))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD15">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="16">
-      <formula>LEN(TRIM(AD15))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD150">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="151">
-      <formula>LEN(TRIM(AD150))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD151">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="152">
-      <formula>LEN(TRIM(AD151))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD152">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="153">
-      <formula>LEN(TRIM(AD152))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD153">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="154">
-      <formula>LEN(TRIM(AD153))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD16">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="17">
-      <formula>LEN(TRIM(AD16))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD17">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="18">
-      <formula>LEN(TRIM(AD17))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD18">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="19">
-      <formula>LEN(TRIM(AD18))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD19">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="20">
-      <formula>LEN(TRIM(AD19))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD2">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="2">
-      <formula>LEN(TRIM(AD2))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD20">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="21">
-      <formula>LEN(TRIM(AD20))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD21">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="22">
-      <formula>LEN(TRIM(AD21))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD22">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="23">
-      <formula>LEN(TRIM(AD22))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD23">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="24">
-      <formula>LEN(TRIM(AD23))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD24">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="25">
-      <formula>LEN(TRIM(AD24))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD25">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="26">
-      <formula>LEN(TRIM(AD25))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD26">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="27">
-      <formula>LEN(TRIM(AD26))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD27">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="28">
-      <formula>LEN(TRIM(AD27))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD28">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="29">
-      <formula>LEN(TRIM(AD28))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD29">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="30">
-      <formula>LEN(TRIM(AD29))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD3">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="3">
-      <formula>LEN(TRIM(AD3))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD30">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="31">
-      <formula>LEN(TRIM(AD30))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD31">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="32">
-      <formula>LEN(TRIM(AD31))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD32">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="33">
-      <formula>LEN(TRIM(AD32))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD33">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="34">
-      <formula>LEN(TRIM(AD33))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD34">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="35">
-      <formula>LEN(TRIM(AD34))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD35">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="36">
-      <formula>LEN(TRIM(AD35))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD36">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="37">
-      <formula>LEN(TRIM(AD36))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD37">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="38">
-      <formula>LEN(TRIM(AD37))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD38">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="39">
-      <formula>LEN(TRIM(AD38))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD39">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="40">
-      <formula>LEN(TRIM(AD39))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD4">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="4">
-      <formula>LEN(TRIM(AD4))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD40">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="41">
-      <formula>LEN(TRIM(AD40))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD41">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="42">
-      <formula>LEN(TRIM(AD41))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD42">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="43">
-      <formula>LEN(TRIM(AD42))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD43">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="44">
-      <formula>LEN(TRIM(AD43))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD44">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="45">
-      <formula>LEN(TRIM(AD44))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD45">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="46">
-      <formula>LEN(TRIM(AD45))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD46">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="47">
-      <formula>LEN(TRIM(AD46))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD47">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="48">
-      <formula>LEN(TRIM(AD47))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD48">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="49">
-      <formula>LEN(TRIM(AD48))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD49">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="50">
-      <formula>LEN(TRIM(AD49))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD5">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="5">
-      <formula>LEN(TRIM(AD5))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD50">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="51">
-      <formula>LEN(TRIM(AD50))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD51">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="52">
-      <formula>LEN(TRIM(AD51))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD52">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="53">
-      <formula>LEN(TRIM(AD52))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD53">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="54">
-      <formula>LEN(TRIM(AD53))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD54">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="55">
-      <formula>LEN(TRIM(AD54))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD55">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="56">
-      <formula>LEN(TRIM(AD55))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD56">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="57">
-      <formula>LEN(TRIM(AD56))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD57">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="58">
-      <formula>LEN(TRIM(AD57))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD58">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="59">
-      <formula>LEN(TRIM(AD58))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD59">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="60">
-      <formula>LEN(TRIM(AD59))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD6">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="6">
-      <formula>LEN(TRIM(AD6))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD60">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="61">
-      <formula>LEN(TRIM(AD60))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD61">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="62">
-      <formula>LEN(TRIM(AD61))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD62">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="63">
-      <formula>LEN(TRIM(AD62))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD63">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="64">
-      <formula>LEN(TRIM(AD63))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD64">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="65">
-      <formula>LEN(TRIM(AD64))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD65">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="66">
-      <formula>LEN(TRIM(AD65))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD66">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="67">
-      <formula>LEN(TRIM(AD66))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD67">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="68">
-      <formula>LEN(TRIM(AD67))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD68">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="69">
-      <formula>LEN(TRIM(AD68))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD69">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="70">
-      <formula>LEN(TRIM(AD69))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD7">
-    <cfRule type="notContainsBlanks" dxfId="2" priority="7">
-      <formula>LEN(TRIM(AD7))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD70">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="71">
-      <formula>LEN(TRIM(AD70))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD71">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="72">
-      <formula>LEN(TRIM(AD71))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD72">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="73">
-      <formula>LEN(TRIM(AD72))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD73">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="74">
-      <formula>LEN(TRIM(AD73))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD74">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="75">
-      <formula>LEN(TRIM(AD74))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD75">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="76">
-      <formula>LEN(TRIM(AD75))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD76">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="77">
-      <formula>LEN(TRIM(AD76))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD77">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="78">
-      <formula>LEN(TRIM(AD77))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD78">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="79">
-      <formula>LEN(TRIM(AD78))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD79">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="80">
-      <formula>LEN(TRIM(AD79))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD8">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="8">
-      <formula>LEN(TRIM(AD8))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD80">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="81">
-      <formula>LEN(TRIM(AD80))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD81">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="82">
-      <formula>LEN(TRIM(AD81))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD82">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="83">
-      <formula>LEN(TRIM(AD82))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD83">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="84">
-      <formula>LEN(TRIM(AD83))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD84">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="85">
-      <formula>LEN(TRIM(AD84))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD85">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="86">
-      <formula>LEN(TRIM(AD85))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD86">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="87">
-      <formula>LEN(TRIM(AD86))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD87">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="88">
-      <formula>LEN(TRIM(AD87))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD88">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="89">
-      <formula>LEN(TRIM(AD88))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD89">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="90">
-      <formula>LEN(TRIM(AD89))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD9">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="9">
-      <formula>LEN(TRIM(AD9))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD90">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="91">
-      <formula>LEN(TRIM(AD90))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD91">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="92">
-      <formula>LEN(TRIM(AD91))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD92">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="93">
-      <formula>LEN(TRIM(AD92))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD93">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="94">
-      <formula>LEN(TRIM(AD93))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD94">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="95">
-      <formula>LEN(TRIM(AD94))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD95">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="96">
-      <formula>LEN(TRIM(AD95))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD96">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="97">
-      <formula>LEN(TRIM(AD96))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD97">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="98">
-      <formula>LEN(TRIM(AD97))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD98">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="99">
-      <formula>LEN(TRIM(AD98))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD99">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="100">
-      <formula>LEN(TRIM(AD99))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
